--- a/Financial Analysis/GAMB.xlsx
+++ b/Financial Analysis/GAMB.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB6662D-1FC4-4391-AEC9-6531E1D0B208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{129F8979-8BC3-4807-8B5D-2B0E68B1469E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{D6459E68-7D6A-410F-A9B8-1584227EFFA5}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="62">
   <si>
     <t>GAMB</t>
   </si>
@@ -209,6 +209,9 @@
   </si>
   <si>
     <t>Heavily undervalued</t>
+  </si>
+  <si>
+    <t>Q125 6K</t>
   </si>
 </sst>
 </file>
@@ -333,6 +336,56 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16131540" y="7620"/>
+          <a:ext cx="0" cy="6134100"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="4" name="Straight Connector 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7F1B35D1-099F-1556-358B-853D4DA27A87}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9433560" y="7620"/>
           <a:ext cx="0" cy="6134100"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -681,17 +734,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>12.25</v>
+        <v>12.02</v>
       </c>
       <c r="E3" s="4">
-        <v>45751</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45751</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="4">
-        <v>45792</v>
+        <v>45883</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -699,7 +752,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="2">
-        <v>34.799999999999997</v>
+        <f>35.6</f>
+        <v>35.6</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -708,7 +765,7 @@
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>426.29999999999995</v>
+        <v>427.91199999999998</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -716,8 +773,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="2">
-        <f>13.7</f>
-        <v>13.7</v>
+        <f>21.5</f>
+        <v>21.5</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -725,8 +785,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="2">
-        <f>19.6+3.3</f>
-        <v>22.900000000000002</v>
+        <f>10.4+78.1</f>
+        <v>88.5</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -735,7 +798,7 @@
       </c>
       <c r="D8" s="2">
         <f>D6-D7</f>
-        <v>-9.2000000000000028</v>
+        <v>-67</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -744,7 +807,7 @@
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>435.49999999999994</v>
+        <v>494.91199999999998</v>
       </c>
     </row>
   </sheetData>
@@ -871,9 +934,15 @@
       <c r="J3" s="8">
         <v>32.5</v>
       </c>
+      <c r="K3" s="8">
+        <v>29.2</v>
+      </c>
       <c r="N3" s="8">
         <v>35.299999999999997</v>
       </c>
+      <c r="O3" s="8">
+        <v>40.6</v>
+      </c>
       <c r="T3" s="8">
         <v>19.3</v>
       </c>
@@ -896,44 +965,44 @@
         <v>170</v>
       </c>
       <c r="AA3" s="8">
-        <f>Z3*1.15</f>
-        <v>195.49999999999997</v>
+        <f>Z3*1.17</f>
+        <v>198.89999999999998</v>
       </c>
       <c r="AB3" s="8">
-        <f>AA3*1.08</f>
-        <v>211.14</v>
+        <f>AA3*1.09</f>
+        <v>216.80099999999999</v>
       </c>
       <c r="AC3" s="8">
         <f>AB3*1.07</f>
-        <v>225.91980000000001</v>
+        <v>231.97707</v>
       </c>
       <c r="AD3" s="8">
         <f>AC3*1.06</f>
-        <v>239.47498800000002</v>
+        <v>245.89569420000001</v>
       </c>
       <c r="AE3" s="8">
         <f>AD3*1.05</f>
-        <v>251.44873740000003</v>
+        <v>258.19047891000002</v>
       </c>
       <c r="AF3" s="8">
         <f t="shared" ref="AF3:AJ3" si="0">AE3*1.05</f>
-        <v>264.02117427000002</v>
+        <v>271.10000285550007</v>
       </c>
       <c r="AG3" s="8">
         <f t="shared" si="0"/>
-        <v>277.22223298350002</v>
+        <v>284.65500299827511</v>
       </c>
       <c r="AH3" s="8">
         <f t="shared" si="0"/>
-        <v>291.08334463267505</v>
+        <v>298.88775314818889</v>
       </c>
       <c r="AI3" s="8">
         <f t="shared" si="0"/>
-        <v>305.63751186430881</v>
+        <v>313.83214080559833</v>
       </c>
       <c r="AJ3" s="8">
         <f t="shared" si="0"/>
-        <v>320.91938745752424</v>
+        <v>329.52374784587823</v>
       </c>
     </row>
     <row r="4" spans="2:36" x14ac:dyDescent="0.3">
@@ -943,7 +1012,13 @@
       <c r="J4" s="2">
         <v>5.0999999999999996</v>
       </c>
+      <c r="K4" s="2">
+        <v>2.2000000000000002</v>
+      </c>
       <c r="N4" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="O4" s="2">
         <v>2.2000000000000002</v>
       </c>
       <c r="T4" s="2"/>
@@ -964,43 +1039,43 @@
       </c>
       <c r="AA4" s="2">
         <f>AA3-AA5</f>
-        <v>11.730000000000018</v>
+        <v>11.933999999999997</v>
       </c>
       <c r="AB4" s="2">
         <f t="shared" ref="AB4:AJ4" si="1">AB3-AB5</f>
-        <v>12.66840000000002</v>
+        <v>13.00806</v>
       </c>
       <c r="AC4" s="2">
         <f t="shared" si="1"/>
-        <v>13.555188000000015</v>
+        <v>13.918624200000011</v>
       </c>
       <c r="AD4" s="2">
         <f t="shared" si="1"/>
-        <v>14.368499280000009</v>
+        <v>14.753741652000002</v>
       </c>
       <c r="AE4" s="2">
         <f t="shared" si="1"/>
-        <v>15.086924244000016</v>
+        <v>15.491428734600021</v>
       </c>
       <c r="AF4" s="2">
         <f t="shared" si="1"/>
-        <v>15.841270456200021</v>
+        <v>16.266000171330006</v>
       </c>
       <c r="AG4" s="2">
         <f t="shared" si="1"/>
-        <v>16.63333397900999</v>
+        <v>17.079300179896507</v>
       </c>
       <c r="AH4" s="2">
         <f t="shared" si="1"/>
-        <v>17.465000677960518</v>
+        <v>17.933265188891369</v>
       </c>
       <c r="AI4" s="2">
         <f t="shared" si="1"/>
-        <v>18.338250711858564</v>
+        <v>18.82992844833592</v>
       </c>
       <c r="AJ4" s="2">
         <f t="shared" si="1"/>
-        <v>19.255163247451492</v>
+        <v>19.771424870752696</v>
       </c>
     </row>
     <row r="5" spans="2:36" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1011,10 +1086,18 @@
         <f>J3-J4</f>
         <v>27.4</v>
       </c>
+      <c r="K5" s="8">
+        <f>K3-K4</f>
+        <v>27</v>
+      </c>
       <c r="N5" s="8">
         <f>N3-N4</f>
         <v>33.099999999999994</v>
       </c>
+      <c r="O5" s="8">
+        <f>O3-O4</f>
+        <v>38.4</v>
+      </c>
       <c r="T5" s="8">
         <f t="shared" ref="T5:Y5" si="2">T3-T4</f>
         <v>19.3</v>
@@ -1045,43 +1128,43 @@
       </c>
       <c r="AA5" s="8">
         <f>AA3*0.94</f>
-        <v>183.76999999999995</v>
+        <v>186.96599999999998</v>
       </c>
       <c r="AB5" s="8">
         <f t="shared" ref="AB5:AJ5" si="3">AB3*0.94</f>
-        <v>198.47159999999997</v>
+        <v>203.79293999999999</v>
       </c>
       <c r="AC5" s="8">
         <f t="shared" si="3"/>
-        <v>212.36461199999999</v>
+        <v>218.05844579999999</v>
       </c>
       <c r="AD5" s="8">
         <f t="shared" si="3"/>
-        <v>225.10648872000002</v>
+        <v>231.14195254800001</v>
       </c>
       <c r="AE5" s="8">
         <f t="shared" si="3"/>
-        <v>236.36181315600001</v>
+        <v>242.6990501754</v>
       </c>
       <c r="AF5" s="8">
         <f t="shared" si="3"/>
-        <v>248.1799038138</v>
+        <v>254.83400268417006</v>
       </c>
       <c r="AG5" s="8">
         <f t="shared" si="3"/>
-        <v>260.58889900449003</v>
+        <v>267.5757028183786</v>
       </c>
       <c r="AH5" s="8">
         <f t="shared" si="3"/>
-        <v>273.61834395471453</v>
+        <v>280.95448795929752</v>
       </c>
       <c r="AI5" s="8">
         <f t="shared" si="3"/>
-        <v>287.29926115245024</v>
+        <v>295.00221235726241</v>
       </c>
       <c r="AJ5" s="8">
         <f t="shared" si="3"/>
-        <v>301.66422421007275</v>
+        <v>309.75232297512554</v>
       </c>
     </row>
     <row r="6" spans="2:36" x14ac:dyDescent="0.3">
@@ -1091,8 +1174,14 @@
       <c r="J6" s="2">
         <v>9.6999999999999993</v>
       </c>
+      <c r="K6" s="2">
+        <v>9.6</v>
+      </c>
       <c r="N6" s="2">
         <v>10.9</v>
+      </c>
+      <c r="O6" s="2">
+        <v>15.2</v>
       </c>
       <c r="T6" s="2">
         <v>10.9</v>
@@ -1118,43 +1207,43 @@
       </c>
       <c r="AA6" s="2">
         <f>AA3*0.31</f>
-        <v>60.60499999999999</v>
+        <v>61.658999999999992</v>
       </c>
       <c r="AB6" s="2">
         <f>AB3*0.31</f>
-        <v>65.453400000000002</v>
+        <v>67.208309999999997</v>
       </c>
       <c r="AC6" s="2">
         <f t="shared" ref="AC6:AJ6" si="4">AC3*0.31</f>
-        <v>70.035138000000003</v>
+        <v>71.912891700000003</v>
       </c>
       <c r="AD6" s="2">
         <f t="shared" si="4"/>
-        <v>74.237246280000008</v>
+        <v>76.227665201999997</v>
       </c>
       <c r="AE6" s="2">
         <f t="shared" si="4"/>
-        <v>77.949108594000009</v>
+        <v>80.039048462100013</v>
       </c>
       <c r="AF6" s="2">
         <f t="shared" si="4"/>
-        <v>81.846564023700012</v>
+        <v>84.041000885205023</v>
       </c>
       <c r="AG6" s="2">
         <f t="shared" si="4"/>
-        <v>85.938892224885009</v>
+        <v>88.243050929465284</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="4"/>
-        <v>90.235836836129266</v>
+        <v>92.655203475938549</v>
       </c>
       <c r="AI6" s="2">
         <f t="shared" si="4"/>
-        <v>94.747628677935722</v>
+        <v>97.287963649735488</v>
       </c>
       <c r="AJ6" s="2">
         <f t="shared" si="4"/>
-        <v>99.485010111832509</v>
+        <v>102.15236183222225</v>
       </c>
     </row>
     <row r="7" spans="2:36" x14ac:dyDescent="0.3">
@@ -1164,8 +1253,14 @@
       <c r="J7" s="2">
         <v>3.1</v>
       </c>
+      <c r="K7" s="2">
+        <v>3.2</v>
+      </c>
       <c r="N7" s="2">
         <v>3.9</v>
+      </c>
+      <c r="O7" s="2">
+        <v>5.2</v>
       </c>
       <c r="T7" s="2">
         <v>2.5</v>
@@ -1190,44 +1285,44 @@
         <v>16.957999999999998</v>
       </c>
       <c r="AA7" s="2">
-        <f>Z7*1.2</f>
-        <v>20.349599999999999</v>
+        <f>Z7*1.18</f>
+        <v>20.010439999999996</v>
       </c>
       <c r="AB7" s="2">
-        <f>AA7*1.15</f>
-        <v>23.402039999999996</v>
+        <f>AA7*1.14</f>
+        <v>22.811901599999992</v>
       </c>
       <c r="AC7" s="2">
         <f>AB7*1.1</f>
-        <v>25.742243999999996</v>
+        <v>25.093091759999993</v>
       </c>
       <c r="AD7" s="2">
         <f>AC7*1.05</f>
-        <v>27.029356199999995</v>
+        <v>26.347746347999994</v>
       </c>
       <c r="AE7" s="2">
-        <f t="shared" ref="AE7:AJ7" si="5">AD7*1.05</f>
-        <v>28.380824009999998</v>
+        <f t="shared" ref="AE7" si="5">AD7*1.05</f>
+        <v>27.665133665399996</v>
       </c>
       <c r="AF7" s="2">
-        <f t="shared" si="5"/>
-        <v>29.799865210499998</v>
+        <f>AE7*1.04</f>
+        <v>28.771739012015995</v>
       </c>
       <c r="AG7" s="2">
-        <f t="shared" si="5"/>
-        <v>31.289858471024999</v>
+        <f>AF7*1.03</f>
+        <v>29.634891182376474</v>
       </c>
       <c r="AH7" s="2">
-        <f t="shared" si="5"/>
-        <v>32.854351394576248</v>
+        <f>AG7*1.02</f>
+        <v>30.227589006024004</v>
       </c>
       <c r="AI7" s="2">
-        <f t="shared" si="5"/>
-        <v>34.497068964305065</v>
+        <f t="shared" ref="AI7:AJ7" si="6">AH7*1.02</f>
+        <v>30.832140786144485</v>
       </c>
       <c r="AJ7" s="2">
-        <f t="shared" si="5"/>
-        <v>36.221922412520321</v>
+        <f t="shared" si="6"/>
+        <v>31.448783601867376</v>
       </c>
     </row>
     <row r="8" spans="2:36" x14ac:dyDescent="0.3">
@@ -1237,8 +1332,14 @@
       <c r="J8" s="2">
         <v>7</v>
       </c>
+      <c r="K8" s="2">
+        <v>6.3</v>
+      </c>
       <c r="N8" s="2">
         <v>9</v>
+      </c>
+      <c r="O8" s="2">
+        <v>7.7</v>
       </c>
       <c r="T8" s="2">
         <v>4.2</v>
@@ -1279,27 +1380,27 @@
         <v>44.624853000000002</v>
       </c>
       <c r="AE8" s="2">
-        <f t="shared" ref="AE8:AJ8" si="6">AD8*1.02</f>
+        <f t="shared" ref="AE8:AJ8" si="7">AD8*1.02</f>
         <v>45.517350060000005</v>
       </c>
       <c r="AF8" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>46.427697061200007</v>
       </c>
       <c r="AG8" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>47.35625100242401</v>
       </c>
       <c r="AH8" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>48.303376022472492</v>
       </c>
       <c r="AI8" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>49.269443542921941</v>
       </c>
       <c r="AJ8" s="2">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>50.254832413780377</v>
       </c>
     </row>
@@ -1311,77 +1412,85 @@
         <f>SUM(J6:J8)</f>
         <v>19.799999999999997</v>
       </c>
+      <c r="K9" s="2">
+        <f>SUM(K6:K8)</f>
+        <v>19.100000000000001</v>
+      </c>
       <c r="N9" s="2">
         <f>SUM(N6:N8)</f>
         <v>23.8</v>
       </c>
+      <c r="O9" s="2">
+        <f>SUM(O6:O8)</f>
+        <v>28.099999999999998</v>
+      </c>
       <c r="T9" s="2">
-        <f t="shared" ref="T9:Y9" si="7">SUM(T6:T8)</f>
+        <f t="shared" ref="T9:Y9" si="8">SUM(T6:T8)</f>
         <v>17.600000000000001</v>
       </c>
       <c r="U9" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>16.600000000000001</v>
       </c>
       <c r="V9" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>31</v>
       </c>
       <c r="W9" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>60</v>
       </c>
       <c r="X9" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>69.899999999999991</v>
       </c>
       <c r="Y9" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>83.4</v>
       </c>
       <c r="Z9" s="2">
-        <f t="shared" ref="Z9:AJ9" si="8">SUM(Z6:Z8)</f>
+        <f t="shared" ref="Z9:AJ9" si="9">SUM(Z6:Z8)</f>
         <v>105.858</v>
       </c>
       <c r="AA9" s="2">
-        <f t="shared" si="8"/>
-        <v>120.62959999999998</v>
+        <f t="shared" si="9"/>
+        <v>121.34443999999998</v>
       </c>
       <c r="AB9" s="2">
-        <f t="shared" si="8"/>
-        <v>130.51418999999999</v>
+        <f t="shared" si="9"/>
+        <v>131.67896159999998</v>
       </c>
       <c r="AC9" s="2">
-        <f t="shared" si="8"/>
-        <v>139.10248200000001</v>
+        <f t="shared" si="9"/>
+        <v>140.33108346</v>
       </c>
       <c r="AD9" s="2">
-        <f t="shared" si="8"/>
-        <v>145.89145547999999</v>
+        <f t="shared" si="9"/>
+        <v>147.20026454999999</v>
       </c>
       <c r="AE9" s="2">
-        <f t="shared" si="8"/>
-        <v>151.84728266400001</v>
+        <f t="shared" si="9"/>
+        <v>153.2215321875</v>
       </c>
       <c r="AF9" s="2">
-        <f t="shared" si="8"/>
-        <v>158.07412629540002</v>
+        <f t="shared" si="9"/>
+        <v>159.24043695842101</v>
       </c>
       <c r="AG9" s="2">
-        <f t="shared" si="8"/>
-        <v>164.58500169833403</v>
+        <f t="shared" si="9"/>
+        <v>165.23419311426576</v>
       </c>
       <c r="AH9" s="2">
-        <f t="shared" si="8"/>
-        <v>171.393564253178</v>
+        <f t="shared" si="9"/>
+        <v>171.18616850443505</v>
       </c>
       <c r="AI9" s="2">
-        <f t="shared" si="8"/>
-        <v>178.51414118516274</v>
+        <f t="shared" si="9"/>
+        <v>177.38954797880191</v>
       </c>
       <c r="AJ9" s="2">
-        <f t="shared" si="8"/>
-        <v>185.9617649381332</v>
+        <f t="shared" si="9"/>
+        <v>183.85597784787001</v>
       </c>
     </row>
     <row r="10" spans="2:36" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1392,77 +1501,85 @@
         <f>J5-J9</f>
         <v>7.6000000000000014</v>
       </c>
+      <c r="K10" s="8">
+        <f>K5-K9</f>
+        <v>7.8999999999999986</v>
+      </c>
       <c r="N10" s="8">
         <f>N5-N9</f>
         <v>9.2999999999999936</v>
       </c>
+      <c r="O10" s="8">
+        <f>O5-O9</f>
+        <v>10.3</v>
+      </c>
       <c r="T10" s="8">
-        <f t="shared" ref="T10:Y10" si="9">T5-T9</f>
+        <f t="shared" ref="T10:Y10" si="10">T5-T9</f>
         <v>1.6999999999999993</v>
       </c>
       <c r="U10" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>11.399999999999999</v>
       </c>
       <c r="V10" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>11.299999999999997</v>
       </c>
       <c r="W10" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>13.5</v>
       </c>
       <c r="X10" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>29.700000000000017</v>
       </c>
       <c r="Y10" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>36.299999999999997</v>
       </c>
       <c r="Z10" s="8">
-        <f t="shared" ref="Z10:AJ10" si="10">Z5-Z9</f>
+        <f t="shared" ref="Z10:AJ10" si="11">Z5-Z9</f>
         <v>53.941999999999979</v>
       </c>
       <c r="AA10" s="8">
-        <f t="shared" si="10"/>
-        <v>63.140399999999971</v>
+        <f t="shared" si="11"/>
+        <v>65.621560000000002</v>
       </c>
       <c r="AB10" s="8">
-        <f t="shared" si="10"/>
-        <v>67.957409999999982</v>
+        <f t="shared" si="11"/>
+        <v>72.113978400000008</v>
       </c>
       <c r="AC10" s="8">
-        <f t="shared" si="10"/>
-        <v>73.262129999999985</v>
+        <f t="shared" si="11"/>
+        <v>77.727362339999985</v>
       </c>
       <c r="AD10" s="8">
-        <f t="shared" si="10"/>
-        <v>79.215033240000025</v>
+        <f t="shared" si="11"/>
+        <v>83.94168799800002</v>
       </c>
       <c r="AE10" s="8">
-        <f t="shared" si="10"/>
-        <v>84.514530492000006</v>
+        <f t="shared" si="11"/>
+        <v>89.477517987900001</v>
       </c>
       <c r="AF10" s="8">
-        <f t="shared" si="10"/>
-        <v>90.105777518399975</v>
+        <f t="shared" si="11"/>
+        <v>95.593565725749045</v>
       </c>
       <c r="AG10" s="8">
-        <f t="shared" si="10"/>
-        <v>96.003897306156006</v>
+        <f t="shared" si="11"/>
+        <v>102.34150970411284</v>
       </c>
       <c r="AH10" s="8">
-        <f t="shared" si="10"/>
-        <v>102.22477970153653</v>
+        <f t="shared" si="11"/>
+        <v>109.76831945486248</v>
       </c>
       <c r="AI10" s="8">
-        <f t="shared" si="10"/>
-        <v>108.7851199672875</v>
+        <f t="shared" si="11"/>
+        <v>117.61266437846049</v>
       </c>
       <c r="AJ10" s="8">
-        <f t="shared" si="10"/>
-        <v>115.70245927193955</v>
+        <f t="shared" si="11"/>
+        <v>125.89634512725553</v>
       </c>
     </row>
     <row r="11" spans="2:36" x14ac:dyDescent="0.3">
@@ -1472,8 +1589,14 @@
       <c r="J11" s="2">
         <v>-0.5</v>
       </c>
+      <c r="K11" s="2">
+        <v>0</v>
+      </c>
       <c r="N11" s="2">
         <v>-0.6</v>
+      </c>
+      <c r="O11" s="2">
+        <v>0</v>
       </c>
       <c r="T11" s="2">
         <v>0.3</v>
@@ -1498,43 +1621,43 @@
         <v>0.52500000000000002</v>
       </c>
       <c r="AA11" s="2">
-        <f t="shared" ref="AA11:AJ11" si="11">Z11*1.05</f>
+        <f t="shared" ref="AA11:AJ11" si="12">Z11*1.05</f>
         <v>0.55125000000000002</v>
       </c>
       <c r="AB11" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.57881250000000006</v>
       </c>
       <c r="AC11" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.60775312500000012</v>
       </c>
       <c r="AD11" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.63814078125000018</v>
       </c>
       <c r="AE11" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.67004782031250021</v>
       </c>
       <c r="AF11" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.70355021132812523</v>
       </c>
       <c r="AG11" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.73872772189453151</v>
       </c>
       <c r="AH11" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.77566410798925811</v>
       </c>
       <c r="AI11" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.81444731338872101</v>
       </c>
       <c r="AJ11" s="2">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.85516967905815711</v>
       </c>
     </row>
@@ -1545,8 +1668,14 @@
       <c r="J12" s="2">
         <v>0</v>
       </c>
+      <c r="K12" s="2">
+        <v>-0.1</v>
+      </c>
       <c r="N12" s="2">
         <v>0</v>
+      </c>
+      <c r="O12" s="2">
+        <v>0.3</v>
       </c>
       <c r="T12" s="2">
         <v>0.1</v>
@@ -1607,8 +1736,14 @@
       <c r="J13" s="2">
         <v>-0.6</v>
       </c>
+      <c r="K13" s="2">
+        <v>-0.9</v>
+      </c>
       <c r="N13" s="2">
         <v>-0.1</v>
+      </c>
+      <c r="O13" s="2">
+        <v>-3.9</v>
       </c>
       <c r="T13" s="2">
         <v>-0.1</v>
@@ -1633,43 +1768,43 @@
         <v>-1.6480000000000001</v>
       </c>
       <c r="AA13" s="2">
-        <f t="shared" ref="AA13:AJ13" si="12">Z13*1.03</f>
+        <f t="shared" ref="AA13:AJ13" si="13">Z13*1.03</f>
         <v>-1.6974400000000003</v>
       </c>
       <c r="AB13" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-1.7483632000000002</v>
       </c>
       <c r="AC13" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-1.8008140960000003</v>
       </c>
       <c r="AD13" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-1.8548385188800003</v>
       </c>
       <c r="AE13" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-1.9104836744464004</v>
       </c>
       <c r="AF13" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-1.9677981846797925</v>
       </c>
       <c r="AG13" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-2.0268321302201864</v>
       </c>
       <c r="AH13" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-2.0876370941267921</v>
       </c>
       <c r="AI13" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-2.150266206950596</v>
       </c>
       <c r="AJ13" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-2.2147741931591138</v>
       </c>
     </row>
@@ -1680,8 +1815,14 @@
       <c r="J14" s="2">
         <v>2.6</v>
       </c>
+      <c r="K14" s="2">
+        <v>0.5</v>
+      </c>
       <c r="N14" s="2">
         <v>0.9</v>
+      </c>
+      <c r="O14" s="2">
+        <v>3</v>
       </c>
       <c r="T14" s="2">
         <v>2.5</v>
@@ -1706,43 +1847,43 @@
         <v>3.1930000000000001</v>
       </c>
       <c r="AA14" s="2">
-        <f t="shared" ref="AA14:AJ14" si="13">Z14*1.03</f>
+        <f t="shared" ref="AA14:AJ14" si="14">Z14*1.03</f>
         <v>3.2887900000000001</v>
       </c>
       <c r="AB14" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.3874537</v>
       </c>
       <c r="AC14" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.489077311</v>
       </c>
       <c r="AD14" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.5937496303300001</v>
       </c>
       <c r="AE14" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.7015621192399002</v>
       </c>
       <c r="AF14" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.8126089828170975</v>
       </c>
       <c r="AG14" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.9269872523016107</v>
       </c>
       <c r="AH14" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.0447968698706589</v>
       </c>
       <c r="AI14" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.1661407759667783</v>
       </c>
       <c r="AJ14" s="2">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.2911249992457821</v>
       </c>
     </row>
@@ -1754,76 +1895,84 @@
         <f>SUM(J11:J14)</f>
         <v>1.5</v>
       </c>
+      <c r="K15" s="2">
+        <f>SUM(K11:K14)</f>
+        <v>-0.5</v>
+      </c>
       <c r="N15" s="2">
         <f>SUM(N11:N14)</f>
         <v>0.20000000000000007</v>
       </c>
+      <c r="O15" s="2">
+        <f>SUM(O11:O14)</f>
+        <v>-0.60000000000000009</v>
+      </c>
       <c r="T15" s="2">
-        <f t="shared" ref="T15:Y15" si="14">SUM(T11:T14)</f>
+        <f t="shared" ref="T15:Y15" si="15">SUM(T11:T14)</f>
         <v>2.8</v>
       </c>
       <c r="U15" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.70000000000000018</v>
       </c>
       <c r="V15" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>-0.90000000000000013</v>
       </c>
       <c r="W15" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>10.700000000000003</v>
       </c>
       <c r="X15" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>9.5</v>
       </c>
       <c r="Y15" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
       <c r="Z15" s="2">
-        <f t="shared" ref="Z15:AJ15" si="15">SUM(Z11:Z14)</f>
+        <f t="shared" ref="Z15:AJ15" si="16">SUM(Z11:Z14)</f>
         <v>2.0699999999999998</v>
       </c>
       <c r="AA15" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.1425999999999998</v>
       </c>
       <c r="AB15" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.2179029999999997</v>
       </c>
       <c r="AC15" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.2960163399999995</v>
       </c>
       <c r="AD15" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.3770518926999999</v>
       </c>
       <c r="AE15" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.461126265106</v>
       </c>
       <c r="AF15" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.5483610094654301</v>
       </c>
       <c r="AG15" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.638882843975956</v>
       </c>
       <c r="AH15" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.7328238837331247</v>
       </c>
       <c r="AI15" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.8303218824049035</v>
       </c>
       <c r="AJ15" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>2.9315204851448255</v>
       </c>
     </row>
@@ -1835,77 +1984,85 @@
         <f>J10-J15</f>
         <v>6.1000000000000014</v>
       </c>
+      <c r="K16" s="8">
+        <f>K10-K15</f>
+        <v>8.3999999999999986</v>
+      </c>
       <c r="N16" s="8">
         <f>N10-N15</f>
         <v>9.0999999999999943</v>
       </c>
+      <c r="O16" s="8">
+        <f>O10-O15</f>
+        <v>10.9</v>
+      </c>
       <c r="T16" s="8">
-        <f t="shared" ref="T16:Y16" si="16">T10-T15</f>
+        <f t="shared" ref="T16:Y16" si="17">T10-T15</f>
         <v>-1.1000000000000005</v>
       </c>
       <c r="U16" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>10.7</v>
       </c>
       <c r="V16" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>12.199999999999998</v>
       </c>
       <c r="W16" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>2.7999999999999972</v>
       </c>
       <c r="X16" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>20.200000000000017</v>
       </c>
       <c r="Y16" s="8">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>34.299999999999997</v>
       </c>
       <c r="Z16" s="8">
-        <f t="shared" ref="Z16:AJ16" si="17">Z10-Z15</f>
+        <f t="shared" ref="Z16:AJ16" si="18">Z10-Z15</f>
         <v>51.871999999999979</v>
       </c>
       <c r="AA16" s="8">
-        <f t="shared" si="17"/>
-        <v>60.99779999999997</v>
+        <f t="shared" si="18"/>
+        <v>63.478960000000001</v>
       </c>
       <c r="AB16" s="8">
-        <f t="shared" si="17"/>
-        <v>65.739506999999975</v>
+        <f t="shared" si="18"/>
+        <v>69.896075400000001</v>
       </c>
       <c r="AC16" s="8">
-        <f t="shared" si="17"/>
-        <v>70.966113659999991</v>
+        <f t="shared" si="18"/>
+        <v>75.431345999999991</v>
       </c>
       <c r="AD16" s="8">
-        <f t="shared" si="17"/>
-        <v>76.83798134730003</v>
+        <f t="shared" si="18"/>
+        <v>81.564636105300025</v>
       </c>
       <c r="AE16" s="8">
-        <f t="shared" si="17"/>
-        <v>82.053404226894003</v>
+        <f t="shared" si="18"/>
+        <v>87.016391722793998</v>
       </c>
       <c r="AF16" s="8">
-        <f t="shared" si="17"/>
-        <v>87.557416508934551</v>
+        <f t="shared" si="18"/>
+        <v>93.045204716283621</v>
       </c>
       <c r="AG16" s="8">
-        <f t="shared" si="17"/>
-        <v>93.365014462180056</v>
+        <f t="shared" si="18"/>
+        <v>99.702626860136888</v>
       </c>
       <c r="AH16" s="8">
-        <f t="shared" si="17"/>
-        <v>99.491955817803415</v>
+        <f t="shared" si="18"/>
+        <v>107.03549557112936</v>
       </c>
       <c r="AI16" s="8">
-        <f t="shared" si="17"/>
-        <v>105.9547980848826</v>
+        <f t="shared" si="18"/>
+        <v>114.78234249605559</v>
       </c>
       <c r="AJ16" s="8">
-        <f t="shared" si="17"/>
-        <v>112.77093878679472</v>
+        <f t="shared" si="18"/>
+        <v>122.9648246421107</v>
       </c>
     </row>
     <row r="17" spans="2:142" x14ac:dyDescent="0.3">
@@ -1915,8 +2072,14 @@
       <c r="J17" s="2">
         <v>-0.2</v>
       </c>
+      <c r="K17" s="2">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="N17" s="2">
         <v>1.1000000000000001</v>
+      </c>
+      <c r="O17" s="2">
+        <v>-0.3</v>
       </c>
       <c r="T17" s="2">
         <v>0.9</v>
@@ -1941,44 +2104,44 @@
         <v>7.7807999999999966</v>
       </c>
       <c r="AA17" s="2">
-        <f t="shared" ref="AA17:AJ17" si="18">AA16*0.15</f>
-        <v>9.1496699999999951</v>
+        <f t="shared" ref="AA17:AJ17" si="19">AA16*0.15</f>
+        <v>9.5218439999999998</v>
       </c>
       <c r="AB17" s="2">
-        <f t="shared" si="18"/>
-        <v>9.8609260499999962</v>
+        <f t="shared" si="19"/>
+        <v>10.48441131</v>
       </c>
       <c r="AC17" s="2">
-        <f t="shared" si="18"/>
-        <v>10.644917048999998</v>
+        <f t="shared" si="19"/>
+        <v>11.314701899999998</v>
       </c>
       <c r="AD17" s="2">
-        <f t="shared" si="18"/>
-        <v>11.525697202095005</v>
+        <f t="shared" si="19"/>
+        <v>12.234695415795004</v>
       </c>
       <c r="AE17" s="2">
-        <f t="shared" si="18"/>
-        <v>12.308010634034099</v>
+        <f t="shared" si="19"/>
+        <v>13.0524587584191</v>
       </c>
       <c r="AF17" s="2">
-        <f t="shared" si="18"/>
-        <v>13.133612476340183</v>
+        <f t="shared" si="19"/>
+        <v>13.956780707442542</v>
       </c>
       <c r="AG17" s="2">
-        <f t="shared" si="18"/>
-        <v>14.004752169327007</v>
+        <f t="shared" si="19"/>
+        <v>14.955394029020532</v>
       </c>
       <c r="AH17" s="2">
-        <f t="shared" si="18"/>
-        <v>14.923793372670511</v>
+        <f t="shared" si="19"/>
+        <v>16.055324335669404</v>
       </c>
       <c r="AI17" s="2">
-        <f t="shared" si="18"/>
-        <v>15.893219712732389</v>
+        <f t="shared" si="19"/>
+        <v>17.217351374408338</v>
       </c>
       <c r="AJ17" s="2">
-        <f t="shared" si="18"/>
-        <v>16.915640818019206</v>
+        <f t="shared" si="19"/>
+        <v>18.444723696316604</v>
       </c>
     </row>
     <row r="18" spans="2:142" s="7" customFormat="1" x14ac:dyDescent="0.3">
@@ -1989,501 +2152,509 @@
         <f>J16-J17</f>
         <v>6.3000000000000016</v>
       </c>
+      <c r="K18" s="8">
+        <f>K16-K17</f>
+        <v>7.2999999999999989</v>
+      </c>
       <c r="N18" s="8">
         <f>N16-N17</f>
         <v>7.9999999999999947</v>
       </c>
+      <c r="O18" s="8">
+        <f>O16-O17</f>
+        <v>11.200000000000001</v>
+      </c>
       <c r="T18" s="8">
-        <f t="shared" ref="T18:Y18" si="19">T16-T17</f>
+        <f t="shared" ref="T18:Y18" si="20">T16-T17</f>
         <v>-2.0000000000000004</v>
       </c>
       <c r="U18" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>15</v>
       </c>
       <c r="V18" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>12.499999999999998</v>
       </c>
       <c r="W18" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2.2999999999999972</v>
       </c>
       <c r="X18" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>18.300000000000018</v>
       </c>
       <c r="Y18" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>30.799999999999997</v>
       </c>
       <c r="Z18" s="8">
-        <f t="shared" ref="Z18" si="20">Z16-Z17</f>
+        <f t="shared" ref="Z18" si="21">Z16-Z17</f>
         <v>44.091199999999979</v>
       </c>
       <c r="AA18" s="8">
-        <f t="shared" ref="AA18" si="21">AA16-AA17</f>
-        <v>51.848129999999976</v>
+        <f t="shared" ref="AA18" si="22">AA16-AA17</f>
+        <v>53.957115999999999</v>
       </c>
       <c r="AB18" s="8">
-        <f t="shared" ref="AB18" si="22">AB16-AB17</f>
-        <v>55.878580949999979</v>
+        <f t="shared" ref="AB18" si="23">AB16-AB17</f>
+        <v>59.411664090000002</v>
       </c>
       <c r="AC18" s="8">
-        <f t="shared" ref="AC18" si="23">AC16-AC17</f>
-        <v>60.321196610999991</v>
+        <f t="shared" ref="AC18" si="24">AC16-AC17</f>
+        <v>64.116644099999988</v>
       </c>
       <c r="AD18" s="8">
-        <f t="shared" ref="AD18" si="24">AD16-AD17</f>
-        <v>65.312284145205027</v>
+        <f t="shared" ref="AD18" si="25">AD16-AD17</f>
+        <v>69.329940689505023</v>
       </c>
       <c r="AE18" s="8">
-        <f t="shared" ref="AE18" si="25">AE16-AE17</f>
-        <v>69.745393592859898</v>
+        <f t="shared" ref="AE18" si="26">AE16-AE17</f>
+        <v>73.963932964374891</v>
       </c>
       <c r="AF18" s="8">
-        <f t="shared" ref="AF18" si="26">AF16-AF17</f>
-        <v>74.423804032594376</v>
+        <f t="shared" ref="AF18" si="27">AF16-AF17</f>
+        <v>79.088424008841073</v>
       </c>
       <c r="AG18" s="8">
-        <f t="shared" ref="AG18" si="27">AG16-AG17</f>
-        <v>79.360262292853051</v>
+        <f t="shared" ref="AG18" si="28">AG16-AG17</f>
+        <v>84.747232831116349</v>
       </c>
       <c r="AH18" s="8">
-        <f t="shared" ref="AH18" si="28">AH16-AH17</f>
-        <v>84.568162445132899</v>
+        <f t="shared" ref="AH18" si="29">AH16-AH17</f>
+        <v>90.980171235459949</v>
       </c>
       <c r="AI18" s="8">
-        <f t="shared" ref="AI18" si="29">AI16-AI17</f>
-        <v>90.061578372150208</v>
+        <f t="shared" ref="AI18" si="30">AI16-AI17</f>
+        <v>97.564991121647253</v>
       </c>
       <c r="AJ18" s="8">
-        <f t="shared" ref="AJ18" si="30">AJ16-AJ17</f>
-        <v>95.855297968775517</v>
+        <f t="shared" ref="AJ18" si="31">AJ16-AJ17</f>
+        <v>104.5201009457941</v>
       </c>
       <c r="AK18" s="7">
         <f>AJ18*(1+$AM$24)</f>
-        <v>94.896744989087765</v>
+        <v>103.47489993633616</v>
       </c>
       <c r="AL18" s="7">
-        <f t="shared" ref="AL18:CW18" si="31">AK18*(1+$AM$24)</f>
-        <v>93.947777539196892</v>
+        <f t="shared" ref="AL18:CW18" si="32">AK18*(1+$AM$24)</f>
+        <v>102.4401509369728</v>
       </c>
       <c r="AM18" s="7">
-        <f t="shared" si="31"/>
-        <v>93.008299763804928</v>
+        <f t="shared" si="32"/>
+        <v>101.41574942760307</v>
       </c>
       <c r="AN18" s="7">
-        <f t="shared" si="31"/>
-        <v>92.078216766166875</v>
+        <f t="shared" si="32"/>
+        <v>100.40159193332704</v>
       </c>
       <c r="AO18" s="7">
-        <f t="shared" si="31"/>
-        <v>91.157434598505205</v>
+        <f t="shared" si="32"/>
+        <v>99.397576013993771</v>
       </c>
       <c r="AP18" s="7">
-        <f t="shared" si="31"/>
-        <v>90.245860252520146</v>
+        <f t="shared" si="32"/>
+        <v>98.403600253853838</v>
       </c>
       <c r="AQ18" s="7">
-        <f t="shared" si="31"/>
-        <v>89.343401649994945</v>
+        <f t="shared" si="32"/>
+        <v>97.419564251315293</v>
       </c>
       <c r="AR18" s="7">
-        <f t="shared" si="31"/>
-        <v>88.449967633494992</v>
+        <f t="shared" si="32"/>
+        <v>96.445368608802141</v>
       </c>
       <c r="AS18" s="7">
-        <f t="shared" si="31"/>
-        <v>87.565467957160038</v>
+        <f t="shared" si="32"/>
+        <v>95.480914922714121</v>
       </c>
       <c r="AT18" s="7">
-        <f t="shared" si="31"/>
-        <v>86.689813277588442</v>
+        <f t="shared" si="32"/>
+        <v>94.526105773486975</v>
       </c>
       <c r="AU18" s="7">
-        <f t="shared" si="31"/>
-        <v>85.822915144812555</v>
+        <f t="shared" si="32"/>
+        <v>93.580844715752107</v>
       </c>
       <c r="AV18" s="7">
-        <f t="shared" si="31"/>
-        <v>84.964685993364427</v>
+        <f t="shared" si="32"/>
+        <v>92.645036268594581</v>
       </c>
       <c r="AW18" s="7">
-        <f t="shared" si="31"/>
-        <v>84.115039133430784</v>
+        <f t="shared" si="32"/>
+        <v>91.71858590590864</v>
       </c>
       <c r="AX18" s="7">
-        <f t="shared" si="31"/>
-        <v>83.273888742096474</v>
+        <f t="shared" si="32"/>
+        <v>90.801400046849551</v>
       </c>
       <c r="AY18" s="7">
-        <f t="shared" si="31"/>
-        <v>82.441149854675515</v>
+        <f t="shared" si="32"/>
+        <v>89.893386046381053</v>
       </c>
       <c r="AZ18" s="7">
-        <f t="shared" si="31"/>
-        <v>81.616738356128764</v>
+        <f t="shared" si="32"/>
+        <v>88.99445218591724</v>
       </c>
       <c r="BA18" s="7">
-        <f t="shared" si="31"/>
-        <v>80.800570972567471</v>
+        <f t="shared" si="32"/>
+        <v>88.104507664058062</v>
       </c>
       <c r="BB18" s="7">
-        <f t="shared" si="31"/>
-        <v>79.992565262841794</v>
+        <f t="shared" si="32"/>
+        <v>87.223462587417487</v>
       </c>
       <c r="BC18" s="7">
-        <f t="shared" si="31"/>
-        <v>79.192639610213376</v>
+        <f t="shared" si="32"/>
+        <v>86.351227961543316</v>
       </c>
       <c r="BD18" s="7">
-        <f t="shared" si="31"/>
-        <v>78.400713214111235</v>
+        <f t="shared" si="32"/>
+        <v>85.487715681927881</v>
       </c>
       <c r="BE18" s="7">
-        <f t="shared" si="31"/>
-        <v>77.616706081970122</v>
+        <f t="shared" si="32"/>
+        <v>84.632838525108596</v>
       </c>
       <c r="BF18" s="7">
-        <f t="shared" si="31"/>
-        <v>76.84053902115042</v>
+        <f t="shared" si="32"/>
+        <v>83.786510139857512</v>
       </c>
       <c r="BG18" s="7">
-        <f t="shared" si="31"/>
-        <v>76.072133630938922</v>
+        <f t="shared" si="32"/>
+        <v>82.948645038458935</v>
       </c>
       <c r="BH18" s="7">
-        <f t="shared" si="31"/>
-        <v>75.311412294629534</v>
+        <f t="shared" si="32"/>
+        <v>82.119158588074342</v>
       </c>
       <c r="BI18" s="7">
-        <f t="shared" si="31"/>
-        <v>74.558298171683234</v>
+        <f t="shared" si="32"/>
+        <v>81.297967002193602</v>
       </c>
       <c r="BJ18" s="7">
-        <f t="shared" si="31"/>
-        <v>73.812715189966397</v>
+        <f t="shared" si="32"/>
+        <v>80.48498733217167</v>
       </c>
       <c r="BK18" s="7">
-        <f t="shared" si="31"/>
-        <v>73.074588038066736</v>
+        <f t="shared" si="32"/>
+        <v>79.680137458849956</v>
       </c>
       <c r="BL18" s="7">
-        <f t="shared" si="31"/>
-        <v>72.343842157686069</v>
+        <f t="shared" si="32"/>
+        <v>78.883336084261458</v>
       </c>
       <c r="BM18" s="7">
-        <f t="shared" si="31"/>
-        <v>71.620403736109211</v>
+        <f t="shared" si="32"/>
+        <v>78.094502723418842</v>
       </c>
       <c r="BN18" s="7">
-        <f t="shared" si="31"/>
-        <v>70.904199698748116</v>
+        <f t="shared" si="32"/>
+        <v>77.31355769618466</v>
       </c>
       <c r="BO18" s="7">
-        <f t="shared" si="31"/>
-        <v>70.195157701760635</v>
+        <f t="shared" si="32"/>
+        <v>76.540422119222811</v>
       </c>
       <c r="BP18" s="7">
-        <f t="shared" si="31"/>
-        <v>69.493206124743025</v>
+        <f t="shared" si="32"/>
+        <v>75.775017898030583</v>
       </c>
       <c r="BQ18" s="7">
-        <f t="shared" si="31"/>
-        <v>68.798274063495597</v>
+        <f t="shared" si="32"/>
+        <v>75.017267719050281</v>
       </c>
       <c r="BR18" s="7">
-        <f t="shared" si="31"/>
-        <v>68.110291322860647</v>
+        <f t="shared" si="32"/>
+        <v>74.267095041859776</v>
       </c>
       <c r="BS18" s="7">
-        <f t="shared" si="31"/>
-        <v>67.429188409632033</v>
+        <f t="shared" si="32"/>
+        <v>73.524424091441176</v>
       </c>
       <c r="BT18" s="7">
-        <f t="shared" si="31"/>
-        <v>66.754896525535713</v>
+        <f t="shared" si="32"/>
+        <v>72.789179850526764</v>
       </c>
       <c r="BU18" s="7">
-        <f t="shared" si="31"/>
-        <v>66.08734756028035</v>
+        <f t="shared" si="32"/>
+        <v>72.061288052021496</v>
       </c>
       <c r="BV18" s="7">
-        <f t="shared" si="31"/>
-        <v>65.426474084677551</v>
+        <f t="shared" si="32"/>
+        <v>71.340675171501275</v>
       </c>
       <c r="BW18" s="7">
-        <f t="shared" si="31"/>
-        <v>64.772209343830781</v>
+        <f t="shared" si="32"/>
+        <v>70.627268419786262</v>
       </c>
       <c r="BX18" s="7">
-        <f t="shared" si="31"/>
-        <v>64.124487250392477</v>
+        <f t="shared" si="32"/>
+        <v>69.920995735588392</v>
       </c>
       <c r="BY18" s="7">
-        <f t="shared" si="31"/>
-        <v>63.483242377888551</v>
+        <f t="shared" si="32"/>
+        <v>69.221785778232501</v>
       </c>
       <c r="BZ18" s="7">
-        <f t="shared" si="31"/>
-        <v>62.848409954109663</v>
+        <f t="shared" si="32"/>
+        <v>68.529567920450177</v>
       </c>
       <c r="CA18" s="7">
-        <f t="shared" si="31"/>
-        <v>62.219925854568565</v>
+        <f t="shared" si="32"/>
+        <v>67.844272241245676</v>
       </c>
       <c r="CB18" s="7">
-        <f t="shared" si="31"/>
-        <v>61.597726596022881</v>
+        <f t="shared" si="32"/>
+        <v>67.16582951883322</v>
       </c>
       <c r="CC18" s="7">
-        <f t="shared" si="31"/>
-        <v>60.981749330062648</v>
+        <f t="shared" si="32"/>
+        <v>66.494171223644884</v>
       </c>
       <c r="CD18" s="7">
-        <f t="shared" si="31"/>
-        <v>60.371931836762023</v>
+        <f t="shared" si="32"/>
+        <v>65.829229511408428</v>
       </c>
       <c r="CE18" s="7">
-        <f t="shared" si="31"/>
-        <v>59.7682125183944</v>
+        <f t="shared" si="32"/>
+        <v>65.170937216294348</v>
       </c>
       <c r="CF18" s="7">
-        <f t="shared" si="31"/>
-        <v>59.170530393210456</v>
+        <f t="shared" si="32"/>
+        <v>64.519227844131407</v>
       </c>
       <c r="CG18" s="7">
-        <f t="shared" si="31"/>
-        <v>58.578825089278354</v>
+        <f t="shared" si="32"/>
+        <v>63.874035565690093</v>
       </c>
       <c r="CH18" s="7">
-        <f t="shared" si="31"/>
-        <v>57.993036838385571</v>
+        <f t="shared" si="32"/>
+        <v>63.235295210033193</v>
       </c>
       <c r="CI18" s="7">
-        <f t="shared" si="31"/>
-        <v>57.413106470001715</v>
+        <f t="shared" si="32"/>
+        <v>62.60294225793286</v>
       </c>
       <c r="CJ18" s="7">
-        <f t="shared" si="31"/>
-        <v>56.838975405301696</v>
+        <f t="shared" si="32"/>
+        <v>61.976912835353531</v>
       </c>
       <c r="CK18" s="7">
-        <f t="shared" si="31"/>
-        <v>56.27058565124868</v>
+        <f t="shared" si="32"/>
+        <v>61.357143706999992</v>
       </c>
       <c r="CL18" s="7">
-        <f t="shared" si="31"/>
-        <v>55.707879794736193</v>
+        <f t="shared" si="32"/>
+        <v>60.743572269929992</v>
       </c>
       <c r="CM18" s="7">
-        <f t="shared" si="31"/>
-        <v>55.150800996788831</v>
+        <f t="shared" si="32"/>
+        <v>60.136136547230691</v>
       </c>
       <c r="CN18" s="7">
-        <f t="shared" si="31"/>
-        <v>54.599292986820942</v>
+        <f t="shared" si="32"/>
+        <v>59.534775181758384</v>
       </c>
       <c r="CO18" s="7">
-        <f t="shared" si="31"/>
-        <v>54.053300056952729</v>
+        <f t="shared" si="32"/>
+        <v>58.9394274299408</v>
       </c>
       <c r="CP18" s="7">
-        <f t="shared" si="31"/>
-        <v>53.512767056383204</v>
+        <f t="shared" si="32"/>
+        <v>58.350033155641391</v>
       </c>
       <c r="CQ18" s="7">
-        <f t="shared" si="31"/>
-        <v>52.977639385819373</v>
+        <f t="shared" si="32"/>
+        <v>57.766532824084976</v>
       </c>
       <c r="CR18" s="7">
-        <f t="shared" si="31"/>
-        <v>52.447862991961181</v>
+        <f t="shared" si="32"/>
+        <v>57.188867495844129</v>
       </c>
       <c r="CS18" s="7">
-        <f t="shared" si="31"/>
-        <v>51.923384362041567</v>
+        <f t="shared" si="32"/>
+        <v>56.616978820885684</v>
       </c>
       <c r="CT18" s="7">
-        <f t="shared" si="31"/>
-        <v>51.404150518421147</v>
+        <f t="shared" si="32"/>
+        <v>56.050809032676824</v>
       </c>
       <c r="CU18" s="7">
-        <f t="shared" si="31"/>
-        <v>50.890109013236938</v>
+        <f t="shared" si="32"/>
+        <v>55.490300942350054</v>
       </c>
       <c r="CV18" s="7">
-        <f t="shared" si="31"/>
-        <v>50.381207923104569</v>
+        <f t="shared" si="32"/>
+        <v>54.935397932926556</v>
       </c>
       <c r="CW18" s="7">
-        <f t="shared" si="31"/>
-        <v>49.877395843873522</v>
+        <f t="shared" si="32"/>
+        <v>54.386043953597287</v>
       </c>
       <c r="CX18" s="7">
-        <f t="shared" ref="CX18:EL18" si="32">CW18*(1+$AM$24)</f>
-        <v>49.378621885434789</v>
+        <f t="shared" ref="CX18:EL18" si="33">CW18*(1+$AM$24)</f>
+        <v>53.842183514061311</v>
       </c>
       <c r="CY18" s="7">
-        <f t="shared" si="32"/>
-        <v>48.884835666580443</v>
+        <f t="shared" si="33"/>
+        <v>53.303761678920701</v>
       </c>
       <c r="CZ18" s="7">
-        <f t="shared" si="32"/>
-        <v>48.395987309914638</v>
+        <f t="shared" si="33"/>
+        <v>52.770724062131492</v>
       </c>
       <c r="DA18" s="7">
-        <f t="shared" si="32"/>
-        <v>47.912027436815492</v>
+        <f t="shared" si="33"/>
+        <v>52.243016821510174</v>
       </c>
       <c r="DB18" s="7">
-        <f t="shared" si="32"/>
-        <v>47.432907162447336</v>
+        <f t="shared" si="33"/>
+        <v>51.720586653295072</v>
       </c>
       <c r="DC18" s="7">
-        <f t="shared" si="32"/>
-        <v>46.958578090822861</v>
+        <f t="shared" si="33"/>
+        <v>51.203380786762118</v>
       </c>
       <c r="DD18" s="7">
-        <f t="shared" si="32"/>
-        <v>46.488992309914636</v>
+        <f t="shared" si="33"/>
+        <v>50.691346978894494</v>
       </c>
       <c r="DE18" s="7">
-        <f t="shared" si="32"/>
-        <v>46.024102386815493</v>
+        <f t="shared" si="33"/>
+        <v>50.184433509105546</v>
       </c>
       <c r="DF18" s="7">
-        <f t="shared" si="32"/>
-        <v>45.563861362947335</v>
+        <f t="shared" si="33"/>
+        <v>49.682589174014488</v>
       </c>
       <c r="DG18" s="7">
-        <f t="shared" si="32"/>
-        <v>45.108222749317861</v>
+        <f t="shared" si="33"/>
+        <v>49.185763282274344</v>
       </c>
       <c r="DH18" s="7">
-        <f t="shared" si="32"/>
-        <v>44.65714052182468</v>
+        <f t="shared" si="33"/>
+        <v>48.693905649451601</v>
       </c>
       <c r="DI18" s="7">
-        <f t="shared" si="32"/>
-        <v>44.210569116606429</v>
+        <f t="shared" si="33"/>
+        <v>48.206966592957087</v>
       </c>
       <c r="DJ18" s="7">
-        <f t="shared" si="32"/>
-        <v>43.768463425440366</v>
+        <f t="shared" si="33"/>
+        <v>47.724896927027515</v>
       </c>
       <c r="DK18" s="7">
-        <f t="shared" si="32"/>
-        <v>43.330778791185963</v>
+        <f t="shared" si="33"/>
+        <v>47.247647957757238</v>
       </c>
       <c r="DL18" s="7">
-        <f t="shared" si="32"/>
-        <v>42.897471003274106</v>
+        <f t="shared" si="33"/>
+        <v>46.775171478179665</v>
       </c>
       <c r="DM18" s="7">
-        <f t="shared" si="32"/>
-        <v>42.468496293241365</v>
+        <f t="shared" si="33"/>
+        <v>46.307419763397867</v>
       </c>
       <c r="DN18" s="7">
-        <f t="shared" si="32"/>
-        <v>42.043811330308948</v>
+        <f t="shared" si="33"/>
+        <v>45.844345565763888</v>
       </c>
       <c r="DO18" s="7">
-        <f t="shared" si="32"/>
-        <v>41.623373217005856</v>
+        <f t="shared" si="33"/>
+        <v>45.385902110106251</v>
       </c>
       <c r="DP18" s="7">
-        <f t="shared" si="32"/>
-        <v>41.2071394848358</v>
+        <f t="shared" si="33"/>
+        <v>44.932043089005191</v>
       </c>
       <c r="DQ18" s="7">
-        <f t="shared" si="32"/>
-        <v>40.795068089987438</v>
+        <f t="shared" si="33"/>
+        <v>44.482722658115136</v>
       </c>
       <c r="DR18" s="7">
-        <f t="shared" si="32"/>
-        <v>40.387117409087566</v>
+        <f t="shared" si="33"/>
+        <v>44.037895431533983</v>
       </c>
       <c r="DS18" s="7">
-        <f t="shared" si="32"/>
-        <v>39.983246234996692</v>
+        <f t="shared" si="33"/>
+        <v>43.59751647721864</v>
       </c>
       <c r="DT18" s="7">
-        <f t="shared" si="32"/>
-        <v>39.583413772646722</v>
+        <f t="shared" si="33"/>
+        <v>43.161541312446452</v>
       </c>
       <c r="DU18" s="7">
-        <f t="shared" si="32"/>
-        <v>39.187579634920255</v>
+        <f t="shared" si="33"/>
+        <v>42.729925899321991</v>
       </c>
       <c r="DV18" s="7">
-        <f t="shared" si="32"/>
-        <v>38.79570383857105</v>
+        <f t="shared" si="33"/>
+        <v>42.302626640328768</v>
       </c>
       <c r="DW18" s="7">
-        <f t="shared" si="32"/>
-        <v>38.407746800185336</v>
+        <f t="shared" si="33"/>
+        <v>41.879600373925477</v>
       </c>
       <c r="DX18" s="7">
-        <f t="shared" si="32"/>
-        <v>38.023669332183481</v>
+        <f t="shared" si="33"/>
+        <v>41.460804370186224</v>
       </c>
       <c r="DY18" s="7">
-        <f t="shared" si="32"/>
-        <v>37.643432638861647</v>
+        <f t="shared" si="33"/>
+        <v>41.046196326484363</v>
       </c>
       <c r="DZ18" s="7">
-        <f t="shared" si="32"/>
-        <v>37.266998312473028</v>
+        <f t="shared" si="33"/>
+        <v>40.63573436321952</v>
       </c>
       <c r="EA18" s="7">
-        <f t="shared" si="32"/>
-        <v>36.894328329348298</v>
+        <f t="shared" si="33"/>
+        <v>40.229377019587325</v>
       </c>
       <c r="EB18" s="7">
-        <f t="shared" si="32"/>
-        <v>36.525385046054815</v>
+        <f t="shared" si="33"/>
+        <v>39.82708324939145</v>
       </c>
       <c r="EC18" s="7">
-        <f t="shared" si="32"/>
-        <v>36.160131195594268</v>
+        <f t="shared" si="33"/>
+        <v>39.428812416897536</v>
       </c>
       <c r="ED18" s="7">
-        <f t="shared" si="32"/>
-        <v>35.798529883638324</v>
+        <f t="shared" si="33"/>
+        <v>39.034524292728563</v>
       </c>
       <c r="EE18" s="7">
-        <f t="shared" si="32"/>
-        <v>35.440544584801941</v>
+        <f t="shared" si="33"/>
+        <v>38.644179049801274</v>
       </c>
       <c r="EF18" s="7">
-        <f t="shared" si="32"/>
-        <v>35.086139138953918</v>
+        <f t="shared" si="33"/>
+        <v>38.257737259303262</v>
       </c>
       <c r="EG18" s="7">
-        <f t="shared" si="32"/>
-        <v>34.735277747564382</v>
+        <f t="shared" si="33"/>
+        <v>37.875159886710229</v>
       </c>
       <c r="EH18" s="7">
-        <f t="shared" si="32"/>
-        <v>34.38792497008874</v>
+        <f t="shared" si="33"/>
+        <v>37.496408287843124</v>
       </c>
       <c r="EI18" s="7">
-        <f t="shared" si="32"/>
-        <v>34.044045720387849</v>
+        <f t="shared" si="33"/>
+        <v>37.121444204964689</v>
       </c>
       <c r="EJ18" s="7">
-        <f t="shared" si="32"/>
-        <v>33.703605263183974</v>
+        <f t="shared" si="33"/>
+        <v>36.750229762915041</v>
       </c>
       <c r="EK18" s="7">
-        <f t="shared" si="32"/>
-        <v>33.366569210552136</v>
+        <f t="shared" si="33"/>
+        <v>36.382727465285889</v>
       </c>
       <c r="EL18" s="7">
-        <f t="shared" si="32"/>
-        <v>33.032903518446616</v>
+        <f t="shared" si="33"/>
+        <v>36.018900190633033</v>
       </c>
     </row>
     <row r="19" spans="2:142" x14ac:dyDescent="0.3">
@@ -2493,8 +2664,15 @@
       <c r="J19" s="2">
         <v>34.799999999999997</v>
       </c>
+      <c r="K19" s="2">
+        <v>34.799999999999997</v>
+      </c>
       <c r="N19" s="2">
         <v>34.799999999999997</v>
+      </c>
+      <c r="O19" s="2">
+        <f>35.6</f>
+        <v>35.6</v>
       </c>
       <c r="T19" s="2">
         <v>34.799999999999997</v>
@@ -2556,77 +2734,85 @@
         <f>J18/J19</f>
         <v>0.18103448275862075</v>
       </c>
+      <c r="K20" s="6">
+        <f>K18/K19</f>
+        <v>0.20977011494252873</v>
+      </c>
       <c r="N20" s="6">
         <f>N18/N19</f>
         <v>0.22988505747126423</v>
       </c>
+      <c r="O20" s="6">
+        <f>O18/O19</f>
+        <v>0.3146067415730337</v>
+      </c>
       <c r="T20" s="6">
-        <f t="shared" ref="T20:Y20" si="33">T18/T19</f>
+        <f t="shared" ref="T20:Y20" si="34">T18/T19</f>
         <v>-5.7471264367816112E-2</v>
       </c>
       <c r="U20" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.43103448275862072</v>
       </c>
       <c r="V20" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.35919540229885055</v>
       </c>
       <c r="W20" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>6.6091954022988425E-2</v>
       </c>
       <c r="X20" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.52586206896551779</v>
       </c>
       <c r="Y20" s="6">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>0.88505747126436785</v>
       </c>
       <c r="Z20" s="6">
-        <f t="shared" ref="Z20" si="34">Z18/Z19</f>
+        <f t="shared" ref="Z20" si="35">Z18/Z19</f>
         <v>1.266988505747126</v>
       </c>
       <c r="AA20" s="6">
-        <f t="shared" ref="AA20" si="35">AA18/AA19</f>
-        <v>1.4898887931034477</v>
+        <f t="shared" ref="AA20" si="36">AA18/AA19</f>
+        <v>1.5504918390804598</v>
       </c>
       <c r="AB20" s="6">
-        <f t="shared" ref="AB20" si="36">AB18/AB19</f>
-        <v>1.6057063491379306</v>
+        <f t="shared" ref="AB20" si="37">AB18/AB19</f>
+        <v>1.7072317267241381</v>
       </c>
       <c r="AC20" s="6">
-        <f t="shared" ref="AC20" si="37">AC18/AC19</f>
-        <v>1.7333677187068963</v>
+        <f t="shared" ref="AC20" si="38">AC18/AC19</f>
+        <v>1.8424323017241377</v>
       </c>
       <c r="AD20" s="6">
-        <f t="shared" ref="AD20" si="38">AD18/AD19</f>
-        <v>1.8767897742875008</v>
+        <f t="shared" ref="AD20" si="39">AD18/AD19</f>
+        <v>1.9922396749857767</v>
       </c>
       <c r="AE20" s="6">
-        <f t="shared" ref="AE20" si="39">AE18/AE19</f>
-        <v>2.0041779768063193</v>
+        <f t="shared" ref="AE20" si="40">AE18/AE19</f>
+        <v>2.1254003725395085</v>
       </c>
       <c r="AF20" s="6">
-        <f t="shared" ref="AF20" si="40">AF18/AF19</f>
-        <v>2.1386150584078845</v>
+        <f t="shared" ref="AF20" si="41">AF18/AF19</f>
+        <v>2.2726558623230195</v>
       </c>
       <c r="AG20" s="6">
-        <f t="shared" ref="AG20" si="41">AG18/AG19</f>
-        <v>2.2804673072658925</v>
+        <f t="shared" ref="AG20" si="42">AG18/AG19</f>
+        <v>2.4352653112389757</v>
       </c>
       <c r="AH20" s="6">
-        <f t="shared" ref="AH20" si="42">AH18/AH19</f>
-        <v>2.4301196104923251</v>
+        <f t="shared" ref="AH20" si="43">AH18/AH19</f>
+        <v>2.614372736651148</v>
       </c>
       <c r="AI20" s="6">
-        <f t="shared" ref="AI20" si="43">AI18/AI19</f>
-        <v>2.5879763900043167</v>
+        <f t="shared" ref="AI20" si="44">AI18/AI19</f>
+        <v>2.8035916988979097</v>
       </c>
       <c r="AJ20" s="6">
-        <f t="shared" ref="AJ20" si="44">AJ18/AJ19</f>
-        <v>2.7544625853096414</v>
+        <f t="shared" ref="AJ20" si="45">AJ18/AJ19</f>
+        <v>3.0034511766032788</v>
       </c>
     </row>
     <row r="22" spans="2:142" x14ac:dyDescent="0.3">
@@ -2638,69 +2824,73 @@
         <f>N3/J3-1</f>
         <v>8.6153846153846025E-2</v>
       </c>
+      <c r="O22" s="9">
+        <f>O3/K3-1</f>
+        <v>0.3904109589041096</v>
+      </c>
       <c r="T22" s="9"/>
       <c r="U22" s="9">
         <f>U3/T3-1</f>
         <v>0.45077720207253891</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" ref="V22:Y22" si="45">V3/U3-1</f>
+        <f t="shared" ref="V22:Y22" si="46">V3/U3-1</f>
         <v>0.51071428571428568</v>
       </c>
       <c r="W22" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.8085106382978724</v>
       </c>
       <c r="X22" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.42091503267973862</v>
       </c>
       <c r="Y22" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.170193192272309</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" ref="Z22:AJ22" si="46">Z3/Y3-1</f>
+        <f t="shared" ref="Z22:AJ22" si="47">Z3/Y3-1</f>
         <v>0.33647798742138368</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" si="46"/>
-        <v>0.14999999999999991</v>
+        <f t="shared" si="47"/>
+        <v>0.16999999999999993</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" si="46"/>
-        <v>8.0000000000000071E-2</v>
+        <f t="shared" si="47"/>
+        <v>9.000000000000008E-2</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AG22" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AH22" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AI22" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AJ22" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
@@ -2716,73 +2906,77 @@
         <f>N5/N3</f>
         <v>0.93767705382436251</v>
       </c>
+      <c r="O23" s="9">
+        <f>O5/O3</f>
+        <v>0.94581280788177335</v>
+      </c>
       <c r="T23" s="9">
-        <f t="shared" ref="T23:Y23" si="47">T5/T3</f>
+        <f t="shared" ref="T23:Y23" si="48">T5/T3</f>
         <v>1</v>
       </c>
       <c r="U23" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>1</v>
       </c>
       <c r="V23" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>1</v>
       </c>
       <c r="W23" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.96078431372549022</v>
       </c>
       <c r="X23" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.91628334866605343</v>
       </c>
       <c r="Y23" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.94103773584905659</v>
       </c>
       <c r="Z23" s="9">
-        <f t="shared" ref="Z23:AJ23" si="48">Z5/Z3</f>
+        <f t="shared" ref="Z23:AJ23" si="49">Z5/Z3</f>
         <v>0.94</v>
       </c>
       <c r="AA23" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
+        <v>0.94000000000000006</v>
+      </c>
+      <c r="AB23" s="9">
+        <f t="shared" si="49"/>
         <v>0.94</v>
       </c>
-      <c r="AB23" s="9">
-        <f t="shared" si="48"/>
+      <c r="AC23" s="9">
+        <f t="shared" si="49"/>
         <v>0.94</v>
       </c>
-      <c r="AC23" s="9">
-        <f t="shared" si="48"/>
+      <c r="AD23" s="9">
+        <f t="shared" si="49"/>
         <v>0.94</v>
       </c>
-      <c r="AD23" s="9">
-        <f t="shared" si="48"/>
+      <c r="AE23" s="9">
+        <f t="shared" si="49"/>
         <v>0.94</v>
       </c>
-      <c r="AE23" s="9">
-        <f t="shared" si="48"/>
+      <c r="AF23" s="9">
+        <f t="shared" si="49"/>
         <v>0.94</v>
       </c>
-      <c r="AF23" s="9">
-        <f t="shared" si="48"/>
+      <c r="AG23" s="9">
+        <f t="shared" si="49"/>
         <v>0.94</v>
       </c>
-      <c r="AG23" s="9">
-        <f t="shared" si="48"/>
-        <v>0.94000000000000006</v>
-      </c>
       <c r="AH23" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
+        <v>0.93999999999999984</v>
+      </c>
+      <c r="AI23" s="9">
+        <f t="shared" si="49"/>
         <v>0.94</v>
       </c>
-      <c r="AI23" s="9">
-        <f t="shared" si="48"/>
-        <v>0.93999999999999984</v>
-      </c>
       <c r="AJ23" s="9">
-        <f t="shared" si="48"/>
-        <v>0.93999999999999984</v>
+        <f t="shared" si="49"/>
+        <v>0.94</v>
       </c>
     </row>
     <row r="24" spans="2:142" x14ac:dyDescent="0.3">
@@ -2797,72 +2991,76 @@
         <f>N6/N3</f>
         <v>0.30878186968838528</v>
       </c>
+      <c r="O24" s="9">
+        <f>O6/O3</f>
+        <v>0.37438423645320196</v>
+      </c>
       <c r="T24" s="9">
-        <f t="shared" ref="T24:Y24" si="49">T6/T3</f>
+        <f t="shared" ref="T24:Y24" si="50">T6/T3</f>
         <v>0.56476683937823835</v>
       </c>
       <c r="U24" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.28928571428571426</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.33333333333333337</v>
       </c>
       <c r="W24" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.44052287581699351</v>
       </c>
       <c r="X24" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.32474701011959517</v>
       </c>
       <c r="Y24" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.32940251572327039</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" ref="Z24:AJ24" si="50">Z6/Z3</f>
+        <f t="shared" ref="Z24:AJ24" si="51">Z6/Z3</f>
         <v>0.32</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.31</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" si="50"/>
-        <v>0.31000000000000005</v>
+        <f t="shared" si="51"/>
+        <v>0.31</v>
       </c>
       <c r="AC24" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.31</v>
       </c>
       <c r="AD24" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.31</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.31</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.31</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.31</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.31</v>
       </c>
       <c r="AI24" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.31</v>
       </c>
       <c r="AJ24" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.31</v>
       </c>
       <c r="AL24" t="s">
@@ -2881,70 +3079,74 @@
         <f>N7/J7-1</f>
         <v>0.25806451612903225</v>
       </c>
+      <c r="O25" s="9">
+        <f>O7/K7-1</f>
+        <v>0.625</v>
+      </c>
       <c r="T25" s="9"/>
       <c r="U25" s="9">
         <f>U7/T7-1</f>
         <v>0</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" ref="V25:Y25" si="51">V7/U7-1</f>
+        <f t="shared" ref="V25:Y25" si="52">V7/U7-1</f>
         <v>0.56000000000000005</v>
       </c>
       <c r="W25" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.74358974358974361</v>
       </c>
       <c r="X25" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.51470588235294135</v>
       </c>
       <c r="Y25" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="52"/>
         <v>0.34951456310679596</v>
       </c>
       <c r="Z25" s="9">
-        <f t="shared" ref="Z25:AJ25" si="52">Z7/Y7-1</f>
+        <f t="shared" ref="Z25:AJ25" si="53">Z7/Y7-1</f>
         <v>0.21999999999999975</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="52"/>
-        <v>0.19999999999999996</v>
+        <f t="shared" si="53"/>
+        <v>0.17999999999999994</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" si="52"/>
-        <v>0.14999999999999991</v>
+        <f t="shared" si="53"/>
+        <v>0.1399999999999999</v>
       </c>
       <c r="AC25" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AE25" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AF25" s="9">
-        <f t="shared" si="52"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="53"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AG25" s="9">
-        <f t="shared" si="52"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="53"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AH25" s="9">
-        <f t="shared" si="52"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="53"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI25" s="9">
-        <f t="shared" si="52"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="53"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ25" s="9">
-        <f t="shared" si="52"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="53"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL25" t="s">
         <v>52</v>
@@ -2962,69 +3164,73 @@
         <f>N8/J8-1</f>
         <v>0.28571428571428581</v>
       </c>
+      <c r="O26" s="9">
+        <f>O8/K8-1</f>
+        <v>0.22222222222222232</v>
+      </c>
       <c r="T26" s="9"/>
       <c r="U26" s="9">
-        <f t="shared" ref="U26:Y26" si="53">U8/T8-1</f>
+        <f t="shared" ref="U26:Y26" si="54">U8/T8-1</f>
         <v>0.4285714285714286</v>
       </c>
       <c r="V26" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>1.1666666666666665</v>
       </c>
       <c r="W26" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0.5</v>
       </c>
       <c r="X26" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0.24615384615384617</v>
       </c>
       <c r="Y26" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="54"/>
         <v>0.13580246913580241</v>
       </c>
       <c r="Z26" s="9">
-        <f t="shared" ref="Z26:AJ26" si="54">Z8/Y8-1</f>
+        <f t="shared" ref="Z26:AJ26" si="55">Z8/Y8-1</f>
         <v>0.25</v>
       </c>
       <c r="AA26" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AB26" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AC26" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AD26" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AE26" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF26" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG26" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH26" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI26" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ26" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL26" t="s">
@@ -3032,7 +3238,7 @@
       </c>
       <c r="AM26" s="2">
         <f>NPV(AM25,Z18:EL18)</f>
-        <v>654.82767746454749</v>
+        <v>701.42605820735139</v>
       </c>
     </row>
     <row r="27" spans="2:142" x14ac:dyDescent="0.3">
@@ -3047,80 +3253,84 @@
         <f>N10/N3</f>
         <v>0.26345609065155789</v>
       </c>
+      <c r="O27" s="9">
+        <f>O10/O3</f>
+        <v>0.2536945812807882</v>
+      </c>
       <c r="T27" s="9">
-        <f t="shared" ref="T27:Y27" si="55">T10/T3</f>
+        <f t="shared" ref="T27:Y27" si="56">T10/T3</f>
         <v>8.8082901554404111E-2</v>
       </c>
       <c r="U27" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.40714285714285708</v>
       </c>
       <c r="V27" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.26713947990543729</v>
       </c>
       <c r="W27" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.17647058823529413</v>
       </c>
       <c r="X27" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.27322907083716669</v>
       </c>
       <c r="Y27" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.285377358490566</v>
       </c>
       <c r="Z27" s="9">
-        <f t="shared" ref="Z27:AJ27" si="56">Z10/Z3</f>
+        <f t="shared" ref="Z27:AJ27" si="57">Z10/Z3</f>
         <v>0.31730588235294105</v>
       </c>
       <c r="AA27" s="9">
-        <f t="shared" si="56"/>
-        <v>0.3229687979539641</v>
+        <f t="shared" si="57"/>
+        <v>0.32992237305178485</v>
       </c>
       <c r="AB27" s="9">
-        <f t="shared" si="56"/>
-        <v>0.32185947712418295</v>
+        <f t="shared" si="57"/>
+        <v>0.33262751740075003</v>
       </c>
       <c r="AC27" s="9">
-        <f t="shared" si="56"/>
-        <v>0.32428379451469053</v>
+        <f t="shared" si="57"/>
+        <v>0.33506485076305165</v>
       </c>
       <c r="AD27" s="9">
-        <f t="shared" si="56"/>
-        <v>0.33078624996110251</v>
+        <f t="shared" si="57"/>
+        <v>0.34137111782740609</v>
       </c>
       <c r="AE27" s="9">
-        <f t="shared" si="56"/>
-        <v>0.33611037926015053</v>
+        <f t="shared" si="57"/>
+        <v>0.34655622610735409</v>
       </c>
       <c r="AF27" s="9">
-        <f t="shared" si="56"/>
-        <v>0.34128239057922577</v>
+        <f t="shared" si="57"/>
+        <v>0.35261366550667911</v>
       </c>
       <c r="AG27" s="9">
-        <f t="shared" si="56"/>
-        <v>0.34630663014632762</v>
+        <f t="shared" si="57"/>
+        <v>0.35952823110835325</v>
       </c>
       <c r="AH27" s="9">
-        <f t="shared" si="56"/>
-        <v>0.35118732001151215</v>
+        <f t="shared" si="57"/>
+        <v>0.36725599593382879</v>
       </c>
       <c r="AI27" s="9">
-        <f t="shared" si="56"/>
-        <v>0.35592856159483416</v>
+        <f t="shared" si="57"/>
+        <v>0.37476296747857651</v>
       </c>
       <c r="AJ27" s="9">
-        <f t="shared" si="56"/>
-        <v>0.3605343391329186</v>
+        <f t="shared" si="57"/>
+        <v>0.38205545412204583</v>
       </c>
       <c r="AL27" t="s">
         <v>57</v>
       </c>
       <c r="AM27" s="2">
         <f>Main!D8</f>
-        <v>-9.2000000000000028</v>
+        <v>-67</v>
       </c>
     </row>
     <row r="28" spans="2:142" x14ac:dyDescent="0.3">
@@ -3135,72 +3345,76 @@
         <f>N17/N16</f>
         <v>0.12087912087912096</v>
       </c>
+      <c r="O28" s="9">
+        <f>O17/O16</f>
+        <v>-2.7522935779816512E-2</v>
+      </c>
       <c r="T28" s="9">
-        <f t="shared" ref="T28:Y28" si="57">T17/T16</f>
+        <f t="shared" ref="T28:Y28" si="58">T17/T16</f>
         <v>-0.81818181818181779</v>
       </c>
       <c r="U28" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>-0.40186915887850466</v>
       </c>
       <c r="V28" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>-2.4590163934426233E-2</v>
       </c>
       <c r="W28" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.17857142857142874</v>
       </c>
       <c r="X28" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>9.4059405940593976E-2</v>
       </c>
       <c r="Y28" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.10204081632653061</v>
       </c>
       <c r="Z28" s="9">
-        <f t="shared" ref="Z28:AJ28" si="58">Z17/Z16</f>
+        <f t="shared" ref="Z28:AJ28" si="59">Z17/Z16</f>
         <v>0.15</v>
       </c>
       <c r="AA28" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.15</v>
       </c>
       <c r="AB28" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.15</v>
       </c>
       <c r="AC28" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.15</v>
       </c>
       <c r="AD28" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.15</v>
       </c>
       <c r="AE28" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.15</v>
       </c>
       <c r="AF28" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.15</v>
       </c>
       <c r="AG28" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.15</v>
       </c>
       <c r="AH28" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.15</v>
       </c>
       <c r="AI28" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.15</v>
       </c>
       <c r="AJ28" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="59"/>
         <v>0.15</v>
       </c>
       <c r="AL28" t="s">
@@ -3208,7 +3422,7 @@
       </c>
       <c r="AM28" s="2">
         <f>AM26+AM27</f>
-        <v>645.62767746454745</v>
+        <v>634.42605820735139</v>
       </c>
     </row>
     <row r="29" spans="2:142" x14ac:dyDescent="0.3">
@@ -3223,80 +3437,84 @@
         <f>N18/N3</f>
         <v>0.22662889518413584</v>
       </c>
+      <c r="O29" s="9">
+        <f>O18/O3</f>
+        <v>0.27586206896551724</v>
+      </c>
       <c r="T29" s="9">
-        <f t="shared" ref="T29:Y29" si="59">T18/T3</f>
+        <f t="shared" ref="T29:Y29" si="60">T18/T3</f>
         <v>-0.10362694300518137</v>
       </c>
       <c r="U29" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.5357142857142857</v>
       </c>
       <c r="V29" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.29550827423167847</v>
       </c>
       <c r="W29" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>3.0065359477124146E-2</v>
       </c>
       <c r="X29" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.16835326586936539</v>
       </c>
       <c r="Y29" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.24213836477987419</v>
       </c>
       <c r="Z29" s="9">
-        <f t="shared" ref="Z29:AJ29" si="60">Z18/Z3</f>
+        <f t="shared" ref="Z29:AJ29" si="61">Z18/Z3</f>
         <v>0.25935999999999987</v>
       </c>
       <c r="AA29" s="9">
-        <f t="shared" si="60"/>
-        <v>0.26520782608695642</v>
+        <f t="shared" si="61"/>
+        <v>0.27127760683760688</v>
       </c>
       <c r="AB29" s="9">
-        <f t="shared" si="60"/>
-        <v>0.26465179951690815</v>
+        <f t="shared" si="61"/>
+        <v>0.27403777699364856</v>
       </c>
       <c r="AC29" s="9">
-        <f t="shared" si="60"/>
-        <v>0.26700270012190164</v>
+        <f t="shared" si="61"/>
+        <v>0.27639216281160889</v>
       </c>
       <c r="AD29" s="9">
-        <f t="shared" si="60"/>
-        <v>0.27273113025567841</v>
+        <f t="shared" si="61"/>
+        <v>0.28194857545213992</v>
       </c>
       <c r="AE29" s="9">
-        <f t="shared" si="60"/>
-        <v>0.27737420483408598</v>
+        <f t="shared" si="61"/>
+        <v>0.28647041237394821</v>
       </c>
       <c r="AF29" s="9">
-        <f t="shared" si="60"/>
-        <v>0.28188573980238879</v>
+        <f t="shared" si="61"/>
+        <v>0.2917315498922966</v>
       </c>
       <c r="AG29" s="9">
-        <f t="shared" si="60"/>
-        <v>0.28626947210823633</v>
+        <f t="shared" si="61"/>
+        <v>0.2977191053678051</v>
       </c>
       <c r="AH29" s="9">
-        <f t="shared" si="60"/>
-        <v>0.29052903233557198</v>
+        <f t="shared" si="61"/>
+        <v>0.3043957816175622</v>
       </c>
       <c r="AI29" s="9">
-        <f t="shared" si="60"/>
-        <v>0.29466794773585925</v>
+        <f t="shared" si="61"/>
+        <v>0.31088272498540348</v>
       </c>
       <c r="AJ29" s="9">
-        <f t="shared" si="60"/>
-        <v>0.29868964517284763</v>
+        <f t="shared" si="61"/>
+        <v>0.31718533680516181</v>
       </c>
       <c r="AL29" t="s">
         <v>55</v>
       </c>
       <c r="AM29" s="1">
         <f>AM28/AJ19</f>
-        <v>18.552519467372054</v>
+        <v>18.230633856533089</v>
       </c>
     </row>
     <row r="30" spans="2:142" x14ac:dyDescent="0.3">
@@ -3305,7 +3523,7 @@
       </c>
       <c r="AM30" s="1">
         <f>Main!D3</f>
-        <v>12.25</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="31" spans="2:142" x14ac:dyDescent="0.3">
@@ -3314,7 +3532,7 @@
       </c>
       <c r="AM31" s="10">
         <f>AM29/AM30-1</f>
-        <v>0.5144913850915962</v>
+        <v>0.51669166859676285</v>
       </c>
     </row>
     <row r="32" spans="2:142" x14ac:dyDescent="0.3">

--- a/Financial Analysis/GAMB.xlsx
+++ b/Financial Analysis/GAMB.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{129F8979-8BC3-4807-8B5D-2B0E68B1469E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C5B38E-18EF-4831-BAF9-1615BAF46C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{D6459E68-7D6A-410F-A9B8-1584227EFFA5}"/>
   </bookViews>
@@ -25,8 +25,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Anton Mniszek</author>
+  </authors>
+  <commentList>
+    <comment ref="Z3" authorId="0" shapeId="0" xr:uid="{777C2709-88CF-4872-8B59-CCCAE5ACE6D0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anton Mniszek:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+175 mill FY guidance</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
   <si>
     <t>GAMB</t>
   </si>
@@ -209,9 +243,6 @@
   </si>
   <si>
     <t>Heavily undervalued</t>
-  </si>
-  <si>
-    <t>Q125 6K</t>
   </si>
 </sst>
 </file>
@@ -221,7 +252,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -250,6 +281,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -361,13 +405,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
+      <xdr:col>15</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
@@ -385,7 +429,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9433560" y="7620"/>
+          <a:off x="10043160" y="7620"/>
           <a:ext cx="0" cy="6134100"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -734,17 +778,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>12.02</v>
+        <v>8.02</v>
       </c>
       <c r="E3" s="4">
-        <v>45804</v>
+        <v>45910</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45910</v>
       </c>
       <c r="G3" s="4">
-        <v>45883</v>
+        <v>45974</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -752,11 +796,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="2">
-        <f>35.6</f>
-        <v>35.6</v>
+        <f>35.7</f>
+        <v>35.700000000000003</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -765,7 +809,7 @@
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>427.91199999999998</v>
+        <v>286.31400000000002</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -773,11 +817,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="2">
-        <f>21.5</f>
-        <v>21.5</v>
+        <f>18.7</f>
+        <v>18.7</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -785,11 +829,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="2">
-        <f>10.4+78.1</f>
-        <v>88.5</v>
+        <f>14.4+75.8</f>
+        <v>90.2</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -798,7 +842,7 @@
       </c>
       <c r="D8" s="2">
         <f>D6-D7</f>
-        <v>-67</v>
+        <v>-71.5</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -807,7 +851,7 @@
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>494.91199999999998</v>
+        <v>357.81400000000002</v>
       </c>
     </row>
   </sheetData>
@@ -816,7 +860,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF643BE1-3816-4557-867E-C0ACDC26617E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF643BE1-3816-4557-867E-C0ACDC26617E}">
   <dimension ref="B2:EL32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -931,18 +975,41 @@
       <c r="B3" s="7" t="s">
         <v>11</v>
       </c>
+      <c r="H3" s="8">
+        <v>26</v>
+      </c>
+      <c r="I3" s="8">
+        <v>23.5</v>
+      </c>
       <c r="J3" s="8">
         <v>32.5</v>
       </c>
       <c r="K3" s="8">
         <v>29.2</v>
       </c>
+      <c r="L3" s="8">
+        <v>30.5</v>
+      </c>
+      <c r="M3" s="8">
+        <v>32.1</v>
+      </c>
       <c r="N3" s="8">
         <v>35.299999999999997</v>
       </c>
       <c r="O3" s="8">
         <v>40.6</v>
       </c>
+      <c r="P3" s="8">
+        <v>39.6</v>
+      </c>
+      <c r="Q3" s="8">
+        <f>M3*1.33</f>
+        <v>42.693000000000005</v>
+      </c>
+      <c r="R3" s="8">
+        <f>N3*1.3</f>
+        <v>45.89</v>
+      </c>
       <c r="T3" s="8">
         <v>19.3</v>
       </c>
@@ -962,64 +1029,88 @@
         <v>127.2</v>
       </c>
       <c r="Z3" s="8">
-        <v>170</v>
+        <f>SUM(O3:R3)</f>
+        <v>168.78300000000002</v>
       </c>
       <c r="AA3" s="8">
         <f>Z3*1.17</f>
-        <v>198.89999999999998</v>
+        <v>197.47611000000001</v>
       </c>
       <c r="AB3" s="8">
         <f>AA3*1.09</f>
-        <v>216.80099999999999</v>
+        <v>215.24895990000002</v>
       </c>
       <c r="AC3" s="8">
         <f>AB3*1.07</f>
-        <v>231.97707</v>
+        <v>230.31638709300003</v>
       </c>
       <c r="AD3" s="8">
         <f>AC3*1.06</f>
-        <v>245.89569420000001</v>
+        <v>244.13537031858004</v>
       </c>
       <c r="AE3" s="8">
         <f>AD3*1.05</f>
-        <v>258.19047891000002</v>
+        <v>256.34213883450906</v>
       </c>
       <c r="AF3" s="8">
-        <f t="shared" ref="AF3:AJ3" si="0">AE3*1.05</f>
-        <v>271.10000285550007</v>
+        <f>AE3*1.04</f>
+        <v>266.59582438788942</v>
       </c>
       <c r="AG3" s="8">
-        <f t="shared" si="0"/>
-        <v>284.65500299827511</v>
+        <f>AF3*1.03</f>
+        <v>274.59369911952609</v>
       </c>
       <c r="AH3" s="8">
-        <f t="shared" si="0"/>
-        <v>298.88775314818889</v>
+        <f>AG3*1.02</f>
+        <v>280.08557310191662</v>
       </c>
       <c r="AI3" s="8">
-        <f t="shared" si="0"/>
-        <v>313.83214080559833</v>
+        <f t="shared" ref="AI3:AJ3" si="0">AH3*1.02</f>
+        <v>285.68728456395496</v>
       </c>
       <c r="AJ3" s="8">
         <f t="shared" si="0"/>
-        <v>329.52374784587823</v>
+        <v>291.40103025523405</v>
       </c>
     </row>
     <row r="4" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>12</v>
       </c>
+      <c r="H4" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="I4" s="2">
+        <v>2.1</v>
+      </c>
       <c r="J4" s="2">
         <v>5.0999999999999996</v>
       </c>
       <c r="K4" s="2">
         <v>2.2000000000000002</v>
       </c>
+      <c r="L4" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="M4" s="2">
+        <v>1.7</v>
+      </c>
       <c r="N4" s="2">
         <v>2.2000000000000002</v>
       </c>
       <c r="O4" s="2">
         <v>2.2000000000000002</v>
+      </c>
+      <c r="P4" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="Q4" s="2">
+        <f>Q3-Q5</f>
+        <v>2.988509999999998</v>
+      </c>
+      <c r="R4" s="2">
+        <f>R3-R5</f>
+        <v>3.212299999999999</v>
       </c>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
@@ -1034,155 +1125,204 @@
         <v>7.5</v>
       </c>
       <c r="Z4" s="2">
-        <f>Z3-Z5</f>
-        <v>10.200000000000017</v>
+        <f>SUM(O4:R4)</f>
+        <v>11.100809999999997</v>
       </c>
       <c r="AA4" s="2">
         <f>AA3-AA5</f>
-        <v>11.933999999999997</v>
+        <v>11.848566599999998</v>
       </c>
       <c r="AB4" s="2">
         <f t="shared" ref="AB4:AJ4" si="1">AB3-AB5</f>
-        <v>13.00806</v>
+        <v>12.914937594000008</v>
       </c>
       <c r="AC4" s="2">
         <f t="shared" si="1"/>
-        <v>13.918624200000011</v>
+        <v>13.818983225580013</v>
       </c>
       <c r="AD4" s="2">
         <f t="shared" si="1"/>
-        <v>14.753741652000002</v>
+        <v>14.648122219114811</v>
       </c>
       <c r="AE4" s="2">
         <f t="shared" si="1"/>
-        <v>15.491428734600021</v>
+        <v>15.380528330070547</v>
       </c>
       <c r="AF4" s="2">
         <f t="shared" si="1"/>
-        <v>16.266000171330006</v>
+        <v>15.99574946327337</v>
       </c>
       <c r="AG4" s="2">
         <f t="shared" si="1"/>
-        <v>17.079300179896507</v>
+        <v>16.475621947171589</v>
       </c>
       <c r="AH4" s="2">
         <f t="shared" si="1"/>
-        <v>17.933265188891369</v>
+        <v>16.805134386115014</v>
       </c>
       <c r="AI4" s="2">
         <f t="shared" si="1"/>
-        <v>18.82992844833592</v>
+        <v>17.141237073837317</v>
       </c>
       <c r="AJ4" s="2">
         <f t="shared" si="1"/>
-        <v>19.771424870752696</v>
+        <v>17.484061815314078</v>
       </c>
     </row>
     <row r="5" spans="2:36" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
         <v>13</v>
       </c>
+      <c r="H5" s="8">
+        <f t="shared" ref="H5:P5" si="2">H3-H4</f>
+        <v>25.1</v>
+      </c>
+      <c r="I5" s="8">
+        <f t="shared" si="2"/>
+        <v>21.4</v>
+      </c>
       <c r="J5" s="8">
-        <f>J3-J4</f>
+        <f t="shared" si="2"/>
         <v>27.4</v>
       </c>
       <c r="K5" s="8">
-        <f>K3-K4</f>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
+      <c r="L5" s="8">
+        <f t="shared" si="2"/>
+        <v>29.1</v>
+      </c>
+      <c r="M5" s="8">
+        <f t="shared" si="2"/>
+        <v>30.400000000000002</v>
+      </c>
       <c r="N5" s="8">
-        <f>N3-N4</f>
+        <f t="shared" si="2"/>
         <v>33.099999999999994</v>
       </c>
       <c r="O5" s="8">
-        <f>O3-O4</f>
+        <f t="shared" si="2"/>
         <v>38.4</v>
       </c>
+      <c r="P5" s="8">
+        <f t="shared" si="2"/>
+        <v>36.9</v>
+      </c>
+      <c r="Q5" s="8">
+        <f>Q3*0.93</f>
+        <v>39.704490000000007</v>
+      </c>
+      <c r="R5" s="8">
+        <f>R3*0.93</f>
+        <v>42.677700000000002</v>
+      </c>
       <c r="T5" s="8">
-        <f t="shared" ref="T5:Y5" si="2">T3-T4</f>
+        <f t="shared" ref="T5:Z5" si="3">T3-T4</f>
         <v>19.3</v>
       </c>
       <c r="U5" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>28</v>
       </c>
       <c r="V5" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>42.3</v>
       </c>
       <c r="W5" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>73.5</v>
       </c>
       <c r="X5" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>99.600000000000009</v>
       </c>
       <c r="Y5" s="8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>119.7</v>
       </c>
       <c r="Z5" s="8">
-        <f>Z3*0.94</f>
-        <v>159.79999999999998</v>
+        <f t="shared" si="3"/>
+        <v>157.68219000000002</v>
       </c>
       <c r="AA5" s="8">
         <f>AA3*0.94</f>
-        <v>186.96599999999998</v>
+        <v>185.62754340000001</v>
       </c>
       <c r="AB5" s="8">
-        <f t="shared" ref="AB5:AJ5" si="3">AB3*0.94</f>
-        <v>203.79293999999999</v>
+        <f t="shared" ref="AB5:AJ5" si="4">AB3*0.94</f>
+        <v>202.33402230600001</v>
       </c>
       <c r="AC5" s="8">
-        <f t="shared" si="3"/>
-        <v>218.05844579999999</v>
+        <f t="shared" si="4"/>
+        <v>216.49740386742002</v>
       </c>
       <c r="AD5" s="8">
-        <f t="shared" si="3"/>
-        <v>231.14195254800001</v>
+        <f t="shared" si="4"/>
+        <v>229.48724809946523</v>
       </c>
       <c r="AE5" s="8">
-        <f t="shared" si="3"/>
-        <v>242.6990501754</v>
+        <f t="shared" si="4"/>
+        <v>240.96161050443851</v>
       </c>
       <c r="AF5" s="8">
-        <f t="shared" si="3"/>
-        <v>254.83400268417006</v>
+        <f t="shared" si="4"/>
+        <v>250.60007492461605</v>
       </c>
       <c r="AG5" s="8">
-        <f t="shared" si="3"/>
-        <v>267.5757028183786</v>
+        <f t="shared" si="4"/>
+        <v>258.1180771723545</v>
       </c>
       <c r="AH5" s="8">
-        <f t="shared" si="3"/>
-        <v>280.95448795929752</v>
+        <f t="shared" si="4"/>
+        <v>263.28043871580161</v>
       </c>
       <c r="AI5" s="8">
-        <f t="shared" si="3"/>
-        <v>295.00221235726241</v>
+        <f t="shared" si="4"/>
+        <v>268.54604749011764</v>
       </c>
       <c r="AJ5" s="8">
-        <f t="shared" si="3"/>
-        <v>309.75232297512554</v>
+        <f t="shared" si="4"/>
+        <v>273.91696843991997</v>
       </c>
     </row>
     <row r="6" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>14</v>
       </c>
+      <c r="H6" s="2">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="I6" s="2">
+        <v>8.6</v>
+      </c>
       <c r="J6" s="2">
         <v>9.6999999999999993</v>
       </c>
       <c r="K6" s="2">
         <v>9.6</v>
       </c>
+      <c r="L6" s="2">
+        <v>10.7</v>
+      </c>
+      <c r="M6" s="2">
+        <v>10.8</v>
+      </c>
       <c r="N6" s="2">
         <v>10.9</v>
       </c>
       <c r="O6" s="2">
         <v>15.2</v>
       </c>
+      <c r="P6" s="2">
+        <v>15.4</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>15</v>
+      </c>
+      <c r="R6" s="2">
+        <v>15</v>
+      </c>
       <c r="T6" s="2">
         <v>10.9</v>
       </c>
@@ -1202,66 +1342,87 @@
         <v>41.9</v>
       </c>
       <c r="Z6" s="2">
-        <f>Z3*0.32</f>
-        <v>54.4</v>
+        <f t="shared" ref="Z6:Z8" si="5">SUM(O6:R6)</f>
+        <v>60.6</v>
       </c>
       <c r="AA6" s="2">
-        <f>AA3*0.31</f>
-        <v>61.658999999999992</v>
+        <f>AA3*0.33</f>
+        <v>65.167116300000004</v>
       </c>
       <c r="AB6" s="2">
-        <f>AB3*0.31</f>
-        <v>67.208309999999997</v>
+        <f>AB3*0.32</f>
+        <v>68.879667168000012</v>
       </c>
       <c r="AC6" s="2">
-        <f t="shared" ref="AC6:AJ6" si="4">AC3*0.31</f>
-        <v>71.912891700000003</v>
+        <f t="shared" ref="AC6:AJ6" si="6">AC3*0.31</f>
+        <v>71.398079998830013</v>
       </c>
       <c r="AD6" s="2">
-        <f t="shared" si="4"/>
-        <v>76.227665201999997</v>
+        <f t="shared" si="6"/>
+        <v>75.681964798759807</v>
       </c>
       <c r="AE6" s="2">
-        <f t="shared" si="4"/>
-        <v>80.039048462100013</v>
+        <f t="shared" si="6"/>
+        <v>79.466063038697811</v>
       </c>
       <c r="AF6" s="2">
-        <f t="shared" si="4"/>
-        <v>84.041000885205023</v>
+        <f t="shared" si="6"/>
+        <v>82.644705560245725</v>
       </c>
       <c r="AG6" s="2">
-        <f t="shared" si="4"/>
-        <v>88.243050929465284</v>
+        <f t="shared" si="6"/>
+        <v>85.124046727053084</v>
       </c>
       <c r="AH6" s="2">
-        <f t="shared" si="4"/>
-        <v>92.655203475938549</v>
+        <f t="shared" si="6"/>
+        <v>86.826527661594156</v>
       </c>
       <c r="AI6" s="2">
-        <f t="shared" si="4"/>
-        <v>97.287963649735488</v>
+        <f t="shared" si="6"/>
+        <v>88.563058214826043</v>
       </c>
       <c r="AJ6" s="2">
-        <f t="shared" si="4"/>
-        <v>102.15236183222225</v>
+        <f t="shared" si="6"/>
+        <v>90.334319379122547</v>
       </c>
     </row>
     <row r="7" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>15</v>
       </c>
+      <c r="H7" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="I7" s="2">
+        <v>2.5</v>
+      </c>
       <c r="J7" s="2">
         <v>3.1</v>
       </c>
       <c r="K7" s="2">
         <v>3.2</v>
       </c>
+      <c r="L7" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="M7" s="2">
+        <v>3.6</v>
+      </c>
       <c r="N7" s="2">
         <v>3.9</v>
       </c>
       <c r="O7" s="2">
         <v>5.2</v>
       </c>
+      <c r="P7" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>6.4</v>
+      </c>
+      <c r="R7" s="2">
+        <v>6.8</v>
+      </c>
       <c r="T7" s="2">
         <v>2.5</v>
       </c>
@@ -1281,66 +1442,89 @@
         <v>13.9</v>
       </c>
       <c r="Z7" s="2">
-        <f>Y7*1.22</f>
-        <v>16.957999999999998</v>
+        <f t="shared" si="5"/>
+        <v>24.500000000000004</v>
       </c>
       <c r="AA7" s="2">
-        <f>Z7*1.18</f>
-        <v>20.010439999999996</v>
+        <f>Z7*1.4</f>
+        <v>34.300000000000004</v>
       </c>
       <c r="AB7" s="2">
-        <f>AA7*1.14</f>
-        <v>22.811901599999992</v>
+        <f>AA7*1.2</f>
+        <v>41.160000000000004</v>
       </c>
       <c r="AC7" s="2">
         <f>AB7*1.1</f>
-        <v>25.093091759999993</v>
+        <v>45.27600000000001</v>
       </c>
       <c r="AD7" s="2">
         <f>AC7*1.05</f>
-        <v>26.347746347999994</v>
+        <v>47.539800000000014</v>
       </c>
       <c r="AE7" s="2">
-        <f t="shared" ref="AE7" si="5">AD7*1.05</f>
-        <v>27.665133665399996</v>
+        <f>AD7*1.04</f>
+        <v>49.441392000000015</v>
       </c>
       <c r="AF7" s="2">
-        <f>AE7*1.04</f>
-        <v>28.771739012015995</v>
+        <f>AE7*1.03</f>
+        <v>50.924633760000013</v>
       </c>
       <c r="AG7" s="2">
-        <f>AF7*1.03</f>
-        <v>29.634891182376474</v>
+        <f>AF7*1.02</f>
+        <v>51.943126435200014</v>
       </c>
       <c r="AH7" s="2">
-        <f>AG7*1.02</f>
-        <v>30.227589006024004</v>
+        <f t="shared" ref="AH7:AJ7" si="7">AG7*1.02</f>
+        <v>52.981988963904016</v>
       </c>
       <c r="AI7" s="2">
-        <f t="shared" ref="AI7:AJ7" si="6">AH7*1.02</f>
-        <v>30.832140786144485</v>
+        <f t="shared" si="7"/>
+        <v>54.041628743182095</v>
       </c>
       <c r="AJ7" s="2">
-        <f t="shared" si="6"/>
-        <v>31.448783601867376</v>
+        <f t="shared" si="7"/>
+        <v>55.122461318045737</v>
       </c>
     </row>
     <row r="8" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>16</v>
       </c>
+      <c r="H8" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="I8" s="2">
+        <v>4.8</v>
+      </c>
       <c r="J8" s="2">
         <v>7</v>
       </c>
       <c r="K8" s="2">
         <v>6.3</v>
       </c>
+      <c r="L8" s="2">
+        <v>6.2</v>
+      </c>
+      <c r="M8" s="2">
+        <v>6</v>
+      </c>
       <c r="N8" s="2">
         <v>9</v>
       </c>
       <c r="O8" s="2">
         <v>7.7</v>
       </c>
+      <c r="P8" s="2">
+        <v>8.4</v>
+      </c>
+      <c r="Q8" s="2">
+        <f>M8*1.5</f>
+        <v>9</v>
+      </c>
+      <c r="R8" s="2">
+        <f>N8*1.15</f>
+        <v>10.35</v>
+      </c>
       <c r="T8" s="2">
         <v>4.2</v>
       </c>
@@ -1360,244 +1544,321 @@
         <v>27.6</v>
       </c>
       <c r="Z8" s="2">
-        <f>Y8*1.25</f>
-        <v>34.5</v>
+        <f t="shared" si="5"/>
+        <v>35.450000000000003</v>
       </c>
       <c r="AA8" s="2">
         <f>Z8*1.15</f>
-        <v>39.674999999999997</v>
+        <v>40.767499999999998</v>
       </c>
       <c r="AB8" s="2">
-        <f>AA8*1.05</f>
-        <v>41.658749999999998</v>
+        <f>AA8*1.08</f>
+        <v>44.0289</v>
       </c>
       <c r="AC8" s="2">
-        <f>AB8*1.04</f>
-        <v>43.325099999999999</v>
+        <f>AB8*1.05</f>
+        <v>46.230345</v>
       </c>
       <c r="AD8" s="2">
         <f>AC8*1.03</f>
-        <v>44.624853000000002</v>
+        <v>47.617255350000001</v>
       </c>
       <c r="AE8" s="2">
-        <f t="shared" ref="AE8:AJ8" si="7">AD8*1.02</f>
-        <v>45.517350060000005</v>
+        <f t="shared" ref="AE8:AJ8" si="8">AD8*1.02</f>
+        <v>48.569600457</v>
       </c>
       <c r="AF8" s="2">
-        <f t="shared" si="7"/>
-        <v>46.427697061200007</v>
+        <f t="shared" si="8"/>
+        <v>49.540992466140004</v>
       </c>
       <c r="AG8" s="2">
-        <f t="shared" si="7"/>
-        <v>47.35625100242401</v>
+        <f t="shared" si="8"/>
+        <v>50.531812315462808</v>
       </c>
       <c r="AH8" s="2">
-        <f t="shared" si="7"/>
-        <v>48.303376022472492</v>
+        <f t="shared" si="8"/>
+        <v>51.542448561772062</v>
       </c>
       <c r="AI8" s="2">
-        <f t="shared" si="7"/>
-        <v>49.269443542921941</v>
+        <f t="shared" si="8"/>
+        <v>52.573297533007505</v>
       </c>
       <c r="AJ8" s="2">
-        <f t="shared" si="7"/>
-        <v>50.254832413780377</v>
+        <f t="shared" si="8"/>
+        <v>53.624763483667657</v>
       </c>
     </row>
     <row r="9" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>18</v>
       </c>
+      <c r="H9" s="2">
+        <f t="shared" ref="H9:P9" si="9">SUM(H6:H8)</f>
+        <v>18.100000000000001</v>
+      </c>
+      <c r="I9" s="2">
+        <f t="shared" si="9"/>
+        <v>15.899999999999999</v>
+      </c>
       <c r="J9" s="2">
-        <f>SUM(J6:J8)</f>
+        <f t="shared" si="9"/>
         <v>19.799999999999997</v>
       </c>
       <c r="K9" s="2">
-        <f>SUM(K6:K8)</f>
+        <f t="shared" si="9"/>
         <v>19.100000000000001</v>
       </c>
+      <c r="L9" s="2">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+      <c r="M9" s="2">
+        <f t="shared" si="9"/>
+        <v>20.399999999999999</v>
+      </c>
       <c r="N9" s="2">
-        <f>SUM(N6:N8)</f>
+        <f t="shared" si="9"/>
         <v>23.8</v>
       </c>
       <c r="O9" s="2">
-        <f>SUM(O6:O8)</f>
+        <f t="shared" si="9"/>
         <v>28.099999999999998</v>
       </c>
+      <c r="P9" s="2">
+        <f t="shared" si="9"/>
+        <v>29.9</v>
+      </c>
+      <c r="Q9" s="2">
+        <f t="shared" ref="Q9" si="10">SUM(Q6:Q8)</f>
+        <v>30.4</v>
+      </c>
+      <c r="R9" s="2">
+        <f t="shared" ref="R9" si="11">SUM(R6:R8)</f>
+        <v>32.15</v>
+      </c>
       <c r="T9" s="2">
-        <f t="shared" ref="T9:Y9" si="8">SUM(T6:T8)</f>
+        <f t="shared" ref="T9:Y9" si="12">SUM(T6:T8)</f>
         <v>17.600000000000001</v>
       </c>
       <c r="U9" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>16.600000000000001</v>
       </c>
       <c r="V9" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="W9" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>60</v>
       </c>
       <c r="X9" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>69.899999999999991</v>
       </c>
       <c r="Y9" s="2">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v>83.4</v>
       </c>
       <c r="Z9" s="2">
-        <f t="shared" ref="Z9:AJ9" si="9">SUM(Z6:Z8)</f>
-        <v>105.858</v>
+        <f t="shared" ref="Z9:AJ9" si="13">SUM(Z6:Z8)</f>
+        <v>120.55000000000001</v>
       </c>
       <c r="AA9" s="2">
-        <f t="shared" si="9"/>
-        <v>121.34443999999998</v>
+        <f t="shared" si="13"/>
+        <v>140.23461630000003</v>
       </c>
       <c r="AB9" s="2">
-        <f t="shared" si="9"/>
-        <v>131.67896159999998</v>
+        <f t="shared" si="13"/>
+        <v>154.06856716800002</v>
       </c>
       <c r="AC9" s="2">
-        <f t="shared" si="9"/>
-        <v>140.33108346</v>
+        <f t="shared" si="13"/>
+        <v>162.90442499883002</v>
       </c>
       <c r="AD9" s="2">
-        <f t="shared" si="9"/>
-        <v>147.20026454999999</v>
+        <f t="shared" si="13"/>
+        <v>170.83902014875983</v>
       </c>
       <c r="AE9" s="2">
-        <f t="shared" si="9"/>
-        <v>153.2215321875</v>
+        <f t="shared" si="13"/>
+        <v>177.47705549569784</v>
       </c>
       <c r="AF9" s="2">
-        <f t="shared" si="9"/>
-        <v>159.24043695842101</v>
+        <f t="shared" si="13"/>
+        <v>183.11033178638576</v>
       </c>
       <c r="AG9" s="2">
-        <f t="shared" si="9"/>
-        <v>165.23419311426576</v>
+        <f t="shared" si="13"/>
+        <v>187.5989854777159</v>
       </c>
       <c r="AH9" s="2">
-        <f t="shared" si="9"/>
-        <v>171.18616850443505</v>
+        <f t="shared" si="13"/>
+        <v>191.35096518727022</v>
       </c>
       <c r="AI9" s="2">
-        <f t="shared" si="9"/>
-        <v>177.38954797880191</v>
+        <f t="shared" si="13"/>
+        <v>195.17798449101565</v>
       </c>
       <c r="AJ9" s="2">
-        <f t="shared" si="9"/>
-        <v>183.85597784787001</v>
+        <f t="shared" si="13"/>
+        <v>199.08154418083595</v>
       </c>
     </row>
     <row r="10" spans="2:36" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="7" t="s">
         <v>17</v>
       </c>
+      <c r="H10" s="8">
+        <f t="shared" ref="H10:P10" si="14">H5-H9</f>
+        <v>7</v>
+      </c>
+      <c r="I10" s="8">
+        <f t="shared" si="14"/>
+        <v>5.5</v>
+      </c>
       <c r="J10" s="8">
-        <f>J5-J9</f>
+        <f t="shared" si="14"/>
         <v>7.6000000000000014</v>
       </c>
       <c r="K10" s="8">
-        <f>K5-K9</f>
+        <f t="shared" si="14"/>
         <v>7.8999999999999986</v>
       </c>
+      <c r="L10" s="8">
+        <f t="shared" si="14"/>
+        <v>9.1000000000000014</v>
+      </c>
+      <c r="M10" s="8">
+        <f t="shared" si="14"/>
+        <v>10.000000000000004</v>
+      </c>
       <c r="N10" s="8">
-        <f>N5-N9</f>
+        <f t="shared" si="14"/>
         <v>9.2999999999999936</v>
       </c>
       <c r="O10" s="8">
-        <f>O5-O9</f>
+        <f t="shared" si="14"/>
         <v>10.3</v>
       </c>
+      <c r="P10" s="8">
+        <f t="shared" si="14"/>
+        <v>7</v>
+      </c>
+      <c r="Q10" s="8">
+        <f t="shared" ref="Q10" si="15">Q5-Q9</f>
+        <v>9.3044900000000084</v>
+      </c>
+      <c r="R10" s="8">
+        <f t="shared" ref="R10" si="16">R5-R9</f>
+        <v>10.527700000000003</v>
+      </c>
       <c r="T10" s="8">
-        <f t="shared" ref="T10:Y10" si="10">T5-T9</f>
+        <f t="shared" ref="T10:Y10" si="17">T5-T9</f>
         <v>1.6999999999999993</v>
       </c>
       <c r="U10" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>11.399999999999999</v>
       </c>
       <c r="V10" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>11.299999999999997</v>
       </c>
       <c r="W10" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>13.5</v>
       </c>
       <c r="X10" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>29.700000000000017</v>
       </c>
       <c r="Y10" s="8">
-        <f t="shared" si="10"/>
+        <f t="shared" si="17"/>
         <v>36.299999999999997</v>
       </c>
       <c r="Z10" s="8">
-        <f t="shared" ref="Z10:AJ10" si="11">Z5-Z9</f>
-        <v>53.941999999999979</v>
+        <f t="shared" ref="Z10:AJ10" si="18">Z5-Z9</f>
+        <v>37.132190000000008</v>
       </c>
       <c r="AA10" s="8">
-        <f t="shared" si="11"/>
-        <v>65.621560000000002</v>
+        <f t="shared" si="18"/>
+        <v>45.39292709999998</v>
       </c>
       <c r="AB10" s="8">
-        <f t="shared" si="11"/>
-        <v>72.113978400000008</v>
+        <f t="shared" si="18"/>
+        <v>48.265455137999993</v>
       </c>
       <c r="AC10" s="8">
-        <f t="shared" si="11"/>
-        <v>77.727362339999985</v>
+        <f t="shared" si="18"/>
+        <v>53.592978868589995</v>
       </c>
       <c r="AD10" s="8">
-        <f t="shared" si="11"/>
-        <v>83.94168799800002</v>
+        <f t="shared" si="18"/>
+        <v>58.648227950705405</v>
       </c>
       <c r="AE10" s="8">
-        <f t="shared" si="11"/>
-        <v>89.477517987900001</v>
+        <f t="shared" si="18"/>
+        <v>63.484555008740671</v>
       </c>
       <c r="AF10" s="8">
-        <f t="shared" si="11"/>
-        <v>95.593565725749045</v>
+        <f t="shared" si="18"/>
+        <v>67.489743138230295</v>
       </c>
       <c r="AG10" s="8">
-        <f t="shared" si="11"/>
-        <v>102.34150970411284</v>
+        <f t="shared" si="18"/>
+        <v>70.519091694638604</v>
       </c>
       <c r="AH10" s="8">
-        <f t="shared" si="11"/>
-        <v>109.76831945486248</v>
+        <f t="shared" si="18"/>
+        <v>71.929473528531389</v>
       </c>
       <c r="AI10" s="8">
-        <f t="shared" si="11"/>
-        <v>117.61266437846049</v>
+        <f t="shared" si="18"/>
+        <v>73.368062999101994</v>
       </c>
       <c r="AJ10" s="8">
-        <f t="shared" si="11"/>
-        <v>125.89634512725553</v>
+        <f t="shared" si="18"/>
+        <v>74.835424259084022</v>
       </c>
     </row>
     <row r="11" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>19</v>
       </c>
+      <c r="H11" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0.6</v>
+      </c>
       <c r="J11" s="2">
         <v>-0.5</v>
       </c>
       <c r="K11" s="2">
         <v>0</v>
       </c>
+      <c r="L11" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="M11" s="2">
+        <v>0.4</v>
+      </c>
       <c r="N11" s="2">
         <v>-0.6</v>
       </c>
       <c r="O11" s="2">
         <v>0</v>
       </c>
+      <c r="P11" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>0</v>
+      </c>
+      <c r="R11" s="2">
+        <v>0</v>
+      </c>
       <c r="T11" s="2">
         <v>0.3</v>
       </c>
@@ -1617,66 +1878,87 @@
         <v>0.5</v>
       </c>
       <c r="Z11" s="2">
-        <f>Y11*1.05</f>
-        <v>0.52500000000000002</v>
+        <f t="shared" ref="Z11:Z14" si="19">SUM(O11:R11)</f>
+        <v>0.1</v>
       </c>
       <c r="AA11" s="2">
-        <f t="shared" ref="AA11:AJ11" si="12">Z11*1.05</f>
-        <v>0.55125000000000002</v>
+        <f t="shared" ref="AA11:AJ11" si="20">Z11*1.05</f>
+        <v>0.10500000000000001</v>
       </c>
       <c r="AB11" s="2">
-        <f t="shared" si="12"/>
-        <v>0.57881250000000006</v>
+        <f t="shared" si="20"/>
+        <v>0.11025000000000001</v>
       </c>
       <c r="AC11" s="2">
-        <f t="shared" si="12"/>
-        <v>0.60775312500000012</v>
+        <f t="shared" si="20"/>
+        <v>0.11576250000000002</v>
       </c>
       <c r="AD11" s="2">
-        <f t="shared" si="12"/>
-        <v>0.63814078125000018</v>
+        <f t="shared" si="20"/>
+        <v>0.12155062500000002</v>
       </c>
       <c r="AE11" s="2">
-        <f t="shared" si="12"/>
-        <v>0.67004782031250021</v>
+        <f t="shared" si="20"/>
+        <v>0.12762815625000004</v>
       </c>
       <c r="AF11" s="2">
-        <f t="shared" si="12"/>
-        <v>0.70355021132812523</v>
+        <f t="shared" si="20"/>
+        <v>0.13400956406250006</v>
       </c>
       <c r="AG11" s="2">
-        <f t="shared" si="12"/>
-        <v>0.73872772189453151</v>
+        <f t="shared" si="20"/>
+        <v>0.14071004226562506</v>
       </c>
       <c r="AH11" s="2">
-        <f t="shared" si="12"/>
-        <v>0.77566410798925811</v>
+        <f t="shared" si="20"/>
+        <v>0.14774554437890633</v>
       </c>
       <c r="AI11" s="2">
-        <f t="shared" si="12"/>
-        <v>0.81444731338872101</v>
+        <f t="shared" si="20"/>
+        <v>0.15513282159785166</v>
       </c>
       <c r="AJ11" s="2">
-        <f t="shared" si="12"/>
-        <v>0.85516967905815711</v>
+        <f t="shared" si="20"/>
+        <v>0.16288946267774426</v>
       </c>
     </row>
     <row r="12" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>20</v>
       </c>
+      <c r="H12" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="I12" s="2">
+        <v>0</v>
+      </c>
       <c r="J12" s="2">
         <v>0</v>
       </c>
       <c r="K12" s="2">
         <v>-0.1</v>
       </c>
+      <c r="L12" s="2">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0</v>
+      </c>
       <c r="N12" s="2">
         <v>0</v>
       </c>
       <c r="O12" s="2">
         <v>0.3</v>
       </c>
+      <c r="P12" s="2">
+        <v>21.2</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>0</v>
+      </c>
+      <c r="R12" s="2">
+        <v>0</v>
+      </c>
       <c r="T12" s="2">
         <v>0.1</v>
       </c>
@@ -1696,7 +1978,8 @@
         <v>0</v>
       </c>
       <c r="Z12" s="2">
-        <v>0</v>
+        <f t="shared" si="19"/>
+        <v>21.5</v>
       </c>
       <c r="AA12" s="2">
         <v>0</v>
@@ -1733,18 +2016,39 @@
       <c r="B13" t="s">
         <v>21</v>
       </c>
+      <c r="H13" s="2">
+        <v>-0.6</v>
+      </c>
+      <c r="I13" s="2">
+        <v>-1</v>
+      </c>
       <c r="J13" s="2">
         <v>-0.6</v>
       </c>
       <c r="K13" s="2">
         <v>-0.9</v>
       </c>
+      <c r="L13" s="2">
+        <v>-0.2</v>
+      </c>
+      <c r="M13" s="2">
+        <v>-0.6</v>
+      </c>
       <c r="N13" s="2">
         <v>-0.1</v>
       </c>
       <c r="O13" s="2">
         <v>-3.9</v>
       </c>
+      <c r="P13" s="2">
+        <v>-4.4000000000000004</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>-4</v>
+      </c>
+      <c r="R13" s="2">
+        <v>-4</v>
+      </c>
       <c r="T13" s="2">
         <v>-0.1</v>
       </c>
@@ -1764,66 +2068,87 @@
         <v>-1.6</v>
       </c>
       <c r="Z13" s="2">
-        <f>Y13*1.03</f>
-        <v>-1.6480000000000001</v>
+        <f t="shared" si="19"/>
+        <v>-16.3</v>
       </c>
       <c r="AA13" s="2">
-        <f t="shared" ref="AA13:AJ13" si="13">Z13*1.03</f>
-        <v>-1.6974400000000003</v>
+        <f t="shared" ref="AA13:AJ13" si="21">Z13*1.03</f>
+        <v>-16.789000000000001</v>
       </c>
       <c r="AB13" s="2">
-        <f t="shared" si="13"/>
-        <v>-1.7483632000000002</v>
+        <f t="shared" si="21"/>
+        <v>-17.292670000000001</v>
       </c>
       <c r="AC13" s="2">
-        <f t="shared" si="13"/>
-        <v>-1.8008140960000003</v>
+        <f t="shared" si="21"/>
+        <v>-17.811450100000002</v>
       </c>
       <c r="AD13" s="2">
-        <f t="shared" si="13"/>
-        <v>-1.8548385188800003</v>
+        <f t="shared" si="21"/>
+        <v>-18.345793603000001</v>
       </c>
       <c r="AE13" s="2">
-        <f t="shared" si="13"/>
-        <v>-1.9104836744464004</v>
+        <f t="shared" si="21"/>
+        <v>-18.896167411090001</v>
       </c>
       <c r="AF13" s="2">
-        <f t="shared" si="13"/>
-        <v>-1.9677981846797925</v>
+        <f t="shared" si="21"/>
+        <v>-19.463052433422703</v>
       </c>
       <c r="AG13" s="2">
-        <f t="shared" si="13"/>
-        <v>-2.0268321302201864</v>
+        <f t="shared" si="21"/>
+        <v>-20.046944006425385</v>
       </c>
       <c r="AH13" s="2">
-        <f t="shared" si="13"/>
-        <v>-2.0876370941267921</v>
+        <f t="shared" si="21"/>
+        <v>-20.648352326618145</v>
       </c>
       <c r="AI13" s="2">
-        <f t="shared" si="13"/>
-        <v>-2.150266206950596</v>
+        <f t="shared" si="21"/>
+        <v>-21.26780289641669</v>
       </c>
       <c r="AJ13" s="2">
-        <f t="shared" si="13"/>
-        <v>-2.2147741931591138</v>
+        <f t="shared" si="21"/>
+        <v>-21.905836983309189</v>
       </c>
     </row>
     <row r="14" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>22</v>
       </c>
+      <c r="H14" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="I14" s="2">
+        <v>0.4</v>
+      </c>
       <c r="J14" s="2">
         <v>2.6</v>
       </c>
       <c r="K14" s="2">
         <v>0.5</v>
       </c>
+      <c r="L14" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="M14" s="2">
+        <v>1.1000000000000001</v>
+      </c>
       <c r="N14" s="2">
         <v>0.9</v>
       </c>
       <c r="O14" s="2">
         <v>3</v>
       </c>
+      <c r="P14" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>2</v>
+      </c>
+      <c r="R14" s="2">
+        <v>2</v>
+      </c>
       <c r="T14" s="2">
         <v>2.5</v>
       </c>
@@ -1843,244 +2168,321 @@
         <v>3.1</v>
       </c>
       <c r="Z14" s="2">
-        <f>Y14*1.03</f>
-        <v>3.1930000000000001</v>
+        <f t="shared" si="19"/>
+        <v>9.3000000000000007</v>
       </c>
       <c r="AA14" s="2">
-        <f t="shared" ref="AA14:AJ14" si="14">Z14*1.03</f>
-        <v>3.2887900000000001</v>
+        <f t="shared" ref="AA14:AJ14" si="22">Z14*1.03</f>
+        <v>9.5790000000000006</v>
       </c>
       <c r="AB14" s="2">
-        <f t="shared" si="14"/>
-        <v>3.3874537</v>
+        <f t="shared" si="22"/>
+        <v>9.8663700000000016</v>
       </c>
       <c r="AC14" s="2">
-        <f t="shared" si="14"/>
-        <v>3.489077311</v>
+        <f t="shared" si="22"/>
+        <v>10.162361100000002</v>
       </c>
       <c r="AD14" s="2">
-        <f t="shared" si="14"/>
-        <v>3.5937496303300001</v>
+        <f t="shared" si="22"/>
+        <v>10.467231933000003</v>
       </c>
       <c r="AE14" s="2">
-        <f t="shared" si="14"/>
-        <v>3.7015621192399002</v>
+        <f t="shared" si="22"/>
+        <v>10.781248890990003</v>
       </c>
       <c r="AF14" s="2">
-        <f t="shared" si="14"/>
-        <v>3.8126089828170975</v>
+        <f t="shared" si="22"/>
+        <v>11.104686357719704</v>
       </c>
       <c r="AG14" s="2">
-        <f t="shared" si="14"/>
-        <v>3.9269872523016107</v>
+        <f t="shared" si="22"/>
+        <v>11.437826948451296</v>
       </c>
       <c r="AH14" s="2">
-        <f t="shared" si="14"/>
-        <v>4.0447968698706589</v>
+        <f t="shared" si="22"/>
+        <v>11.780961756904835</v>
       </c>
       <c r="AI14" s="2">
-        <f t="shared" si="14"/>
-        <v>4.1661407759667783</v>
+        <f t="shared" si="22"/>
+        <v>12.13439060961198</v>
       </c>
       <c r="AJ14" s="2">
-        <f t="shared" si="14"/>
-        <v>4.2911249992457821</v>
+        <f t="shared" si="22"/>
+        <v>12.498422327900339</v>
       </c>
     </row>
     <row r="15" spans="2:36" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>23</v>
       </c>
+      <c r="H15" s="2">
+        <f t="shared" ref="H15:P15" si="23">SUM(H11:H14)</f>
+        <v>6</v>
+      </c>
+      <c r="I15" s="2">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
       <c r="J15" s="2">
-        <f>SUM(J11:J14)</f>
+        <f t="shared" si="23"/>
         <v>1.5</v>
       </c>
       <c r="K15" s="2">
-        <f>SUM(K11:K14)</f>
+        <f t="shared" si="23"/>
         <v>-0.5</v>
       </c>
+      <c r="L15" s="2">
+        <f t="shared" si="23"/>
+        <v>1.4</v>
+      </c>
+      <c r="M15" s="2">
+        <f t="shared" si="23"/>
+        <v>0.90000000000000013</v>
+      </c>
       <c r="N15" s="2">
-        <f>SUM(N11:N14)</f>
+        <f t="shared" si="23"/>
         <v>0.20000000000000007</v>
       </c>
       <c r="O15" s="2">
-        <f>SUM(O11:O14)</f>
+        <f t="shared" si="23"/>
         <v>-0.60000000000000009</v>
       </c>
+      <c r="P15" s="2">
+        <f t="shared" si="23"/>
+        <v>19.2</v>
+      </c>
+      <c r="Q15" s="2">
+        <f t="shared" ref="Q15" si="24">SUM(Q11:Q14)</f>
+        <v>-2</v>
+      </c>
+      <c r="R15" s="2">
+        <f t="shared" ref="R15" si="25">SUM(R11:R14)</f>
+        <v>-2</v>
+      </c>
       <c r="T15" s="2">
-        <f t="shared" ref="T15:Y15" si="15">SUM(T11:T14)</f>
+        <f t="shared" ref="T15:Y15" si="26">SUM(T11:T14)</f>
         <v>2.8</v>
       </c>
       <c r="U15" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="26"/>
         <v>0.70000000000000018</v>
       </c>
       <c r="V15" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="26"/>
         <v>-0.90000000000000013</v>
       </c>
       <c r="W15" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="26"/>
         <v>10.700000000000003</v>
       </c>
       <c r="X15" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="26"/>
         <v>9.5</v>
       </c>
       <c r="Y15" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="26"/>
         <v>2</v>
       </c>
       <c r="Z15" s="2">
-        <f t="shared" ref="Z15:AJ15" si="16">SUM(Z11:Z14)</f>
-        <v>2.0699999999999998</v>
+        <f t="shared" ref="Z15:AJ15" si="27">SUM(Z11:Z14)</f>
+        <v>14.600000000000001</v>
       </c>
       <c r="AA15" s="2">
-        <f t="shared" si="16"/>
-        <v>2.1425999999999998</v>
+        <f t="shared" si="27"/>
+        <v>-7.1050000000000004</v>
       </c>
       <c r="AB15" s="2">
-        <f t="shared" si="16"/>
-        <v>2.2179029999999997</v>
+        <f t="shared" si="27"/>
+        <v>-7.3160499999999988</v>
       </c>
       <c r="AC15" s="2">
-        <f t="shared" si="16"/>
-        <v>2.2960163399999995</v>
+        <f t="shared" si="27"/>
+        <v>-7.5333265000000011</v>
       </c>
       <c r="AD15" s="2">
-        <f t="shared" si="16"/>
-        <v>2.3770518926999999</v>
+        <f t="shared" si="27"/>
+        <v>-7.7570110449999969</v>
       </c>
       <c r="AE15" s="2">
-        <f t="shared" si="16"/>
-        <v>2.461126265106</v>
+        <f t="shared" si="27"/>
+        <v>-7.987290363849997</v>
       </c>
       <c r="AF15" s="2">
-        <f t="shared" si="16"/>
-        <v>2.5483610094654301</v>
+        <f t="shared" si="27"/>
+        <v>-8.2243565116405009</v>
       </c>
       <c r="AG15" s="2">
-        <f t="shared" si="16"/>
-        <v>2.638882843975956</v>
+        <f t="shared" si="27"/>
+        <v>-8.4684070157084648</v>
       </c>
       <c r="AH15" s="2">
-        <f t="shared" si="16"/>
-        <v>2.7328238837331247</v>
+        <f t="shared" si="27"/>
+        <v>-8.7196450253344029</v>
       </c>
       <c r="AI15" s="2">
-        <f t="shared" si="16"/>
-        <v>2.8303218824049035</v>
+        <f t="shared" si="27"/>
+        <v>-8.9782794652068567</v>
       </c>
       <c r="AJ15" s="2">
-        <f t="shared" si="16"/>
-        <v>2.9315204851448255</v>
+        <f t="shared" si="27"/>
+        <v>-9.244525192731107</v>
       </c>
     </row>
     <row r="16" spans="2:36" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B16" s="7" t="s">
         <v>24</v>
       </c>
+      <c r="H16" s="8">
+        <f t="shared" ref="H16:P16" si="28">H10-H15</f>
+        <v>1</v>
+      </c>
+      <c r="I16" s="8">
+        <f t="shared" si="28"/>
+        <v>5.5</v>
+      </c>
       <c r="J16" s="8">
-        <f>J10-J15</f>
+        <f t="shared" si="28"/>
         <v>6.1000000000000014</v>
       </c>
       <c r="K16" s="8">
-        <f>K10-K15</f>
+        <f t="shared" si="28"/>
         <v>8.3999999999999986</v>
       </c>
+      <c r="L16" s="8">
+        <f t="shared" si="28"/>
+        <v>7.7000000000000011</v>
+      </c>
+      <c r="M16" s="8">
+        <f t="shared" si="28"/>
+        <v>9.1000000000000032</v>
+      </c>
       <c r="N16" s="8">
-        <f>N10-N15</f>
+        <f t="shared" si="28"/>
         <v>9.0999999999999943</v>
       </c>
       <c r="O16" s="8">
-        <f>O10-O15</f>
+        <f t="shared" si="28"/>
         <v>10.9</v>
       </c>
+      <c r="P16" s="8">
+        <f t="shared" si="28"/>
+        <v>-12.2</v>
+      </c>
+      <c r="Q16" s="8">
+        <f t="shared" ref="Q16" si="29">Q10-Q15</f>
+        <v>11.304490000000008</v>
+      </c>
+      <c r="R16" s="8">
+        <f t="shared" ref="R16" si="30">R10-R15</f>
+        <v>12.527700000000003</v>
+      </c>
       <c r="T16" s="8">
-        <f t="shared" ref="T16:Y16" si="17">T10-T15</f>
+        <f t="shared" ref="T16:Y16" si="31">T10-T15</f>
         <v>-1.1000000000000005</v>
       </c>
       <c r="U16" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="31"/>
         <v>10.7</v>
       </c>
       <c r="V16" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="31"/>
         <v>12.199999999999998</v>
       </c>
       <c r="W16" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="31"/>
         <v>2.7999999999999972</v>
       </c>
       <c r="X16" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="31"/>
         <v>20.200000000000017</v>
       </c>
       <c r="Y16" s="8">
-        <f t="shared" si="17"/>
+        <f t="shared" si="31"/>
         <v>34.299999999999997</v>
       </c>
       <c r="Z16" s="8">
-        <f t="shared" ref="Z16:AJ16" si="18">Z10-Z15</f>
-        <v>51.871999999999979</v>
+        <f t="shared" ref="Z16:AJ16" si="32">Z10-Z15</f>
+        <v>22.532190000000007</v>
       </c>
       <c r="AA16" s="8">
-        <f t="shared" si="18"/>
-        <v>63.478960000000001</v>
+        <f t="shared" si="32"/>
+        <v>52.497927099999984</v>
       </c>
       <c r="AB16" s="8">
-        <f t="shared" si="18"/>
-        <v>69.896075400000001</v>
+        <f t="shared" si="32"/>
+        <v>55.58150513799999</v>
       </c>
       <c r="AC16" s="8">
-        <f t="shared" si="18"/>
-        <v>75.431345999999991</v>
+        <f t="shared" si="32"/>
+        <v>61.126305368589996</v>
       </c>
       <c r="AD16" s="8">
-        <f t="shared" si="18"/>
-        <v>81.564636105300025</v>
+        <f t="shared" si="32"/>
+        <v>66.405238995705403</v>
       </c>
       <c r="AE16" s="8">
-        <f t="shared" si="18"/>
-        <v>87.016391722793998</v>
+        <f t="shared" si="32"/>
+        <v>71.471845372590664</v>
       </c>
       <c r="AF16" s="8">
-        <f t="shared" si="18"/>
-        <v>93.045204716283621</v>
+        <f t="shared" si="32"/>
+        <v>75.714099649870803</v>
       </c>
       <c r="AG16" s="8">
-        <f t="shared" si="18"/>
-        <v>99.702626860136888</v>
+        <f t="shared" si="32"/>
+        <v>78.987498710347069</v>
       </c>
       <c r="AH16" s="8">
-        <f t="shared" si="18"/>
-        <v>107.03549557112936</v>
+        <f t="shared" si="32"/>
+        <v>80.64911855386579</v>
       </c>
       <c r="AI16" s="8">
-        <f t="shared" si="18"/>
-        <v>114.78234249605559</v>
+        <f t="shared" si="32"/>
+        <v>82.346342464308847</v>
       </c>
       <c r="AJ16" s="8">
-        <f t="shared" si="18"/>
-        <v>122.9648246421107</v>
+        <f t="shared" si="32"/>
+        <v>84.079949451815125</v>
       </c>
     </row>
     <row r="17" spans="2:142" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>25</v>
       </c>
+      <c r="H17" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="I17" s="2">
+        <v>0.3</v>
+      </c>
       <c r="J17" s="2">
         <v>-0.2</v>
       </c>
       <c r="K17" s="2">
         <v>1.1000000000000001</v>
       </c>
+      <c r="L17" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="M17" s="2">
+        <v>0.6</v>
+      </c>
       <c r="N17" s="2">
         <v>1.1000000000000001</v>
       </c>
       <c r="O17" s="2">
         <v>-0.3</v>
       </c>
+      <c r="P17" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>0</v>
+      </c>
+      <c r="R17" s="2">
+        <v>0</v>
+      </c>
       <c r="T17" s="2">
         <v>0.9</v>
       </c>
@@ -2100,571 +2502,611 @@
         <v>3.5</v>
       </c>
       <c r="Z17" s="2">
-        <f>Z16*0.15</f>
-        <v>7.7807999999999966</v>
+        <f>SUM(O17:R17)</f>
+        <v>0.89999999999999991</v>
       </c>
       <c r="AA17" s="2">
-        <f t="shared" ref="AA17:AJ17" si="19">AA16*0.15</f>
-        <v>9.5218439999999998</v>
+        <f t="shared" ref="AA17:AJ17" si="33">AA16*0.15</f>
+        <v>7.8746890649999974</v>
       </c>
       <c r="AB17" s="2">
-        <f t="shared" si="19"/>
-        <v>10.48441131</v>
+        <f t="shared" si="33"/>
+        <v>8.3372257706999982</v>
       </c>
       <c r="AC17" s="2">
-        <f t="shared" si="19"/>
-        <v>11.314701899999998</v>
+        <f t="shared" si="33"/>
+        <v>9.1689458052884998</v>
       </c>
       <c r="AD17" s="2">
-        <f t="shared" si="19"/>
-        <v>12.234695415795004</v>
+        <f t="shared" si="33"/>
+        <v>9.9607858493558101</v>
       </c>
       <c r="AE17" s="2">
-        <f t="shared" si="19"/>
-        <v>13.0524587584191</v>
+        <f t="shared" si="33"/>
+        <v>10.720776805888599</v>
       </c>
       <c r="AF17" s="2">
-        <f t="shared" si="19"/>
-        <v>13.956780707442542</v>
+        <f t="shared" si="33"/>
+        <v>11.357114947480619</v>
       </c>
       <c r="AG17" s="2">
-        <f t="shared" si="19"/>
-        <v>14.955394029020532</v>
+        <f t="shared" si="33"/>
+        <v>11.848124806552059</v>
       </c>
       <c r="AH17" s="2">
-        <f t="shared" si="19"/>
-        <v>16.055324335669404</v>
+        <f t="shared" si="33"/>
+        <v>12.097367783079868</v>
       </c>
       <c r="AI17" s="2">
-        <f t="shared" si="19"/>
-        <v>17.217351374408338</v>
+        <f t="shared" si="33"/>
+        <v>12.351951369646327</v>
       </c>
       <c r="AJ17" s="2">
-        <f t="shared" si="19"/>
-        <v>18.444723696316604</v>
+        <f t="shared" si="33"/>
+        <v>12.611992417772269</v>
       </c>
     </row>
     <row r="18" spans="2:142" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B18" s="7" t="s">
         <v>26</v>
       </c>
+      <c r="H18" s="8">
+        <f t="shared" ref="H18:P18" si="34">H16-H17</f>
+        <v>0.4</v>
+      </c>
+      <c r="I18" s="8">
+        <f t="shared" si="34"/>
+        <v>5.2</v>
+      </c>
       <c r="J18" s="8">
-        <f>J16-J17</f>
+        <f t="shared" si="34"/>
         <v>6.3000000000000016</v>
       </c>
       <c r="K18" s="8">
-        <f>K16-K17</f>
+        <f t="shared" si="34"/>
         <v>7.2999999999999989</v>
       </c>
+      <c r="L18" s="8">
+        <f t="shared" si="34"/>
+        <v>7.0000000000000009</v>
+      </c>
+      <c r="M18" s="8">
+        <f t="shared" si="34"/>
+        <v>8.5000000000000036</v>
+      </c>
       <c r="N18" s="8">
-        <f>N16-N17</f>
+        <f t="shared" si="34"/>
         <v>7.9999999999999947</v>
       </c>
       <c r="O18" s="8">
-        <f>O16-O17</f>
+        <f t="shared" si="34"/>
         <v>11.200000000000001</v>
       </c>
+      <c r="P18" s="8">
+        <f t="shared" si="34"/>
+        <v>-13.399999999999999</v>
+      </c>
+      <c r="Q18" s="8">
+        <f t="shared" ref="Q18" si="35">Q16-Q17</f>
+        <v>11.304490000000008</v>
+      </c>
+      <c r="R18" s="8">
+        <f t="shared" ref="R18" si="36">R16-R17</f>
+        <v>12.527700000000003</v>
+      </c>
       <c r="T18" s="8">
-        <f t="shared" ref="T18:Y18" si="20">T16-T17</f>
+        <f t="shared" ref="T18:Y18" si="37">T16-T17</f>
         <v>-2.0000000000000004</v>
       </c>
       <c r="U18" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="37"/>
         <v>15</v>
       </c>
       <c r="V18" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="37"/>
         <v>12.499999999999998</v>
       </c>
       <c r="W18" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="37"/>
         <v>2.2999999999999972</v>
       </c>
       <c r="X18" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="37"/>
         <v>18.300000000000018</v>
       </c>
       <c r="Y18" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="37"/>
         <v>30.799999999999997</v>
       </c>
       <c r="Z18" s="8">
-        <f t="shared" ref="Z18" si="21">Z16-Z17</f>
-        <v>44.091199999999979</v>
+        <f t="shared" ref="Z18" si="38">Z16-Z17</f>
+        <v>21.632190000000008</v>
       </c>
       <c r="AA18" s="8">
-        <f t="shared" ref="AA18" si="22">AA16-AA17</f>
-        <v>53.957115999999999</v>
+        <f t="shared" ref="AA18" si="39">AA16-AA17</f>
+        <v>44.623238034999986</v>
       </c>
       <c r="AB18" s="8">
-        <f t="shared" ref="AB18" si="23">AB16-AB17</f>
-        <v>59.411664090000002</v>
+        <f t="shared" ref="AB18" si="40">AB16-AB17</f>
+        <v>47.244279367299995</v>
       </c>
       <c r="AC18" s="8">
-        <f t="shared" ref="AC18" si="24">AC16-AC17</f>
-        <v>64.116644099999988</v>
+        <f t="shared" ref="AC18" si="41">AC16-AC17</f>
+        <v>51.957359563301495</v>
       </c>
       <c r="AD18" s="8">
-        <f t="shared" ref="AD18" si="25">AD16-AD17</f>
-        <v>69.329940689505023</v>
+        <f t="shared" ref="AD18" si="42">AD16-AD17</f>
+        <v>56.444453146349595</v>
       </c>
       <c r="AE18" s="8">
-        <f t="shared" ref="AE18" si="26">AE16-AE17</f>
-        <v>73.963932964374891</v>
+        <f t="shared" ref="AE18" si="43">AE16-AE17</f>
+        <v>60.751068566702067</v>
       </c>
       <c r="AF18" s="8">
-        <f t="shared" ref="AF18" si="27">AF16-AF17</f>
-        <v>79.088424008841073</v>
+        <f t="shared" ref="AF18" si="44">AF16-AF17</f>
+        <v>64.356984702390179</v>
       </c>
       <c r="AG18" s="8">
-        <f t="shared" ref="AG18" si="28">AG16-AG17</f>
-        <v>84.747232831116349</v>
+        <f t="shared" ref="AG18" si="45">AG16-AG17</f>
+        <v>67.139373903795004</v>
       </c>
       <c r="AH18" s="8">
-        <f t="shared" ref="AH18" si="29">AH16-AH17</f>
-        <v>90.980171235459949</v>
+        <f t="shared" ref="AH18" si="46">AH16-AH17</f>
+        <v>68.551750770785929</v>
       </c>
       <c r="AI18" s="8">
-        <f t="shared" ref="AI18" si="30">AI16-AI17</f>
-        <v>97.564991121647253</v>
+        <f t="shared" ref="AI18" si="47">AI16-AI17</f>
+        <v>69.994391094662518</v>
       </c>
       <c r="AJ18" s="8">
-        <f t="shared" ref="AJ18" si="31">AJ16-AJ17</f>
-        <v>104.5201009457941</v>
+        <f t="shared" ref="AJ18" si="48">AJ16-AJ17</f>
+        <v>71.467957034042854</v>
       </c>
       <c r="AK18" s="7">
         <f>AJ18*(1+$AM$24)</f>
-        <v>103.47489993633616</v>
+        <v>70.753277463702432</v>
       </c>
       <c r="AL18" s="7">
-        <f t="shared" ref="AL18:CW18" si="32">AK18*(1+$AM$24)</f>
-        <v>102.4401509369728</v>
+        <f t="shared" ref="AL18:CW18" si="49">AK18*(1+$AM$24)</f>
+        <v>70.045744689065401</v>
       </c>
       <c r="AM18" s="7">
-        <f t="shared" si="32"/>
-        <v>101.41574942760307</v>
+        <f t="shared" si="49"/>
+        <v>69.345287242174749</v>
       </c>
       <c r="AN18" s="7">
-        <f t="shared" si="32"/>
-        <v>100.40159193332704</v>
+        <f t="shared" si="49"/>
+        <v>68.651834369753004</v>
       </c>
       <c r="AO18" s="7">
-        <f t="shared" si="32"/>
-        <v>99.397576013993771</v>
+        <f t="shared" si="49"/>
+        <v>67.965316026055476</v>
       </c>
       <c r="AP18" s="7">
-        <f t="shared" si="32"/>
-        <v>98.403600253853838</v>
+        <f t="shared" si="49"/>
+        <v>67.285662865794919</v>
       </c>
       <c r="AQ18" s="7">
-        <f t="shared" si="32"/>
-        <v>97.419564251315293</v>
+        <f t="shared" si="49"/>
+        <v>66.612806237136965</v>
       </c>
       <c r="AR18" s="7">
-        <f t="shared" si="32"/>
-        <v>96.445368608802141</v>
+        <f t="shared" si="49"/>
+        <v>65.946678174765594</v>
       </c>
       <c r="AS18" s="7">
-        <f t="shared" si="32"/>
-        <v>95.480914922714121</v>
+        <f t="shared" si="49"/>
+        <v>65.287211393017941</v>
       </c>
       <c r="AT18" s="7">
-        <f t="shared" si="32"/>
-        <v>94.526105773486975</v>
+        <f t="shared" si="49"/>
+        <v>64.634339279087754</v>
       </c>
       <c r="AU18" s="7">
-        <f t="shared" si="32"/>
-        <v>93.580844715752107</v>
+        <f t="shared" si="49"/>
+        <v>63.987995886296879</v>
       </c>
       <c r="AV18" s="7">
-        <f t="shared" si="32"/>
-        <v>92.645036268594581</v>
+        <f t="shared" si="49"/>
+        <v>63.348115927433909</v>
       </c>
       <c r="AW18" s="7">
-        <f t="shared" si="32"/>
-        <v>91.71858590590864</v>
+        <f t="shared" si="49"/>
+        <v>62.71463476815957</v>
       </c>
       <c r="AX18" s="7">
-        <f t="shared" si="32"/>
-        <v>90.801400046849551</v>
+        <f t="shared" si="49"/>
+        <v>62.087488420477975</v>
       </c>
       <c r="AY18" s="7">
-        <f t="shared" si="32"/>
-        <v>89.893386046381053</v>
+        <f t="shared" si="49"/>
+        <v>61.466613536273194</v>
       </c>
       <c r="AZ18" s="7">
-        <f t="shared" si="32"/>
-        <v>88.99445218591724</v>
+        <f t="shared" si="49"/>
+        <v>60.851947400910461</v>
       </c>
       <c r="BA18" s="7">
-        <f t="shared" si="32"/>
-        <v>88.104507664058062</v>
+        <f t="shared" si="49"/>
+        <v>60.243427926901354</v>
       </c>
       <c r="BB18" s="7">
-        <f t="shared" si="32"/>
-        <v>87.223462587417487</v>
+        <f t="shared" si="49"/>
+        <v>59.640993647632342</v>
       </c>
       <c r="BC18" s="7">
-        <f t="shared" si="32"/>
-        <v>86.351227961543316</v>
+        <f t="shared" si="49"/>
+        <v>59.044583711156015</v>
       </c>
       <c r="BD18" s="7">
-        <f t="shared" si="32"/>
-        <v>85.487715681927881</v>
+        <f t="shared" si="49"/>
+        <v>58.454137874044456</v>
       </c>
       <c r="BE18" s="7">
-        <f t="shared" si="32"/>
-        <v>84.632838525108596</v>
+        <f t="shared" si="49"/>
+        <v>57.869596495304009</v>
       </c>
       <c r="BF18" s="7">
-        <f t="shared" si="32"/>
-        <v>83.786510139857512</v>
+        <f t="shared" si="49"/>
+        <v>57.290900530350967</v>
       </c>
       <c r="BG18" s="7">
-        <f t="shared" si="32"/>
-        <v>82.948645038458935</v>
+        <f t="shared" si="49"/>
+        <v>56.717991525047459</v>
       </c>
       <c r="BH18" s="7">
-        <f t="shared" si="32"/>
-        <v>82.119158588074342</v>
+        <f t="shared" si="49"/>
+        <v>56.150811609796982</v>
       </c>
       <c r="BI18" s="7">
-        <f t="shared" si="32"/>
-        <v>81.297967002193602</v>
+        <f t="shared" si="49"/>
+        <v>55.589303493699013</v>
       </c>
       <c r="BJ18" s="7">
-        <f t="shared" si="32"/>
-        <v>80.48498733217167</v>
+        <f t="shared" si="49"/>
+        <v>55.03341045876202</v>
       </c>
       <c r="BK18" s="7">
-        <f t="shared" si="32"/>
-        <v>79.680137458849956</v>
+        <f t="shared" si="49"/>
+        <v>54.483076354174401</v>
       </c>
       <c r="BL18" s="7">
-        <f t="shared" si="32"/>
-        <v>78.883336084261458</v>
+        <f t="shared" si="49"/>
+        <v>53.938245590632654</v>
       </c>
       <c r="BM18" s="7">
-        <f t="shared" si="32"/>
-        <v>78.094502723418842</v>
+        <f t="shared" si="49"/>
+        <v>53.398863134726327</v>
       </c>
       <c r="BN18" s="7">
-        <f t="shared" si="32"/>
-        <v>77.31355769618466</v>
+        <f t="shared" si="49"/>
+        <v>52.864874503379063</v>
       </c>
       <c r="BO18" s="7">
-        <f t="shared" si="32"/>
-        <v>76.540422119222811</v>
+        <f t="shared" si="49"/>
+        <v>52.336225758345272</v>
       </c>
       <c r="BP18" s="7">
-        <f t="shared" si="32"/>
-        <v>75.775017898030583</v>
+        <f t="shared" si="49"/>
+        <v>51.812863500761821</v>
       </c>
       <c r="BQ18" s="7">
-        <f t="shared" si="32"/>
-        <v>75.017267719050281</v>
+        <f t="shared" si="49"/>
+        <v>51.294734865754201</v>
       </c>
       <c r="BR18" s="7">
-        <f t="shared" si="32"/>
-        <v>74.267095041859776</v>
+        <f t="shared" si="49"/>
+        <v>50.78178751709666</v>
       </c>
       <c r="BS18" s="7">
-        <f t="shared" si="32"/>
-        <v>73.524424091441176</v>
+        <f t="shared" si="49"/>
+        <v>50.273969641925696</v>
       </c>
       <c r="BT18" s="7">
-        <f t="shared" si="32"/>
-        <v>72.789179850526764</v>
+        <f t="shared" si="49"/>
+        <v>49.771229945506441</v>
       </c>
       <c r="BU18" s="7">
-        <f t="shared" si="32"/>
-        <v>72.061288052021496</v>
+        <f t="shared" si="49"/>
+        <v>49.273517646051374</v>
       </c>
       <c r="BV18" s="7">
-        <f t="shared" si="32"/>
-        <v>71.340675171501275</v>
+        <f t="shared" si="49"/>
+        <v>48.780782469590861</v>
       </c>
       <c r="BW18" s="7">
-        <f t="shared" si="32"/>
-        <v>70.627268419786262</v>
+        <f t="shared" si="49"/>
+        <v>48.292974644894954</v>
       </c>
       <c r="BX18" s="7">
-        <f t="shared" si="32"/>
-        <v>69.920995735588392</v>
+        <f t="shared" si="49"/>
+        <v>47.810044898446002</v>
       </c>
       <c r="BY18" s="7">
-        <f t="shared" si="32"/>
-        <v>69.221785778232501</v>
+        <f t="shared" si="49"/>
+        <v>47.331944449461538</v>
       </c>
       <c r="BZ18" s="7">
-        <f t="shared" si="32"/>
-        <v>68.529567920450177</v>
+        <f t="shared" si="49"/>
+        <v>46.858625004966925</v>
       </c>
       <c r="CA18" s="7">
-        <f t="shared" si="32"/>
-        <v>67.844272241245676</v>
+        <f t="shared" si="49"/>
+        <v>46.390038754917256</v>
       </c>
       <c r="CB18" s="7">
-        <f t="shared" si="32"/>
-        <v>67.16582951883322</v>
+        <f t="shared" si="49"/>
+        <v>45.926138367368083</v>
       </c>
       <c r="CC18" s="7">
-        <f t="shared" si="32"/>
-        <v>66.494171223644884</v>
+        <f t="shared" si="49"/>
+        <v>45.466876983694398</v>
       </c>
       <c r="CD18" s="7">
-        <f t="shared" si="32"/>
-        <v>65.829229511408428</v>
+        <f t="shared" si="49"/>
+        <v>45.012208213857456</v>
       </c>
       <c r="CE18" s="7">
-        <f t="shared" si="32"/>
-        <v>65.170937216294348</v>
+        <f t="shared" si="49"/>
+        <v>44.562086131718878</v>
       </c>
       <c r="CF18" s="7">
-        <f t="shared" si="32"/>
-        <v>64.519227844131407</v>
+        <f t="shared" si="49"/>
+        <v>44.11646527040169</v>
       </c>
       <c r="CG18" s="7">
-        <f t="shared" si="32"/>
-        <v>63.874035565690093</v>
+        <f t="shared" si="49"/>
+        <v>43.675300617697673</v>
       </c>
       <c r="CH18" s="7">
-        <f t="shared" si="32"/>
-        <v>63.235295210033193</v>
+        <f t="shared" si="49"/>
+        <v>43.238547611520694</v>
       </c>
       <c r="CI18" s="7">
-        <f t="shared" si="32"/>
-        <v>62.60294225793286</v>
+        <f t="shared" si="49"/>
+        <v>42.806162135405486</v>
       </c>
       <c r="CJ18" s="7">
-        <f t="shared" si="32"/>
-        <v>61.976912835353531</v>
+        <f t="shared" si="49"/>
+        <v>42.378100514051432</v>
       </c>
       <c r="CK18" s="7">
-        <f t="shared" si="32"/>
-        <v>61.357143706999992</v>
+        <f t="shared" si="49"/>
+        <v>41.95431950891092</v>
       </c>
       <c r="CL18" s="7">
-        <f t="shared" si="32"/>
-        <v>60.743572269929992</v>
+        <f t="shared" si="49"/>
+        <v>41.534776313821808</v>
       </c>
       <c r="CM18" s="7">
-        <f t="shared" si="32"/>
-        <v>60.136136547230691</v>
+        <f t="shared" si="49"/>
+        <v>41.119428550683587</v>
       </c>
       <c r="CN18" s="7">
-        <f t="shared" si="32"/>
-        <v>59.534775181758384</v>
+        <f t="shared" si="49"/>
+        <v>40.708234265176749</v>
       </c>
       <c r="CO18" s="7">
-        <f t="shared" si="32"/>
-        <v>58.9394274299408</v>
+        <f t="shared" si="49"/>
+        <v>40.30115192252498</v>
       </c>
       <c r="CP18" s="7">
-        <f t="shared" si="32"/>
-        <v>58.350033155641391</v>
+        <f t="shared" si="49"/>
+        <v>39.898140403299728</v>
       </c>
       <c r="CQ18" s="7">
-        <f t="shared" si="32"/>
-        <v>57.766532824084976</v>
+        <f t="shared" si="49"/>
+        <v>39.499158999266733</v>
       </c>
       <c r="CR18" s="7">
-        <f t="shared" si="32"/>
-        <v>57.188867495844129</v>
+        <f t="shared" si="49"/>
+        <v>39.104167409274062</v>
       </c>
       <c r="CS18" s="7">
-        <f t="shared" si="32"/>
-        <v>56.616978820885684</v>
+        <f t="shared" si="49"/>
+        <v>38.713125735181322</v>
       </c>
       <c r="CT18" s="7">
-        <f t="shared" si="32"/>
-        <v>56.050809032676824</v>
+        <f t="shared" si="49"/>
+        <v>38.325994477829511</v>
       </c>
       <c r="CU18" s="7">
-        <f t="shared" si="32"/>
-        <v>55.490300942350054</v>
+        <f t="shared" si="49"/>
+        <v>37.942734533051215</v>
       </c>
       <c r="CV18" s="7">
-        <f t="shared" si="32"/>
-        <v>54.935397932926556</v>
+        <f t="shared" si="49"/>
+        <v>37.563307187720703</v>
       </c>
       <c r="CW18" s="7">
-        <f t="shared" si="32"/>
-        <v>54.386043953597287</v>
+        <f t="shared" si="49"/>
+        <v>37.187674115843492</v>
       </c>
       <c r="CX18" s="7">
-        <f t="shared" ref="CX18:EL18" si="33">CW18*(1+$AM$24)</f>
-        <v>53.842183514061311</v>
+        <f t="shared" ref="CX18:EL18" si="50">CW18*(1+$AM$24)</f>
+        <v>36.815797374685054</v>
       </c>
       <c r="CY18" s="7">
-        <f t="shared" si="33"/>
-        <v>53.303761678920701</v>
+        <f t="shared" si="50"/>
+        <v>36.447639400938201</v>
       </c>
       <c r="CZ18" s="7">
-        <f t="shared" si="33"/>
-        <v>52.770724062131492</v>
+        <f t="shared" si="50"/>
+        <v>36.083163006928821</v>
       </c>
       <c r="DA18" s="7">
-        <f t="shared" si="33"/>
-        <v>52.243016821510174</v>
+        <f t="shared" si="50"/>
+        <v>35.722331376859529</v>
       </c>
       <c r="DB18" s="7">
-        <f t="shared" si="33"/>
-        <v>51.720586653295072</v>
+        <f t="shared" si="50"/>
+        <v>35.365108063090936</v>
       </c>
       <c r="DC18" s="7">
-        <f t="shared" si="33"/>
-        <v>51.203380786762118</v>
+        <f t="shared" si="50"/>
+        <v>35.011456982460025</v>
       </c>
       <c r="DD18" s="7">
-        <f t="shared" si="33"/>
-        <v>50.691346978894494</v>
+        <f t="shared" si="50"/>
+        <v>34.661342412635427</v>
       </c>
       <c r="DE18" s="7">
-        <f t="shared" si="33"/>
-        <v>50.184433509105546</v>
+        <f t="shared" si="50"/>
+        <v>34.314728988509074</v>
       </c>
       <c r="DF18" s="7">
-        <f t="shared" si="33"/>
-        <v>49.682589174014488</v>
+        <f t="shared" si="50"/>
+        <v>33.971581698623986</v>
       </c>
       <c r="DG18" s="7">
-        <f t="shared" si="33"/>
-        <v>49.185763282274344</v>
+        <f t="shared" si="50"/>
+        <v>33.631865881637744</v>
       </c>
       <c r="DH18" s="7">
-        <f t="shared" si="33"/>
-        <v>48.693905649451601</v>
+        <f t="shared" si="50"/>
+        <v>33.295547222821369</v>
       </c>
       <c r="DI18" s="7">
-        <f t="shared" si="33"/>
-        <v>48.206966592957087</v>
+        <f t="shared" si="50"/>
+        <v>32.962591750593155</v>
       </c>
       <c r="DJ18" s="7">
-        <f t="shared" si="33"/>
-        <v>47.724896927027515</v>
+        <f t="shared" si="50"/>
+        <v>32.632965833087226</v>
       </c>
       <c r="DK18" s="7">
-        <f t="shared" si="33"/>
-        <v>47.247647957757238</v>
+        <f t="shared" si="50"/>
+        <v>32.306636174756356</v>
       </c>
       <c r="DL18" s="7">
-        <f t="shared" si="33"/>
-        <v>46.775171478179665</v>
+        <f t="shared" si="50"/>
+        <v>31.983569813008792</v>
       </c>
       <c r="DM18" s="7">
-        <f t="shared" si="33"/>
-        <v>46.307419763397867</v>
+        <f t="shared" si="50"/>
+        <v>31.663734114878704</v>
       </c>
       <c r="DN18" s="7">
-        <f t="shared" si="33"/>
-        <v>45.844345565763888</v>
+        <f t="shared" si="50"/>
+        <v>31.347096773729916</v>
       </c>
       <c r="DO18" s="7">
-        <f t="shared" si="33"/>
-        <v>45.385902110106251</v>
+        <f t="shared" si="50"/>
+        <v>31.033625805992617</v>
       </c>
       <c r="DP18" s="7">
-        <f t="shared" si="33"/>
-        <v>44.932043089005191</v>
+        <f t="shared" si="50"/>
+        <v>30.723289547932691</v>
       </c>
       <c r="DQ18" s="7">
-        <f t="shared" si="33"/>
-        <v>44.482722658115136</v>
+        <f t="shared" si="50"/>
+        <v>30.416056652453364</v>
       </c>
       <c r="DR18" s="7">
-        <f t="shared" si="33"/>
-        <v>44.037895431533983</v>
+        <f t="shared" si="50"/>
+        <v>30.11189608592883</v>
       </c>
       <c r="DS18" s="7">
-        <f t="shared" si="33"/>
-        <v>43.59751647721864</v>
+        <f t="shared" si="50"/>
+        <v>29.810777125069542</v>
       </c>
       <c r="DT18" s="7">
-        <f t="shared" si="33"/>
-        <v>43.161541312446452</v>
+        <f t="shared" si="50"/>
+        <v>29.512669353818847</v>
       </c>
       <c r="DU18" s="7">
-        <f t="shared" si="33"/>
-        <v>42.729925899321991</v>
+        <f t="shared" si="50"/>
+        <v>29.217542660280657</v>
       </c>
       <c r="DV18" s="7">
-        <f t="shared" si="33"/>
-        <v>42.302626640328768</v>
+        <f t="shared" si="50"/>
+        <v>28.92536723367785</v>
       </c>
       <c r="DW18" s="7">
-        <f t="shared" si="33"/>
-        <v>41.879600373925477</v>
+        <f t="shared" si="50"/>
+        <v>28.63611356134107</v>
       </c>
       <c r="DX18" s="7">
-        <f t="shared" si="33"/>
-        <v>41.460804370186224</v>
+        <f t="shared" si="50"/>
+        <v>28.349752425727658</v>
       </c>
       <c r="DY18" s="7">
-        <f t="shared" si="33"/>
-        <v>41.046196326484363</v>
+        <f t="shared" si="50"/>
+        <v>28.06625490147038</v>
       </c>
       <c r="DZ18" s="7">
-        <f t="shared" si="33"/>
-        <v>40.63573436321952</v>
+        <f t="shared" si="50"/>
+        <v>27.785592352455676</v>
       </c>
       <c r="EA18" s="7">
-        <f t="shared" si="33"/>
-        <v>40.229377019587325</v>
+        <f t="shared" si="50"/>
+        <v>27.507736428931121</v>
       </c>
       <c r="EB18" s="7">
-        <f t="shared" si="33"/>
-        <v>39.82708324939145</v>
+        <f t="shared" si="50"/>
+        <v>27.232659064641808</v>
       </c>
       <c r="EC18" s="7">
-        <f t="shared" si="33"/>
-        <v>39.428812416897536</v>
+        <f t="shared" si="50"/>
+        <v>26.96033247399539</v>
       </c>
       <c r="ED18" s="7">
-        <f t="shared" si="33"/>
-        <v>39.034524292728563</v>
+        <f t="shared" si="50"/>
+        <v>26.690729149255436</v>
       </c>
       <c r="EE18" s="7">
-        <f t="shared" si="33"/>
-        <v>38.644179049801274</v>
+        <f t="shared" si="50"/>
+        <v>26.423821857762881</v>
       </c>
       <c r="EF18" s="7">
-        <f t="shared" si="33"/>
-        <v>38.257737259303262</v>
+        <f t="shared" si="50"/>
+        <v>26.159583639185254</v>
       </c>
       <c r="EG18" s="7">
-        <f t="shared" si="33"/>
-        <v>37.875159886710229</v>
+        <f t="shared" si="50"/>
+        <v>25.897987802793402</v>
       </c>
       <c r="EH18" s="7">
-        <f t="shared" si="33"/>
-        <v>37.496408287843124</v>
+        <f t="shared" si="50"/>
+        <v>25.639007924765469</v>
       </c>
       <c r="EI18" s="7">
-        <f t="shared" si="33"/>
-        <v>37.121444204964689</v>
+        <f t="shared" si="50"/>
+        <v>25.382617845517814</v>
       </c>
       <c r="EJ18" s="7">
-        <f t="shared" si="33"/>
-        <v>36.750229762915041</v>
+        <f t="shared" si="50"/>
+        <v>25.128791667062636</v>
       </c>
       <c r="EK18" s="7">
-        <f t="shared" si="33"/>
-        <v>36.382727465285889</v>
+        <f t="shared" si="50"/>
+        <v>24.877503750392009</v>
       </c>
       <c r="EL18" s="7">
-        <f t="shared" si="33"/>
-        <v>36.018900190633033</v>
+        <f t="shared" si="50"/>
+        <v>24.628728712888087</v>
       </c>
     </row>
     <row r="19" spans="2:142" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>2</v>
       </c>
+      <c r="H19" s="2">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="I19" s="2">
+        <v>34.799999999999997</v>
+      </c>
       <c r="J19" s="2">
         <v>34.799999999999997</v>
       </c>
       <c r="K19" s="2">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="L19" s="2">
+        <v>34.799999999999997</v>
+      </c>
+      <c r="M19" s="2">
         <v>34.799999999999997</v>
       </c>
       <c r="N19" s="2">
@@ -2674,6 +3116,18 @@
         <f>35.6</f>
         <v>35.6</v>
       </c>
+      <c r="P19" s="2">
+        <f>35.7</f>
+        <v>35.700000000000003</v>
+      </c>
+      <c r="Q19" s="2">
+        <f t="shared" ref="Q19:R19" si="51">35.7</f>
+        <v>35.700000000000003</v>
+      </c>
+      <c r="R19" s="2">
+        <f t="shared" si="51"/>
+        <v>35.700000000000003</v>
+      </c>
       <c r="T19" s="2">
         <v>34.799999999999997</v>
       </c>
@@ -2693,133 +3147,183 @@
         <v>34.799999999999997</v>
       </c>
       <c r="Z19" s="2">
-        <v>34.799999999999997</v>
+        <f t="shared" ref="Z19:AJ19" si="52">35.7</f>
+        <v>35.700000000000003</v>
       </c>
       <c r="AA19" s="2">
-        <v>34.799999999999997</v>
+        <f t="shared" si="52"/>
+        <v>35.700000000000003</v>
       </c>
       <c r="AB19" s="2">
-        <v>34.799999999999997</v>
+        <f t="shared" si="52"/>
+        <v>35.700000000000003</v>
       </c>
       <c r="AC19" s="2">
-        <v>34.799999999999997</v>
+        <f t="shared" si="52"/>
+        <v>35.700000000000003</v>
       </c>
       <c r="AD19" s="2">
-        <v>34.799999999999997</v>
+        <f t="shared" si="52"/>
+        <v>35.700000000000003</v>
       </c>
       <c r="AE19" s="2">
-        <v>34.799999999999997</v>
+        <f t="shared" si="52"/>
+        <v>35.700000000000003</v>
       </c>
       <c r="AF19" s="2">
-        <v>34.799999999999997</v>
+        <f t="shared" si="52"/>
+        <v>35.700000000000003</v>
       </c>
       <c r="AG19" s="2">
-        <v>34.799999999999997</v>
+        <f t="shared" si="52"/>
+        <v>35.700000000000003</v>
       </c>
       <c r="AH19" s="2">
-        <v>34.799999999999997</v>
+        <f t="shared" si="52"/>
+        <v>35.700000000000003</v>
       </c>
       <c r="AI19" s="2">
-        <v>34.799999999999997</v>
+        <f t="shared" si="52"/>
+        <v>35.700000000000003</v>
       </c>
       <c r="AJ19" s="2">
-        <v>34.799999999999997</v>
+        <f t="shared" si="52"/>
+        <v>35.700000000000003</v>
       </c>
     </row>
     <row r="20" spans="2:142" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>27</v>
       </c>
+      <c r="H20" s="6">
+        <f t="shared" ref="H20:P20" si="53">H18/H19</f>
+        <v>1.149425287356322E-2</v>
+      </c>
+      <c r="I20" s="6">
+        <f t="shared" si="53"/>
+        <v>0.14942528735632185</v>
+      </c>
       <c r="J20" s="6">
-        <f>J18/J19</f>
+        <f t="shared" si="53"/>
         <v>0.18103448275862075</v>
       </c>
       <c r="K20" s="6">
-        <f>K18/K19</f>
+        <f t="shared" si="53"/>
         <v>0.20977011494252873</v>
       </c>
+      <c r="L20" s="6">
+        <f t="shared" si="53"/>
+        <v>0.20114942528735635</v>
+      </c>
+      <c r="M20" s="6">
+        <f t="shared" si="53"/>
+        <v>0.24425287356321851</v>
+      </c>
       <c r="N20" s="6">
-        <f>N18/N19</f>
+        <f t="shared" si="53"/>
         <v>0.22988505747126423</v>
       </c>
       <c r="O20" s="6">
-        <f>O18/O19</f>
+        <f t="shared" si="53"/>
         <v>0.3146067415730337</v>
       </c>
+      <c r="P20" s="6">
+        <f t="shared" si="53"/>
+        <v>-0.37535014005602235</v>
+      </c>
+      <c r="Q20" s="6">
+        <f t="shared" ref="Q20" si="54">Q18/Q19</f>
+        <v>0.31665238095238118</v>
+      </c>
+      <c r="R20" s="6">
+        <f t="shared" ref="R20" si="55">R18/R19</f>
+        <v>0.3509159663865547</v>
+      </c>
       <c r="T20" s="6">
-        <f t="shared" ref="T20:Y20" si="34">T18/T19</f>
+        <f t="shared" ref="T20:Y20" si="56">T18/T19</f>
         <v>-5.7471264367816112E-2</v>
       </c>
       <c r="U20" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>0.43103448275862072</v>
       </c>
       <c r="V20" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>0.35919540229885055</v>
       </c>
       <c r="W20" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>6.6091954022988425E-2</v>
       </c>
       <c r="X20" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>0.52586206896551779</v>
       </c>
       <c r="Y20" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="56"/>
         <v>0.88505747126436785</v>
       </c>
       <c r="Z20" s="6">
-        <f t="shared" ref="Z20" si="35">Z18/Z19</f>
-        <v>1.266988505747126</v>
+        <f t="shared" ref="Z20" si="57">Z18/Z19</f>
+        <v>0.60594369747899179</v>
       </c>
       <c r="AA20" s="6">
-        <f t="shared" ref="AA20" si="36">AA18/AA19</f>
-        <v>1.5504918390804598</v>
+        <f t="shared" ref="AA20" si="58">AA18/AA19</f>
+        <v>1.2499506452380948</v>
       </c>
       <c r="AB20" s="6">
-        <f t="shared" ref="AB20" si="37">AB18/AB19</f>
-        <v>1.7072317267241381</v>
+        <f t="shared" ref="AB20" si="59">AB18/AB19</f>
+        <v>1.3233691699523806</v>
       </c>
       <c r="AC20" s="6">
-        <f t="shared" ref="AC20" si="38">AC18/AC19</f>
-        <v>1.8424323017241377</v>
+        <f t="shared" ref="AC20" si="60">AC18/AC19</f>
+        <v>1.4553882230616664</v>
       </c>
       <c r="AD20" s="6">
-        <f t="shared" ref="AD20" si="39">AD18/AD19</f>
-        <v>1.9922396749857767</v>
+        <f t="shared" ref="AD20" si="61">AD18/AD19</f>
+        <v>1.5810771189453667</v>
       </c>
       <c r="AE20" s="6">
-        <f t="shared" ref="AE20" si="40">AE18/AE19</f>
-        <v>2.1254003725395085</v>
+        <f t="shared" ref="AE20" si="62">AE18/AE19</f>
+        <v>1.7017106041093015</v>
       </c>
       <c r="AF20" s="6">
-        <f t="shared" ref="AF20" si="41">AF18/AF19</f>
-        <v>2.2726558623230195</v>
+        <f t="shared" ref="AF20" si="63">AF18/AF19</f>
+        <v>1.802716658330257</v>
       </c>
       <c r="AG20" s="6">
-        <f t="shared" ref="AG20" si="42">AG18/AG19</f>
-        <v>2.4352653112389757</v>
+        <f t="shared" ref="AG20" si="64">AG18/AG19</f>
+        <v>1.8806547311987394</v>
       </c>
       <c r="AH20" s="6">
-        <f t="shared" ref="AH20" si="43">AH18/AH19</f>
-        <v>2.614372736651148</v>
+        <f t="shared" ref="AH20" si="65">AH18/AH19</f>
+        <v>1.9202171084253761</v>
       </c>
       <c r="AI20" s="6">
-        <f t="shared" ref="AI20" si="44">AI18/AI19</f>
-        <v>2.8035916988979097</v>
+        <f t="shared" ref="AI20" si="66">AI18/AI19</f>
+        <v>1.9606272015311628</v>
       </c>
       <c r="AJ20" s="6">
-        <f t="shared" ref="AJ20" si="45">AJ18/AJ19</f>
-        <v>3.0034511766032788</v>
+        <f t="shared" ref="AJ20" si="67">AJ18/AJ19</f>
+        <v>2.0019035583765503</v>
       </c>
     </row>
     <row r="22" spans="2:142" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>44</v>
       </c>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
       <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9">
+        <f t="shared" ref="L22:M22" si="68">L3/H3-1</f>
+        <v>0.17307692307692313</v>
+      </c>
+      <c r="M22" s="9">
+        <f t="shared" si="68"/>
+        <v>0.36595744680851072</v>
+      </c>
       <c r="N22" s="9">
         <f>N3/J3-1</f>
         <v>8.6153846153846025E-2</v>
@@ -2827,6 +3331,18 @@
       <c r="O22" s="9">
         <f>O3/K3-1</f>
         <v>0.3904109589041096</v>
+      </c>
+      <c r="P22" s="9">
+        <f>P3/L3-1</f>
+        <v>0.29836065573770498</v>
+      </c>
+      <c r="Q22" s="9">
+        <f t="shared" ref="Q22:R22" si="69">Q3/M3-1</f>
+        <v>0.33000000000000007</v>
+      </c>
+      <c r="R22" s="9">
+        <f t="shared" si="69"/>
+        <v>0.30000000000000004</v>
       </c>
       <c r="T22" s="9"/>
       <c r="U22" s="9">
@@ -2834,73 +3350,93 @@
         <v>0.45077720207253891</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" ref="V22:Y22" si="46">V3/U3-1</f>
+        <f t="shared" ref="V22:Y22" si="70">V3/U3-1</f>
         <v>0.51071428571428568</v>
       </c>
       <c r="W22" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="70"/>
         <v>0.8085106382978724</v>
       </c>
       <c r="X22" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="70"/>
         <v>0.42091503267973862</v>
       </c>
       <c r="Y22" s="9">
-        <f t="shared" si="46"/>
+        <f t="shared" si="70"/>
         <v>0.170193192272309</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" ref="Z22:AJ22" si="47">Z3/Y3-1</f>
-        <v>0.33647798742138368</v>
+        <f t="shared" ref="Z22:AJ22" si="71">Z3/Y3-1</f>
+        <v>0.32691037735849071</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="71"/>
         <v>0.16999999999999993</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="71"/>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="71"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="71"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="71"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" si="47"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="71"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AG22" s="9">
-        <f t="shared" si="47"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="71"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AH22" s="9">
-        <f t="shared" si="47"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="71"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI22" s="9">
-        <f t="shared" si="47"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="71"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ22" s="9">
-        <f t="shared" si="47"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="71"/>
+        <v>2.0000000000000018E-2</v>
       </c>
     </row>
     <row r="23" spans="2:142" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>45</v>
       </c>
+      <c r="H23" s="9">
+        <f t="shared" ref="H23:M23" si="72">H5/H3</f>
+        <v>0.9653846153846154</v>
+      </c>
+      <c r="I23" s="9">
+        <f t="shared" si="72"/>
+        <v>0.91063829787234041</v>
+      </c>
       <c r="J23" s="9">
-        <f>J5/J3</f>
+        <f t="shared" si="72"/>
         <v>0.84307692307692306</v>
+      </c>
+      <c r="K23" s="9">
+        <f t="shared" si="72"/>
+        <v>0.92465753424657537</v>
+      </c>
+      <c r="L23" s="9">
+        <f t="shared" si="72"/>
+        <v>0.95409836065573772</v>
+      </c>
+      <c r="M23" s="9">
+        <f t="shared" si="72"/>
+        <v>0.9470404984423676</v>
       </c>
       <c r="N23" s="9">
         <f>N5/N3</f>
@@ -2910,82 +3446,114 @@
         <f>O5/O3</f>
         <v>0.94581280788177335</v>
       </c>
+      <c r="P23" s="9">
+        <f>P5/P3</f>
+        <v>0.93181818181818177</v>
+      </c>
+      <c r="Q23" s="9">
+        <f t="shared" ref="Q23:R23" si="73">Q5/Q3</f>
+        <v>0.93</v>
+      </c>
+      <c r="R23" s="9">
+        <f t="shared" si="73"/>
+        <v>0.93</v>
+      </c>
       <c r="T23" s="9">
-        <f t="shared" ref="T23:Y23" si="48">T5/T3</f>
+        <f t="shared" ref="T23:Y23" si="74">T5/T3</f>
         <v>1</v>
       </c>
       <c r="U23" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="74"/>
         <v>1</v>
       </c>
       <c r="V23" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="74"/>
         <v>1</v>
       </c>
       <c r="W23" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="74"/>
         <v>0.96078431372549022</v>
       </c>
       <c r="X23" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="74"/>
         <v>0.91628334866605343</v>
       </c>
       <c r="Y23" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="74"/>
         <v>0.94103773584905659</v>
       </c>
       <c r="Z23" s="9">
-        <f t="shared" ref="Z23:AJ23" si="49">Z5/Z3</f>
+        <f t="shared" ref="Z23:AJ23" si="75">Z5/Z3</f>
+        <v>0.93423028385560158</v>
+      </c>
+      <c r="AA23" s="9">
+        <f t="shared" si="75"/>
+        <v>0.94000000000000006</v>
+      </c>
+      <c r="AB23" s="9">
+        <f t="shared" si="75"/>
         <v>0.94</v>
       </c>
-      <c r="AA23" s="9">
-        <f t="shared" si="49"/>
-        <v>0.94000000000000006</v>
-      </c>
-      <c r="AB23" s="9">
-        <f t="shared" si="49"/>
+      <c r="AC23" s="9">
+        <f t="shared" si="75"/>
         <v>0.94</v>
       </c>
-      <c r="AC23" s="9">
-        <f t="shared" si="49"/>
+      <c r="AD23" s="9">
+        <f t="shared" si="75"/>
         <v>0.94</v>
       </c>
-      <c r="AD23" s="9">
-        <f t="shared" si="49"/>
+      <c r="AE23" s="9">
+        <f t="shared" si="75"/>
         <v>0.94</v>
       </c>
-      <c r="AE23" s="9">
-        <f t="shared" si="49"/>
+      <c r="AF23" s="9">
+        <f t="shared" si="75"/>
         <v>0.94</v>
       </c>
-      <c r="AF23" s="9">
-        <f t="shared" si="49"/>
+      <c r="AG23" s="9">
+        <f t="shared" si="75"/>
         <v>0.94</v>
       </c>
-      <c r="AG23" s="9">
-        <f t="shared" si="49"/>
+      <c r="AH23" s="9">
+        <f t="shared" si="75"/>
         <v>0.94</v>
       </c>
-      <c r="AH23" s="9">
-        <f t="shared" si="49"/>
+      <c r="AI23" s="9">
+        <f t="shared" si="75"/>
+        <v>0.94</v>
+      </c>
+      <c r="AJ23" s="9">
+        <f t="shared" si="75"/>
         <v>0.93999999999999984</v>
-      </c>
-      <c r="AI23" s="9">
-        <f t="shared" si="49"/>
-        <v>0.94</v>
-      </c>
-      <c r="AJ23" s="9">
-        <f t="shared" si="49"/>
-        <v>0.94</v>
       </c>
     </row>
     <row r="24" spans="2:142" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>46</v>
       </c>
+      <c r="H24" s="9">
+        <f t="shared" ref="H24:M24" si="76">H6/H3</f>
+        <v>0.33461538461538459</v>
+      </c>
+      <c r="I24" s="9">
+        <f t="shared" si="76"/>
+        <v>0.36595744680851061</v>
+      </c>
       <c r="J24" s="9">
-        <f>J6/J3</f>
+        <f t="shared" si="76"/>
         <v>0.29846153846153844</v>
+      </c>
+      <c r="K24" s="9">
+        <f t="shared" si="76"/>
+        <v>0.32876712328767121</v>
+      </c>
+      <c r="L24" s="9">
+        <f t="shared" si="76"/>
+        <v>0.35081967213114751</v>
+      </c>
+      <c r="M24" s="9">
+        <f t="shared" si="76"/>
+        <v>0.3364485981308411</v>
       </c>
       <c r="N24" s="9">
         <f>N6/N3</f>
@@ -2995,72 +3563,84 @@
         <f>O6/O3</f>
         <v>0.37438423645320196</v>
       </c>
+      <c r="P24" s="9">
+        <f>P6/P3</f>
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="Q24" s="9">
+        <f t="shared" ref="Q24:R24" si="77">Q6/Q3</f>
+        <v>0.35134565385426181</v>
+      </c>
+      <c r="R24" s="9">
+        <f t="shared" si="77"/>
+        <v>0.32686859882327302</v>
+      </c>
       <c r="T24" s="9">
-        <f t="shared" ref="T24:Y24" si="50">T6/T3</f>
+        <f t="shared" ref="T24:Y24" si="78">T6/T3</f>
         <v>0.56476683937823835</v>
       </c>
       <c r="U24" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="78"/>
         <v>0.28928571428571426</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="78"/>
         <v>0.33333333333333337</v>
       </c>
       <c r="W24" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="78"/>
         <v>0.44052287581699351</v>
       </c>
       <c r="X24" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="78"/>
         <v>0.32474701011959517</v>
       </c>
       <c r="Y24" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="78"/>
         <v>0.32940251572327039</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" ref="Z24:AJ24" si="51">Z6/Z3</f>
+        <f t="shared" ref="Z24:AJ24" si="79">Z6/Z3</f>
+        <v>0.35904089866870476</v>
+      </c>
+      <c r="AA24" s="9">
+        <f t="shared" si="79"/>
+        <v>0.33</v>
+      </c>
+      <c r="AB24" s="9">
+        <f t="shared" si="79"/>
         <v>0.32</v>
       </c>
-      <c r="AA24" s="9">
-        <f t="shared" si="51"/>
+      <c r="AC24" s="9">
+        <f t="shared" si="79"/>
         <v>0.31</v>
       </c>
-      <c r="AB24" s="9">
-        <f t="shared" si="51"/>
+      <c r="AD24" s="9">
+        <f t="shared" si="79"/>
         <v>0.31</v>
       </c>
-      <c r="AC24" s="9">
-        <f t="shared" si="51"/>
+      <c r="AE24" s="9">
+        <f t="shared" si="79"/>
         <v>0.31</v>
       </c>
-      <c r="AD24" s="9">
-        <f t="shared" si="51"/>
+      <c r="AF24" s="9">
+        <f t="shared" si="79"/>
         <v>0.31</v>
       </c>
-      <c r="AE24" s="9">
-        <f t="shared" si="51"/>
+      <c r="AG24" s="9">
+        <f t="shared" si="79"/>
         <v>0.31</v>
       </c>
-      <c r="AF24" s="9">
-        <f t="shared" si="51"/>
+      <c r="AH24" s="9">
+        <f t="shared" si="79"/>
         <v>0.31</v>
       </c>
-      <c r="AG24" s="9">
-        <f t="shared" si="51"/>
+      <c r="AI24" s="9">
+        <f t="shared" si="79"/>
         <v>0.31</v>
       </c>
-      <c r="AH24" s="9">
-        <f t="shared" si="51"/>
-        <v>0.31</v>
-      </c>
-      <c r="AI24" s="9">
-        <f t="shared" si="51"/>
-        <v>0.31</v>
-      </c>
       <c r="AJ24" s="9">
-        <f t="shared" si="51"/>
+        <f t="shared" si="79"/>
         <v>0.31</v>
       </c>
       <c r="AL24" t="s">
@@ -3074,14 +3654,37 @@
       <c r="B25" t="s">
         <v>47</v>
       </c>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
       <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9">
+        <f t="shared" ref="L25:M25" si="80">L7/H7-1</f>
+        <v>0.24</v>
+      </c>
+      <c r="M25" s="9">
+        <f t="shared" si="80"/>
+        <v>0.43999999999999995</v>
+      </c>
       <c r="N25" s="9">
-        <f>N7/J7-1</f>
+        <f t="shared" ref="N25:P26" si="81">N7/J7-1</f>
         <v>0.25806451612903225</v>
       </c>
       <c r="O25" s="9">
-        <f>O7/K7-1</f>
+        <f t="shared" si="81"/>
         <v>0.625</v>
+      </c>
+      <c r="P25" s="9">
+        <f t="shared" si="81"/>
+        <v>0.96774193548387077</v>
+      </c>
+      <c r="Q25" s="9">
+        <f t="shared" ref="Q25:R25" si="82">Q7/M7-1</f>
+        <v>0.7777777777777779</v>
+      </c>
+      <c r="R25" s="9">
+        <f t="shared" si="82"/>
+        <v>0.74358974358974361</v>
       </c>
       <c r="T25" s="9"/>
       <c r="U25" s="9">
@@ -3089,63 +3692,63 @@
         <v>0</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" ref="V25:Y25" si="52">V7/U7-1</f>
+        <f t="shared" ref="V25:Y25" si="83">V7/U7-1</f>
         <v>0.56000000000000005</v>
       </c>
       <c r="W25" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="83"/>
         <v>0.74358974358974361</v>
       </c>
       <c r="X25" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="83"/>
         <v>0.51470588235294135</v>
       </c>
       <c r="Y25" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="83"/>
         <v>0.34951456310679596</v>
       </c>
       <c r="Z25" s="9">
-        <f t="shared" ref="Z25:AJ25" si="53">Z7/Y7-1</f>
-        <v>0.21999999999999975</v>
+        <f t="shared" ref="Z25:AJ25" si="84">Z7/Y7-1</f>
+        <v>0.7625899280575541</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="53"/>
-        <v>0.17999999999999994</v>
+        <f t="shared" si="84"/>
+        <v>0.39999999999999991</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" si="53"/>
-        <v>0.1399999999999999</v>
+        <f t="shared" si="84"/>
+        <v>0.19999999999999996</v>
       </c>
       <c r="AC25" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="84"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="84"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AE25" s="9">
-        <f t="shared" si="53"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="84"/>
+        <v>4.0000000000000036E-2</v>
       </c>
       <c r="AF25" s="9">
-        <f t="shared" si="53"/>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" si="84"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AG25" s="9">
-        <f t="shared" si="53"/>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" si="84"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH25" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="84"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI25" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="84"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ25" s="9">
-        <f t="shared" si="53"/>
+        <f t="shared" si="84"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL25" t="s">
@@ -3159,78 +3762,101 @@
       <c r="B26" t="s">
         <v>48</v>
       </c>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
       <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9">
+        <f t="shared" ref="L26:M26" si="85">L8/H8-1</f>
+        <v>-0.10144927536231885</v>
+      </c>
+      <c r="M26" s="9">
+        <f t="shared" si="85"/>
+        <v>0.25</v>
+      </c>
       <c r="N26" s="9">
-        <f>N8/J8-1</f>
+        <f t="shared" si="81"/>
         <v>0.28571428571428581</v>
       </c>
       <c r="O26" s="9">
-        <f>O8/K8-1</f>
+        <f t="shared" si="81"/>
         <v>0.22222222222222232</v>
+      </c>
+      <c r="P26" s="9">
+        <f t="shared" si="81"/>
+        <v>0.35483870967741948</v>
+      </c>
+      <c r="Q26" s="9">
+        <f t="shared" ref="Q26:R26" si="86">Q8/M8-1</f>
+        <v>0.5</v>
+      </c>
+      <c r="R26" s="9">
+        <f t="shared" si="86"/>
+        <v>0.14999999999999991</v>
       </c>
       <c r="T26" s="9"/>
       <c r="U26" s="9">
-        <f t="shared" ref="U26:Y26" si="54">U8/T8-1</f>
+        <f t="shared" ref="U26:Y26" si="87">U8/T8-1</f>
         <v>0.4285714285714286</v>
       </c>
       <c r="V26" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="87"/>
         <v>1.1666666666666665</v>
       </c>
       <c r="W26" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="87"/>
         <v>0.5</v>
       </c>
       <c r="X26" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="87"/>
         <v>0.24615384615384617</v>
       </c>
       <c r="Y26" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="87"/>
         <v>0.13580246913580241</v>
       </c>
       <c r="Z26" s="9">
-        <f t="shared" ref="Z26:AJ26" si="55">Z8/Y8-1</f>
-        <v>0.25</v>
+        <f t="shared" ref="Z26:AJ26" si="88">Z8/Y8-1</f>
+        <v>0.28442028985507251</v>
       </c>
       <c r="AA26" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="88"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AB26" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="88"/>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="AC26" s="9">
+        <f t="shared" si="88"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AC26" s="9">
-        <f t="shared" si="55"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
       <c r="AD26" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="88"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AE26" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="88"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF26" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="88"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG26" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="88"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH26" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="88"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI26" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="88"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ26" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="88"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL26" t="s">
@@ -3238,16 +3864,36 @@
       </c>
       <c r="AM26" s="2">
         <f>NPV(AM25,Z18:EL18)</f>
-        <v>701.42605820735139</v>
+        <v>511.78260029003911</v>
       </c>
     </row>
     <row r="27" spans="2:142" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>49</v>
       </c>
+      <c r="H27" s="9">
+        <f t="shared" ref="H27:M27" si="89">H10/H3</f>
+        <v>0.26923076923076922</v>
+      </c>
+      <c r="I27" s="9">
+        <f t="shared" si="89"/>
+        <v>0.23404255319148937</v>
+      </c>
       <c r="J27" s="9">
-        <f>J10/J3</f>
+        <f t="shared" si="89"/>
         <v>0.2338461538461539</v>
+      </c>
+      <c r="K27" s="9">
+        <f t="shared" si="89"/>
+        <v>0.27054794520547942</v>
+      </c>
+      <c r="L27" s="9">
+        <f t="shared" si="89"/>
+        <v>0.29836065573770498</v>
+      </c>
+      <c r="M27" s="9">
+        <f t="shared" si="89"/>
+        <v>0.31152647975077891</v>
       </c>
       <c r="N27" s="9">
         <f>N10/N3</f>
@@ -3257,89 +3903,121 @@
         <f>O10/O3</f>
         <v>0.2536945812807882</v>
       </c>
+      <c r="P27" s="9">
+        <f>P10/P3</f>
+        <v>0.17676767676767677</v>
+      </c>
+      <c r="Q27" s="9">
+        <f t="shared" ref="Q27:R27" si="90">Q10/Q3</f>
+        <v>0.21793947485536289</v>
+      </c>
+      <c r="R27" s="9">
+        <f t="shared" si="90"/>
+        <v>0.22941163652211816</v>
+      </c>
       <c r="T27" s="9">
-        <f t="shared" ref="T27:Y27" si="56">T10/T3</f>
+        <f t="shared" ref="T27:Y27" si="91">T10/T3</f>
         <v>8.8082901554404111E-2</v>
       </c>
       <c r="U27" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="91"/>
         <v>0.40714285714285708</v>
       </c>
       <c r="V27" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="91"/>
         <v>0.26713947990543729</v>
       </c>
       <c r="W27" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="91"/>
         <v>0.17647058823529413</v>
       </c>
       <c r="X27" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="91"/>
         <v>0.27322907083716669</v>
       </c>
       <c r="Y27" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="91"/>
         <v>0.285377358490566</v>
       </c>
       <c r="Z27" s="9">
-        <f t="shared" ref="Z27:AJ27" si="57">Z10/Z3</f>
-        <v>0.31730588235294105</v>
+        <f t="shared" ref="Z27:AJ27" si="92">Z10/Z3</f>
+        <v>0.21999958526628868</v>
       </c>
       <c r="AA27" s="9">
-        <f t="shared" si="57"/>
-        <v>0.32992237305178485</v>
+        <f t="shared" si="92"/>
+        <v>0.2298654105552311</v>
       </c>
       <c r="AB27" s="9">
-        <f t="shared" si="57"/>
-        <v>0.33262751740075003</v>
+        <f t="shared" si="92"/>
+        <v>0.22423084023459661</v>
       </c>
       <c r="AC27" s="9">
-        <f t="shared" si="57"/>
-        <v>0.33506485076305165</v>
+        <f t="shared" si="92"/>
+        <v>0.23269286022166347</v>
       </c>
       <c r="AD27" s="9">
-        <f t="shared" si="57"/>
-        <v>0.34137111782740609</v>
+        <f t="shared" si="92"/>
+        <v>0.24022831216211504</v>
       </c>
       <c r="AE27" s="9">
-        <f t="shared" si="57"/>
-        <v>0.34655622610735409</v>
+        <f t="shared" si="92"/>
+        <v>0.24765555634895214</v>
       </c>
       <c r="AF27" s="9">
-        <f t="shared" si="57"/>
-        <v>0.35261366550667911</v>
+        <f t="shared" si="92"/>
+        <v>0.25315378923577819</v>
       </c>
       <c r="AG27" s="9">
-        <f t="shared" si="57"/>
-        <v>0.35952823110835325</v>
+        <f t="shared" si="92"/>
+        <v>0.25681249031115899</v>
       </c>
       <c r="AH27" s="9">
-        <f t="shared" si="57"/>
-        <v>0.36725599593382879</v>
+        <f t="shared" si="92"/>
+        <v>0.25681249031115905</v>
       </c>
       <c r="AI27" s="9">
-        <f t="shared" si="57"/>
-        <v>0.37476296747857651</v>
+        <f t="shared" si="92"/>
+        <v>0.25681249031115894</v>
       </c>
       <c r="AJ27" s="9">
-        <f t="shared" si="57"/>
-        <v>0.38205545412204583</v>
+        <f t="shared" si="92"/>
+        <v>0.25681249031115894</v>
       </c>
       <c r="AL27" t="s">
         <v>57</v>
       </c>
       <c r="AM27" s="2">
         <f>Main!D8</f>
-        <v>-67</v>
+        <v>-71.5</v>
       </c>
     </row>
     <row r="28" spans="2:142" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
         <v>25</v>
       </c>
+      <c r="H28" s="9">
+        <f t="shared" ref="H28:M28" si="93">H17/H16</f>
+        <v>0.6</v>
+      </c>
+      <c r="I28" s="9">
+        <f t="shared" si="93"/>
+        <v>5.4545454545454543E-2</v>
+      </c>
       <c r="J28" s="9">
-        <f>J17/J16</f>
+        <f t="shared" si="93"/>
         <v>-3.2786885245901634E-2</v>
+      </c>
+      <c r="K28" s="9">
+        <f t="shared" si="93"/>
+        <v>0.13095238095238099</v>
+      </c>
+      <c r="L28" s="9">
+        <f t="shared" si="93"/>
+        <v>9.0909090909090884E-2</v>
+      </c>
+      <c r="M28" s="9">
+        <f t="shared" si="93"/>
+        <v>6.5934065934065908E-2</v>
       </c>
       <c r="N28" s="9">
         <f>N17/N16</f>
@@ -3349,72 +4027,84 @@
         <f>O17/O16</f>
         <v>-2.7522935779816512E-2</v>
       </c>
+      <c r="P28" s="9">
+        <f>P17/P16</f>
+        <v>-9.8360655737704916E-2</v>
+      </c>
+      <c r="Q28" s="9">
+        <f t="shared" ref="Q28:R28" si="94">Q17/Q16</f>
+        <v>0</v>
+      </c>
+      <c r="R28" s="9">
+        <f t="shared" si="94"/>
+        <v>0</v>
+      </c>
       <c r="T28" s="9">
-        <f t="shared" ref="T28:Y28" si="58">T17/T16</f>
+        <f t="shared" ref="T28:Y28" si="95">T17/T16</f>
         <v>-0.81818181818181779</v>
       </c>
       <c r="U28" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="95"/>
         <v>-0.40186915887850466</v>
       </c>
       <c r="V28" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="95"/>
         <v>-2.4590163934426233E-2</v>
       </c>
       <c r="W28" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="95"/>
         <v>0.17857142857142874</v>
       </c>
       <c r="X28" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="95"/>
         <v>9.4059405940593976E-2</v>
       </c>
       <c r="Y28" s="9">
-        <f t="shared" si="58"/>
+        <f t="shared" si="95"/>
         <v>0.10204081632653061</v>
       </c>
       <c r="Z28" s="9">
-        <f t="shared" ref="Z28:AJ28" si="59">Z17/Z16</f>
+        <f t="shared" ref="Z28:AJ28" si="96">Z17/Z16</f>
+        <v>3.9942855088653154E-2</v>
+      </c>
+      <c r="AA28" s="9">
+        <f t="shared" si="96"/>
         <v>0.15</v>
       </c>
-      <c r="AA28" s="9">
-        <f t="shared" si="59"/>
+      <c r="AB28" s="9">
+        <f t="shared" si="96"/>
         <v>0.15</v>
       </c>
-      <c r="AB28" s="9">
-        <f t="shared" si="59"/>
+      <c r="AC28" s="9">
+        <f t="shared" si="96"/>
         <v>0.15</v>
       </c>
-      <c r="AC28" s="9">
-        <f t="shared" si="59"/>
+      <c r="AD28" s="9">
+        <f t="shared" si="96"/>
         <v>0.15</v>
       </c>
-      <c r="AD28" s="9">
-        <f t="shared" si="59"/>
+      <c r="AE28" s="9">
+        <f t="shared" si="96"/>
         <v>0.15</v>
       </c>
-      <c r="AE28" s="9">
-        <f t="shared" si="59"/>
+      <c r="AF28" s="9">
+        <f t="shared" si="96"/>
         <v>0.15</v>
       </c>
-      <c r="AF28" s="9">
-        <f t="shared" si="59"/>
+      <c r="AG28" s="9">
+        <f t="shared" si="96"/>
         <v>0.15</v>
       </c>
-      <c r="AG28" s="9">
-        <f t="shared" si="59"/>
+      <c r="AH28" s="9">
+        <f t="shared" si="96"/>
         <v>0.15</v>
       </c>
-      <c r="AH28" s="9">
-        <f t="shared" si="59"/>
+      <c r="AI28" s="9">
+        <f t="shared" si="96"/>
         <v>0.15</v>
       </c>
-      <c r="AI28" s="9">
-        <f t="shared" si="59"/>
-        <v>0.15</v>
-      </c>
       <c r="AJ28" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="96"/>
         <v>0.15</v>
       </c>
       <c r="AL28" t="s">
@@ -3422,16 +4112,36 @@
       </c>
       <c r="AM28" s="2">
         <f>AM26+AM27</f>
-        <v>634.42605820735139</v>
+        <v>440.28260029003911</v>
       </c>
     </row>
     <row r="29" spans="2:142" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>50</v>
       </c>
+      <c r="H29" s="9">
+        <f t="shared" ref="H29:M29" si="97">H18/H3</f>
+        <v>1.5384615384615385E-2</v>
+      </c>
+      <c r="I29" s="9">
+        <f t="shared" si="97"/>
+        <v>0.22127659574468087</v>
+      </c>
       <c r="J29" s="9">
-        <f>J18/J3</f>
+        <f t="shared" si="97"/>
         <v>0.19384615384615389</v>
+      </c>
+      <c r="K29" s="9">
+        <f t="shared" si="97"/>
+        <v>0.24999999999999997</v>
+      </c>
+      <c r="L29" s="9">
+        <f t="shared" si="97"/>
+        <v>0.22950819672131151</v>
+      </c>
+      <c r="M29" s="9">
+        <f t="shared" si="97"/>
+        <v>0.26479750778816208</v>
       </c>
       <c r="N29" s="9">
         <f>N18/N3</f>
@@ -3441,80 +4151,92 @@
         <f>O18/O3</f>
         <v>0.27586206896551724</v>
       </c>
+      <c r="P29" s="9">
+        <f>P18/P3</f>
+        <v>-0.33838383838383834</v>
+      </c>
+      <c r="Q29" s="9">
+        <f t="shared" ref="Q29:R29" si="98">Q18/Q3</f>
+        <v>0.26478556203593112</v>
+      </c>
+      <c r="R29" s="9">
+        <f t="shared" si="98"/>
+        <v>0.27299411636522125</v>
+      </c>
       <c r="T29" s="9">
-        <f t="shared" ref="T29:Y29" si="60">T18/T3</f>
+        <f t="shared" ref="T29:Y29" si="99">T18/T3</f>
         <v>-0.10362694300518137</v>
       </c>
       <c r="U29" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="99"/>
         <v>0.5357142857142857</v>
       </c>
       <c r="V29" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="99"/>
         <v>0.29550827423167847</v>
       </c>
       <c r="W29" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="99"/>
         <v>3.0065359477124146E-2</v>
       </c>
       <c r="X29" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="99"/>
         <v>0.16835326586936539</v>
       </c>
       <c r="Y29" s="9">
-        <f t="shared" si="60"/>
+        <f t="shared" si="99"/>
         <v>0.24213836477987419</v>
       </c>
       <c r="Z29" s="9">
-        <f t="shared" ref="Z29:AJ29" si="61">Z18/Z3</f>
-        <v>0.25935999999999987</v>
+        <f t="shared" ref="Z29:AJ29" si="100">Z18/Z3</f>
+        <v>0.12816569204244507</v>
       </c>
       <c r="AA29" s="9">
-        <f t="shared" si="61"/>
-        <v>0.27127760683760688</v>
+        <f t="shared" si="100"/>
+        <v>0.22596777926707176</v>
       </c>
       <c r="AB29" s="9">
-        <f t="shared" si="61"/>
-        <v>0.27403777699364856</v>
+        <f t="shared" si="100"/>
+        <v>0.2194866790029957</v>
       </c>
       <c r="AC29" s="9">
-        <f t="shared" si="61"/>
-        <v>0.27639216281160889</v>
+        <f t="shared" si="100"/>
+        <v>0.2255912408973379</v>
       </c>
       <c r="AD29" s="9">
-        <f t="shared" si="61"/>
-        <v>0.28194857545213992</v>
+        <f t="shared" si="100"/>
+        <v>0.23120145627687386</v>
       </c>
       <c r="AE29" s="9">
-        <f t="shared" si="61"/>
-        <v>0.28647041237394821</v>
+        <f t="shared" si="100"/>
+        <v>0.23699212639371053</v>
       </c>
       <c r="AF29" s="9">
-        <f t="shared" si="61"/>
-        <v>0.2917315498922966</v>
+        <f t="shared" si="100"/>
+        <v>0.24140282335687516</v>
       </c>
       <c r="AG29" s="9">
-        <f t="shared" si="61"/>
-        <v>0.2977191053678051</v>
+        <f t="shared" si="100"/>
+        <v>0.24450442278564574</v>
       </c>
       <c r="AH29" s="9">
-        <f t="shared" si="61"/>
-        <v>0.3043957816175622</v>
+        <f t="shared" si="100"/>
+        <v>0.24475288038431578</v>
       </c>
       <c r="AI29" s="9">
-        <f t="shared" si="61"/>
-        <v>0.31088272498540348</v>
+        <f t="shared" si="100"/>
+        <v>0.24500352265063211</v>
       </c>
       <c r="AJ29" s="9">
-        <f t="shared" si="61"/>
-        <v>0.31718533680516181</v>
+        <f t="shared" si="100"/>
+        <v>0.24525636361492983</v>
       </c>
       <c r="AL29" t="s">
         <v>55</v>
       </c>
       <c r="AM29" s="1">
         <f>AM28/AJ19</f>
-        <v>18.230633856533089</v>
+        <v>12.332845946499694</v>
       </c>
     </row>
     <row r="30" spans="2:142" x14ac:dyDescent="0.3">
@@ -3523,7 +4245,7 @@
       </c>
       <c r="AM30" s="1">
         <f>Main!D3</f>
-        <v>12.02</v>
+        <v>8.02</v>
       </c>
     </row>
     <row r="31" spans="2:142" x14ac:dyDescent="0.3">
@@ -3532,7 +4254,7 @@
       </c>
       <c r="AM31" s="10">
         <f>AM29/AM30-1</f>
-        <v>0.51669166859676285</v>
+        <v>0.53776133996255537</v>
       </c>
     </row>
     <row r="32" spans="2:142" x14ac:dyDescent="0.3">
@@ -3547,5 +4269,6 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Financial Analysis/GAMB.xlsx
+++ b/Financial Analysis/GAMB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C5B38E-18EF-4831-BAF9-1615BAF46C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52FE56F7-15C8-45D7-8075-1DCF9D46277C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{D6459E68-7D6A-410F-A9B8-1584227EFFA5}"/>
   </bookViews>
@@ -778,14 +778,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>8.02</v>
+        <v>8.16</v>
       </c>
       <c r="E3" s="4">
-        <v>45910</v>
+        <v>45937</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45910</v>
+        <v>45937</v>
       </c>
       <c r="G3" s="4">
         <v>45974</v>
@@ -809,7 +809,7 @@
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>286.31400000000002</v>
+        <v>291.31200000000001</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -851,7 +851,7 @@
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>357.81400000000002</v>
+        <v>362.81200000000001</v>
       </c>
     </row>
   </sheetData>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="AM30" s="1">
         <f>Main!D3</f>
-        <v>8.02</v>
+        <v>8.16</v>
       </c>
     </row>
     <row r="31" spans="2:142" x14ac:dyDescent="0.3">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AM31" s="10">
         <f>AM29/AM30-1</f>
-        <v>0.53776133996255537</v>
+        <v>0.51137817971809962</v>
       </c>
     </row>
     <row r="32" spans="2:142" x14ac:dyDescent="0.3">

--- a/Financial Analysis/GAMB.xlsx
+++ b/Financial Analysis/GAMB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52FE56F7-15C8-45D7-8075-1DCF9D46277C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F76186-5313-47A5-8373-A0D0D86F13A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{D6459E68-7D6A-410F-A9B8-1584227EFFA5}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="71">
   <si>
     <t>GAMB</t>
   </si>
@@ -243,6 +243,36 @@
   </si>
   <si>
     <t>Heavily undervalued</t>
+  </si>
+  <si>
+    <t>D&amp;A</t>
+  </si>
+  <si>
+    <t>Credit loss</t>
+  </si>
+  <si>
+    <t>SBC</t>
+  </si>
+  <si>
+    <t>Contingent</t>
+  </si>
+  <si>
+    <t>Other consideration</t>
+  </si>
+  <si>
+    <t>T/R</t>
+  </si>
+  <si>
+    <t>T/P</t>
+  </si>
+  <si>
+    <t>CFFO</t>
+  </si>
+  <si>
+    <t>PP&amp;E</t>
+  </si>
+  <si>
+    <t>FCF</t>
   </si>
 </sst>
 </file>
@@ -363,7 +393,7 @@
     <xdr:to>
       <xdr:col>25</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -380,7 +410,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16131540" y="7620"/>
-          <a:ext cx="0" cy="6134100"/>
+          <a:ext cx="0" cy="9060180"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -405,15 +435,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -429,8 +459,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10043160" y="7620"/>
-          <a:ext cx="0" cy="6134100"/>
+          <a:off x="10652760" y="7620"/>
+          <a:ext cx="0" cy="8877300"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -778,14 +808,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>8.16</v>
+        <v>7.73</v>
       </c>
       <c r="E3" s="4">
-        <v>45937</v>
+        <v>45957</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>45957</v>
       </c>
       <c r="G3" s="4">
         <v>45974</v>
@@ -800,7 +830,7 @@
         <v>35.700000000000003</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -809,7 +839,7 @@
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>291.31200000000001</v>
+        <v>275.96100000000001</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -851,7 +881,7 @@
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>362.81200000000001</v>
+        <v>347.46100000000001</v>
       </c>
     </row>
   </sheetData>
@@ -861,7 +891,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF643BE1-3816-4557-867E-C0ACDC26617E}">
-  <dimension ref="B2:EL32"/>
+  <dimension ref="B2:EN51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
@@ -4245,24 +4275,1674 @@
       </c>
       <c r="AM30" s="1">
         <f>Main!D3</f>
-        <v>8.16</v>
+        <v>7.73</v>
       </c>
     </row>
-    <row r="31" spans="2:142" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:142" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="I31" s="8">
+        <f t="shared" ref="I31:P31" si="101">I16</f>
+        <v>5.5</v>
+      </c>
+      <c r="J31" s="8">
+        <f t="shared" si="101"/>
+        <v>6.1000000000000014</v>
+      </c>
+      <c r="K31" s="8">
+        <f t="shared" si="101"/>
+        <v>8.3999999999999986</v>
+      </c>
+      <c r="L31" s="8">
+        <f t="shared" si="101"/>
+        <v>7.7000000000000011</v>
+      </c>
+      <c r="M31" s="8">
+        <f t="shared" si="101"/>
+        <v>9.1000000000000032</v>
+      </c>
+      <c r="N31" s="8">
+        <f t="shared" si="101"/>
+        <v>9.0999999999999943</v>
+      </c>
+      <c r="O31" s="8">
+        <f t="shared" si="101"/>
+        <v>10.9</v>
+      </c>
+      <c r="P31" s="8">
+        <f t="shared" si="101"/>
+        <v>-12.2</v>
+      </c>
+      <c r="Q31" s="8">
+        <f t="shared" ref="Q31:R31" si="102">Q16</f>
+        <v>11.304490000000008</v>
+      </c>
+      <c r="R31" s="8">
+        <f t="shared" si="102"/>
+        <v>12.527700000000003</v>
+      </c>
+      <c r="W31" s="8">
+        <f>W16</f>
+        <v>2.7999999999999972</v>
+      </c>
+      <c r="X31" s="8">
+        <f>X16</f>
+        <v>20.200000000000017</v>
+      </c>
+      <c r="Y31" s="8">
+        <f>Y16</f>
+        <v>34.299999999999997</v>
+      </c>
+      <c r="Z31" s="8">
+        <f t="shared" ref="Z31:AJ31" si="103">Z16</f>
+        <v>22.532190000000007</v>
+      </c>
+      <c r="AA31" s="8">
+        <f t="shared" si="103"/>
+        <v>52.497927099999984</v>
+      </c>
+      <c r="AB31" s="8">
+        <f t="shared" si="103"/>
+        <v>55.58150513799999</v>
+      </c>
+      <c r="AC31" s="8">
+        <f t="shared" si="103"/>
+        <v>61.126305368589996</v>
+      </c>
+      <c r="AD31" s="8">
+        <f t="shared" si="103"/>
+        <v>66.405238995705403</v>
+      </c>
+      <c r="AE31" s="8">
+        <f t="shared" si="103"/>
+        <v>71.471845372590664</v>
+      </c>
+      <c r="AF31" s="8">
+        <f t="shared" si="103"/>
+        <v>75.714099649870803</v>
+      </c>
+      <c r="AG31" s="8">
+        <f t="shared" si="103"/>
+        <v>78.987498710347069</v>
+      </c>
+      <c r="AH31" s="8">
+        <f t="shared" si="103"/>
+        <v>80.64911855386579</v>
+      </c>
+      <c r="AI31" s="8">
+        <f t="shared" si="103"/>
+        <v>82.346342464308847</v>
+      </c>
+      <c r="AJ31" s="8">
+        <f t="shared" si="103"/>
+        <v>84.079949451815125</v>
+      </c>
       <c r="AL31" s="7" t="s">
         <v>58</v>
       </c>
       <c r="AM31" s="10">
         <f>AM29/AM30-1</f>
-        <v>0.51137817971809962</v>
+        <v>0.5954522569857299</v>
       </c>
     </row>
     <row r="32" spans="2:142" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>22</v>
+      </c>
+      <c r="I32" s="2">
+        <v>-0.6</v>
+      </c>
+      <c r="J32" s="2">
+        <v>2</v>
+      </c>
+      <c r="K32" s="2">
+        <v>-0.5</v>
+      </c>
+      <c r="L32" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="M32" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="N32" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="O32" s="2">
+        <v>-0.9</v>
+      </c>
+      <c r="P32" s="2">
+        <v>-2.1</v>
+      </c>
+      <c r="Q32" s="2">
+        <v>-1</v>
+      </c>
+      <c r="R32" s="2">
+        <v>-1</v>
+      </c>
+      <c r="W32" s="2">
+        <v>1</v>
+      </c>
+      <c r="X32" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="Y32" s="2">
+        <f>SUM(K32:N32)</f>
+        <v>1.6</v>
+      </c>
+      <c r="Z32" s="2">
+        <f>SUM(O32:R32)</f>
+        <v>-5</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>0</v>
+      </c>
+      <c r="AE32">
+        <v>0</v>
+      </c>
+      <c r="AF32">
+        <v>0</v>
+      </c>
+      <c r="AG32">
+        <v>0</v>
+      </c>
+      <c r="AH32">
+        <v>0</v>
+      </c>
+      <c r="AI32">
+        <v>0</v>
+      </c>
+      <c r="AJ32">
+        <v>0</v>
+      </c>
       <c r="AL32" t="s">
         <v>59</v>
       </c>
       <c r="AM32" s="5" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>25</v>
+      </c>
+      <c r="I33" s="2">
+        <v>0</v>
+      </c>
+      <c r="J33" s="2">
+        <v>-2.1</v>
+      </c>
+      <c r="K33" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="L33" s="2">
+        <v>-1.7</v>
+      </c>
+      <c r="M33" s="2">
+        <v>-0.1</v>
+      </c>
+      <c r="N33" s="2">
+        <v>-0.3</v>
+      </c>
+      <c r="O33" s="2">
+        <v>-0.8</v>
+      </c>
+      <c r="P33" s="2">
+        <v>-5.5</v>
+      </c>
+      <c r="Q33" s="2">
+        <f>Q17</f>
+        <v>0</v>
+      </c>
+      <c r="R33" s="2">
+        <f>R17</f>
+        <v>0</v>
+      </c>
+      <c r="W33" s="2">
+        <v>-1.4</v>
+      </c>
+      <c r="X33" s="2">
+        <v>-3.8</v>
+      </c>
+      <c r="Y33" s="2">
+        <f t="shared" ref="Y33:Y40" si="104">SUM(K33:N33)</f>
+        <v>-1.9000000000000001</v>
+      </c>
+      <c r="Z33" s="2">
+        <f t="shared" ref="Z33:Z40" si="105">SUM(O33:R33)</f>
+        <v>-6.3</v>
+      </c>
+      <c r="AA33" s="2">
+        <f>-AA17</f>
+        <v>-7.8746890649999974</v>
+      </c>
+      <c r="AB33" s="2">
+        <f t="shared" ref="AB33:AJ33" si="106">-AB17</f>
+        <v>-8.3372257706999982</v>
+      </c>
+      <c r="AC33" s="2">
+        <f t="shared" si="106"/>
+        <v>-9.1689458052884998</v>
+      </c>
+      <c r="AD33" s="2">
+        <f t="shared" si="106"/>
+        <v>-9.9607858493558101</v>
+      </c>
+      <c r="AE33" s="2">
+        <f t="shared" si="106"/>
+        <v>-10.720776805888599</v>
+      </c>
+      <c r="AF33" s="2">
+        <f t="shared" si="106"/>
+        <v>-11.357114947480619</v>
+      </c>
+      <c r="AG33" s="2">
+        <f t="shared" si="106"/>
+        <v>-11.848124806552059</v>
+      </c>
+      <c r="AH33" s="2">
+        <f t="shared" si="106"/>
+        <v>-12.097367783079868</v>
+      </c>
+      <c r="AI33" s="2">
+        <f t="shared" si="106"/>
+        <v>-12.351951369646327</v>
+      </c>
+      <c r="AJ33" s="2">
+        <f t="shared" si="106"/>
+        <v>-12.611992417772269</v>
+      </c>
+    </row>
+    <row r="34" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>61</v>
+      </c>
+      <c r="I34" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="J34" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="K34" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="L34" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="M34" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="N34" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="O34" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="P34" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="Q34" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="R34" s="2">
+        <v>4</v>
+      </c>
+      <c r="W34" s="2">
+        <v>7</v>
+      </c>
+      <c r="X34" s="2">
+        <v>2.1</v>
+      </c>
+      <c r="Y34" s="2">
+        <f t="shared" si="104"/>
+        <v>5.8</v>
+      </c>
+      <c r="Z34" s="2">
+        <f t="shared" si="105"/>
+        <v>14.6</v>
+      </c>
+      <c r="AA34" s="2">
+        <f>Z34*1.03</f>
+        <v>15.038</v>
+      </c>
+      <c r="AB34" s="2">
+        <f t="shared" ref="AB34:AJ34" si="107">AA34*1.03</f>
+        <v>15.489140000000001</v>
+      </c>
+      <c r="AC34" s="2">
+        <f t="shared" si="107"/>
+        <v>15.953814200000002</v>
+      </c>
+      <c r="AD34" s="2">
+        <f t="shared" si="107"/>
+        <v>16.432428626000004</v>
+      </c>
+      <c r="AE34" s="2">
+        <f t="shared" si="107"/>
+        <v>16.925401484780004</v>
+      </c>
+      <c r="AF34" s="2">
+        <f t="shared" si="107"/>
+        <v>17.433163529323405</v>
+      </c>
+      <c r="AG34" s="2">
+        <f t="shared" si="107"/>
+        <v>17.956158435203108</v>
+      </c>
+      <c r="AH34" s="2">
+        <f t="shared" si="107"/>
+        <v>18.4948431882592</v>
+      </c>
+      <c r="AI34" s="2">
+        <f t="shared" si="107"/>
+        <v>19.049688483906976</v>
+      </c>
+      <c r="AJ34" s="2">
+        <f t="shared" si="107"/>
+        <v>19.621179138424186</v>
+      </c>
+    </row>
+    <row r="35" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>62</v>
+      </c>
+      <c r="I35" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="J35" s="2">
+        <v>-0.5</v>
+      </c>
+      <c r="K35" s="2">
+        <v>0</v>
+      </c>
+      <c r="L35" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="M35" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="N35" s="2">
+        <v>-0.6</v>
+      </c>
+      <c r="O35" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="P35" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="Q35" s="2">
+        <v>0</v>
+      </c>
+      <c r="R35" s="2">
+        <v>0</v>
+      </c>
+      <c r="W35" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="X35" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="Y35" s="2">
+        <f t="shared" si="104"/>
+        <v>0.50000000000000011</v>
+      </c>
+      <c r="Z35" s="2">
+        <f t="shared" si="105"/>
+        <v>0.4</v>
+      </c>
+      <c r="AA35" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>63</v>
+      </c>
+      <c r="I36" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="J36" s="2">
+        <v>1</v>
+      </c>
+      <c r="K36" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="L36" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="M36" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="N36" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="O36" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="P36" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q36" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="R36" s="2">
+        <v>2.4</v>
+      </c>
+      <c r="W36" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="X36" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="Y36" s="2">
+        <f t="shared" si="104"/>
+        <v>5.4</v>
+      </c>
+      <c r="Z36" s="2">
+        <f t="shared" si="105"/>
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="AA36" s="2">
+        <f>Z36*1.03</f>
+        <v>8.5490000000000013</v>
+      </c>
+      <c r="AB36" s="2">
+        <f t="shared" ref="AB36:AJ36" si="108">AA36*1.03</f>
+        <v>8.8054700000000015</v>
+      </c>
+      <c r="AC36" s="2">
+        <f t="shared" si="108"/>
+        <v>9.0696341000000018</v>
+      </c>
+      <c r="AD36" s="2">
+        <f t="shared" si="108"/>
+        <v>9.3417231230000013</v>
+      </c>
+      <c r="AE36" s="2">
+        <f t="shared" si="108"/>
+        <v>9.6219748166900008</v>
+      </c>
+      <c r="AF36" s="2">
+        <f t="shared" si="108"/>
+        <v>9.9106340611907005</v>
+      </c>
+      <c r="AG36" s="2">
+        <f t="shared" si="108"/>
+        <v>10.207953083026421</v>
+      </c>
+      <c r="AH36" s="2">
+        <f t="shared" si="108"/>
+        <v>10.514191675517214</v>
+      </c>
+      <c r="AI36" s="2">
+        <f t="shared" si="108"/>
+        <v>10.829617425782731</v>
+      </c>
+      <c r="AJ36" s="2">
+        <f t="shared" si="108"/>
+        <v>11.154505948556213</v>
+      </c>
+    </row>
+    <row r="37" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>64</v>
+      </c>
+      <c r="I37" s="2">
+        <v>0</v>
+      </c>
+      <c r="J37" s="2">
+        <v>0</v>
+      </c>
+      <c r="K37" s="2">
+        <v>0</v>
+      </c>
+      <c r="L37" s="2">
+        <v>0</v>
+      </c>
+      <c r="M37" s="2">
+        <v>0</v>
+      </c>
+      <c r="N37" s="2">
+        <v>0</v>
+      </c>
+      <c r="O37" s="2">
+        <v>0</v>
+      </c>
+      <c r="P37" s="2">
+        <v>21.2</v>
+      </c>
+      <c r="Q37" s="2">
+        <v>0</v>
+      </c>
+      <c r="R37" s="2">
+        <v>0</v>
+      </c>
+      <c r="W37" s="2">
+        <v>10.9</v>
+      </c>
+      <c r="X37" s="2">
+        <v>6.9</v>
+      </c>
+      <c r="Y37" s="2">
+        <f t="shared" si="104"/>
+        <v>0</v>
+      </c>
+      <c r="Z37" s="2">
+        <f t="shared" si="105"/>
+        <v>21.2</v>
+      </c>
+      <c r="AA37" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG37" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH37" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI37" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ37" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>65</v>
+      </c>
+      <c r="I38" s="2">
+        <v>-2.9</v>
+      </c>
+      <c r="J38" s="2">
+        <v>0</v>
+      </c>
+      <c r="K38" s="2">
+        <v>0</v>
+      </c>
+      <c r="L38" s="2">
+        <v>-7.2</v>
+      </c>
+      <c r="M38" s="2">
+        <v>0</v>
+      </c>
+      <c r="N38" s="2">
+        <v>0</v>
+      </c>
+      <c r="O38" s="2">
+        <v>0</v>
+      </c>
+      <c r="P38" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="2">
+        <v>0</v>
+      </c>
+      <c r="R38" s="2">
+        <v>0</v>
+      </c>
+      <c r="W38" s="2">
+        <v>-0.8</v>
+      </c>
+      <c r="X38" s="2">
+        <f>-4.6-2.9</f>
+        <v>-7.5</v>
+      </c>
+      <c r="Y38" s="2">
+        <f t="shared" si="104"/>
+        <v>-7.2</v>
+      </c>
+      <c r="Z38" s="2">
+        <v>-20</v>
+      </c>
+      <c r="AA38" s="2">
+        <f>Z38*0.98</f>
+        <v>-19.600000000000001</v>
+      </c>
+      <c r="AB38" s="2">
+        <f t="shared" ref="AB38:AJ38" si="109">AA38*0.98</f>
+        <v>-19.208000000000002</v>
+      </c>
+      <c r="AC38" s="2">
+        <f t="shared" si="109"/>
+        <v>-18.823840000000001</v>
+      </c>
+      <c r="AD38" s="2">
+        <f t="shared" si="109"/>
+        <v>-18.447363200000002</v>
+      </c>
+      <c r="AE38" s="2">
+        <f t="shared" si="109"/>
+        <v>-18.078415936000003</v>
+      </c>
+      <c r="AF38" s="2">
+        <f t="shared" si="109"/>
+        <v>-17.716847617280003</v>
+      </c>
+      <c r="AG38" s="2">
+        <f t="shared" si="109"/>
+        <v>-17.362510664934401</v>
+      </c>
+      <c r="AH38" s="2">
+        <f t="shared" si="109"/>
+        <v>-17.015260451635712</v>
+      </c>
+      <c r="AI38" s="2">
+        <f t="shared" si="109"/>
+        <v>-16.674955242602998</v>
+      </c>
+      <c r="AJ38" s="2">
+        <f t="shared" si="109"/>
+        <v>-16.341456137750939</v>
+      </c>
+    </row>
+    <row r="39" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
+        <v>66</v>
+      </c>
+      <c r="I39" s="2">
+        <v>-5.2</v>
+      </c>
+      <c r="J39" s="2">
+        <v>-3.3</v>
+      </c>
+      <c r="K39" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="L39" s="2">
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="M39" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="N39" s="2">
+        <v>-0.7</v>
+      </c>
+      <c r="O39" s="2">
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="P39" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="Q39" s="2">
+        <v>0</v>
+      </c>
+      <c r="R39" s="2">
+        <v>0</v>
+      </c>
+      <c r="W39" s="2">
+        <f>-5.8-0.1</f>
+        <v>-5.8999999999999995</v>
+      </c>
+      <c r="X39" s="2">
+        <f>-10.4+0.1</f>
+        <v>-10.3</v>
+      </c>
+      <c r="Y39" s="2">
+        <f t="shared" si="104"/>
+        <v>-0.19999999999999996</v>
+      </c>
+      <c r="Z39" s="2">
+        <f t="shared" si="105"/>
+        <v>-0.50000000000000022</v>
+      </c>
+      <c r="AA39" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF39" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG39" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI39" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ39" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
+        <v>67</v>
+      </c>
+      <c r="I40" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="J40" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="K40" s="2">
+        <v>-3</v>
+      </c>
+      <c r="L40" s="2">
+        <v>-1.2</v>
+      </c>
+      <c r="M40" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="N40" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="O40" s="2">
+        <v>-1.2</v>
+      </c>
+      <c r="P40" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="Q40" s="2">
+        <v>0</v>
+      </c>
+      <c r="R40" s="2">
+        <v>0</v>
+      </c>
+      <c r="W40" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="X40" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="Y40" s="2">
+        <f t="shared" si="104"/>
+        <v>-0.10000000000000009</v>
+      </c>
+      <c r="Z40" s="2">
+        <f t="shared" si="105"/>
+        <v>-0.5</v>
+      </c>
+      <c r="AA40" s="2">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="2">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="2">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="2">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF40" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG40" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH40" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI40" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ40" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:144" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="I41" s="8">
+        <f t="shared" ref="I41:P41" si="110">I31+SUM(I32:I40)</f>
+        <v>-0.5</v>
+      </c>
+      <c r="J41" s="8">
+        <f t="shared" si="110"/>
+        <v>7.0000000000000018</v>
+      </c>
+      <c r="K41" s="8">
+        <f t="shared" si="110"/>
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="L41" s="8">
+        <f t="shared" si="110"/>
+        <v>0.60000000000000053</v>
+      </c>
+      <c r="M41" s="8">
+        <f t="shared" si="110"/>
+        <v>15.000000000000004</v>
+      </c>
+      <c r="N41" s="8">
+        <f t="shared" si="110"/>
+        <v>13.899999999999995</v>
+      </c>
+      <c r="O41" s="8">
+        <f t="shared" si="110"/>
+        <v>11.299999999999999</v>
+      </c>
+      <c r="P41" s="8">
+        <f t="shared" si="110"/>
+        <v>9.5</v>
+      </c>
+      <c r="Q41" s="8">
+        <f t="shared" ref="Q41:R41" si="111">Q31+SUM(Q32:Q40)</f>
+        <v>16.004490000000008</v>
+      </c>
+      <c r="R41" s="8">
+        <f t="shared" si="111"/>
+        <v>17.927700000000002</v>
+      </c>
+      <c r="W41" s="8">
+        <f>W31+SUM(W32:W40)</f>
+        <v>20.799999999999997</v>
+      </c>
+      <c r="X41" s="8">
+        <f>X31+SUM(X32:X40)</f>
+        <v>17.900000000000016</v>
+      </c>
+      <c r="Y41" s="8">
+        <f>Y31+SUM(Y32:Y40)</f>
+        <v>38.199999999999996</v>
+      </c>
+      <c r="Z41" s="8">
+        <f>Z31+SUM(Z32:Z40)</f>
+        <v>34.73219000000001</v>
+      </c>
+      <c r="AA41" s="8">
+        <f>AA31+SUM(AA32:AA40)</f>
+        <v>48.610238034999988</v>
+      </c>
+      <c r="AB41" s="8">
+        <f t="shared" ref="AB41:AJ41" si="112">AB31+SUM(AB32:AB40)</f>
+        <v>52.330889367299989</v>
+      </c>
+      <c r="AC41" s="8">
+        <f t="shared" si="112"/>
+        <v>58.156967863301503</v>
+      </c>
+      <c r="AD41" s="8">
+        <f t="shared" si="112"/>
+        <v>63.771241695349595</v>
+      </c>
+      <c r="AE41" s="8">
+        <f t="shared" si="112"/>
+        <v>69.22002893217207</v>
+      </c>
+      <c r="AF41" s="8">
+        <f t="shared" si="112"/>
+        <v>73.983934675624283</v>
+      </c>
+      <c r="AG41" s="8">
+        <f t="shared" si="112"/>
+        <v>77.940974757090132</v>
+      </c>
+      <c r="AH41" s="8">
+        <f t="shared" si="112"/>
+        <v>80.545525182926625</v>
+      </c>
+      <c r="AI41" s="8">
+        <f t="shared" si="112"/>
+        <v>83.198741761749233</v>
+      </c>
+      <c r="AJ41" s="8">
+        <f t="shared" si="112"/>
+        <v>85.902185983272318</v>
+      </c>
+    </row>
+    <row r="42" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="B42" t="s">
+        <v>69</v>
+      </c>
+      <c r="I42" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="J42" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="K42" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="L42" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="M42" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="N42" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="O42" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="P42" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="Q42" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="R42" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="V42">
+        <v>0.3</v>
+      </c>
+      <c r="W42" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="X42" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="Y42" s="2">
+        <f>SUM(K42:N42)</f>
+        <v>1.3</v>
+      </c>
+      <c r="Z42" s="2">
+        <f>SUM(O42:R42)</f>
+        <v>1.4</v>
+      </c>
+      <c r="AA42" s="2">
+        <f>Z42*1.05</f>
+        <v>1.47</v>
+      </c>
+      <c r="AB42" s="2">
+        <f t="shared" ref="AB42:AJ42" si="113">AA42*1.05</f>
+        <v>1.5435000000000001</v>
+      </c>
+      <c r="AC42" s="2">
+        <f t="shared" si="113"/>
+        <v>1.6206750000000001</v>
+      </c>
+      <c r="AD42" s="2">
+        <f t="shared" si="113"/>
+        <v>1.7017087500000001</v>
+      </c>
+      <c r="AE42" s="2">
+        <f t="shared" si="113"/>
+        <v>1.7867941875000002</v>
+      </c>
+      <c r="AF42" s="2">
+        <f t="shared" si="113"/>
+        <v>1.8761338968750003</v>
+      </c>
+      <c r="AG42" s="2">
+        <f t="shared" si="113"/>
+        <v>1.9699405917187505</v>
+      </c>
+      <c r="AH42" s="2">
+        <f t="shared" si="113"/>
+        <v>2.068437621304688</v>
+      </c>
+      <c r="AI42" s="2">
+        <f t="shared" si="113"/>
+        <v>2.1718595023699225</v>
+      </c>
+      <c r="AJ42" s="2">
+        <f t="shared" si="113"/>
+        <v>2.2804524774884189</v>
+      </c>
+    </row>
+    <row r="43" spans="2:144" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I43" s="8">
+        <f t="shared" ref="I43:P43" si="114">I41-I42</f>
+        <v>-0.6</v>
+      </c>
+      <c r="J43" s="8">
+        <f t="shared" si="114"/>
+        <v>6.8000000000000016</v>
+      </c>
+      <c r="K43" s="8">
+        <f t="shared" si="114"/>
+        <v>8.6</v>
+      </c>
+      <c r="L43" s="8">
+        <f t="shared" si="114"/>
+        <v>-0.19999999999999951</v>
+      </c>
+      <c r="M43" s="8">
+        <f t="shared" si="114"/>
+        <v>14.700000000000003</v>
+      </c>
+      <c r="N43" s="8">
+        <f t="shared" si="114"/>
+        <v>13.799999999999995</v>
+      </c>
+      <c r="O43" s="8">
+        <f t="shared" si="114"/>
+        <v>10.999999999999998</v>
+      </c>
+      <c r="P43" s="8">
+        <f t="shared" si="114"/>
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="Q43" s="8">
+        <f t="shared" ref="Q43:R43" si="115">Q41-Q42</f>
+        <v>15.604490000000007</v>
+      </c>
+      <c r="R43" s="8">
+        <f t="shared" si="115"/>
+        <v>17.427700000000002</v>
+      </c>
+      <c r="W43" s="8">
+        <f>W41-W42</f>
+        <v>20.499999999999996</v>
+      </c>
+      <c r="X43" s="8">
+        <f>X41-X42</f>
+        <v>17.400000000000016</v>
+      </c>
+      <c r="Y43" s="8">
+        <f>Y41-Y42</f>
+        <v>36.9</v>
+      </c>
+      <c r="Z43" s="8">
+        <f>Z41-Z42</f>
+        <v>33.332190000000011</v>
+      </c>
+      <c r="AA43" s="8">
+        <f>AA41-AA42</f>
+        <v>47.140238034999989</v>
+      </c>
+      <c r="AB43" s="8">
+        <f t="shared" ref="AB43:AJ43" si="116">AB41-AB42</f>
+        <v>50.787389367299987</v>
+      </c>
+      <c r="AC43" s="8">
+        <f t="shared" si="116"/>
+        <v>56.536292863301504</v>
+      </c>
+      <c r="AD43" s="8">
+        <f t="shared" si="116"/>
+        <v>62.069532945349593</v>
+      </c>
+      <c r="AE43" s="8">
+        <f t="shared" si="116"/>
+        <v>67.433234744672063</v>
+      </c>
+      <c r="AF43" s="8">
+        <f t="shared" si="116"/>
+        <v>72.107800778749279</v>
+      </c>
+      <c r="AG43" s="8">
+        <f t="shared" si="116"/>
+        <v>75.971034165371378</v>
+      </c>
+      <c r="AH43" s="8">
+        <f t="shared" si="116"/>
+        <v>78.477087561621943</v>
+      </c>
+      <c r="AI43" s="8">
+        <f t="shared" si="116"/>
+        <v>81.026882259379306</v>
+      </c>
+      <c r="AJ43" s="8">
+        <f t="shared" si="116"/>
+        <v>83.621733505783894</v>
+      </c>
+      <c r="AK43" s="7">
+        <f>AJ43*(1+$AM$24)</f>
+        <v>82.785516170726055</v>
+      </c>
+      <c r="AL43" s="7">
+        <f t="shared" ref="AL43:CW43" si="117">AK43*(1+$AM$24)</f>
+        <v>81.957661009018793</v>
+      </c>
+      <c r="AM43" s="7">
+        <f t="shared" si="117"/>
+        <v>81.138084398928598</v>
+      </c>
+      <c r="AN43" s="7">
+        <f t="shared" si="117"/>
+        <v>80.326703554939314</v>
+      </c>
+      <c r="AO43" s="7">
+        <f t="shared" si="117"/>
+        <v>79.523436519389918</v>
+      </c>
+      <c r="AP43" s="7">
+        <f t="shared" si="117"/>
+        <v>78.728202154196012</v>
+      </c>
+      <c r="AQ43" s="7">
+        <f t="shared" si="117"/>
+        <v>77.940920132654057</v>
+      </c>
+      <c r="AR43" s="7">
+        <f t="shared" si="117"/>
+        <v>77.161510931327513</v>
+      </c>
+      <c r="AS43" s="7">
+        <f t="shared" si="117"/>
+        <v>76.389895822014239</v>
+      </c>
+      <c r="AT43" s="7">
+        <f t="shared" si="117"/>
+        <v>75.6259968637941</v>
+      </c>
+      <c r="AU43" s="7">
+        <f t="shared" si="117"/>
+        <v>74.869736895156151</v>
+      </c>
+      <c r="AV43" s="7">
+        <f t="shared" si="117"/>
+        <v>74.121039526204584</v>
+      </c>
+      <c r="AW43" s="7">
+        <f t="shared" si="117"/>
+        <v>73.379829130942539</v>
+      </c>
+      <c r="AX43" s="7">
+        <f t="shared" si="117"/>
+        <v>72.646030839633113</v>
+      </c>
+      <c r="AY43" s="7">
+        <f t="shared" si="117"/>
+        <v>71.919570531236786</v>
+      </c>
+      <c r="AZ43" s="7">
+        <f t="shared" si="117"/>
+        <v>71.200374825924413</v>
+      </c>
+      <c r="BA43" s="7">
+        <f t="shared" si="117"/>
+        <v>70.488371077665164</v>
+      </c>
+      <c r="BB43" s="7">
+        <f t="shared" si="117"/>
+        <v>69.783487366888508</v>
+      </c>
+      <c r="BC43" s="7">
+        <f t="shared" si="117"/>
+        <v>69.085652493219627</v>
+      </c>
+      <c r="BD43" s="7">
+        <f t="shared" si="117"/>
+        <v>68.394795968287426</v>
+      </c>
+      <c r="BE43" s="7">
+        <f t="shared" si="117"/>
+        <v>67.710848008604557</v>
+      </c>
+      <c r="BF43" s="7">
+        <f t="shared" si="117"/>
+        <v>67.03373952851851</v>
+      </c>
+      <c r="BG43" s="7">
+        <f t="shared" si="117"/>
+        <v>66.363402133233322</v>
+      </c>
+      <c r="BH43" s="7">
+        <f t="shared" si="117"/>
+        <v>65.699768111900994</v>
+      </c>
+      <c r="BI43" s="7">
+        <f t="shared" si="117"/>
+        <v>65.042770430781985</v>
+      </c>
+      <c r="BJ43" s="7">
+        <f t="shared" si="117"/>
+        <v>64.392342726474169</v>
+      </c>
+      <c r="BK43" s="7">
+        <f t="shared" si="117"/>
+        <v>63.748419299209424</v>
+      </c>
+      <c r="BL43" s="7">
+        <f t="shared" si="117"/>
+        <v>63.110935106217326</v>
+      </c>
+      <c r="BM43" s="7">
+        <f t="shared" si="117"/>
+        <v>62.479825755155154</v>
+      </c>
+      <c r="BN43" s="7">
+        <f t="shared" si="117"/>
+        <v>61.855027497603601</v>
+      </c>
+      <c r="BO43" s="7">
+        <f t="shared" si="117"/>
+        <v>61.236477222627563</v>
+      </c>
+      <c r="BP43" s="7">
+        <f t="shared" si="117"/>
+        <v>60.624112450401284</v>
+      </c>
+      <c r="BQ43" s="7">
+        <f t="shared" si="117"/>
+        <v>60.017871325897268</v>
+      </c>
+      <c r="BR43" s="7">
+        <f t="shared" si="117"/>
+        <v>59.417692612638298</v>
+      </c>
+      <c r="BS43" s="7">
+        <f t="shared" si="117"/>
+        <v>58.823515686511918</v>
+      </c>
+      <c r="BT43" s="7">
+        <f t="shared" si="117"/>
+        <v>58.235280529646801</v>
+      </c>
+      <c r="BU43" s="7">
+        <f t="shared" si="117"/>
+        <v>57.652927724350334</v>
+      </c>
+      <c r="BV43" s="7">
+        <f t="shared" si="117"/>
+        <v>57.076398447106833</v>
+      </c>
+      <c r="BW43" s="7">
+        <f t="shared" si="117"/>
+        <v>56.505634462635761</v>
+      </c>
+      <c r="BX43" s="7">
+        <f t="shared" si="117"/>
+        <v>55.940578118009405</v>
+      </c>
+      <c r="BY43" s="7">
+        <f t="shared" si="117"/>
+        <v>55.381172336829309</v>
+      </c>
+      <c r="BZ43" s="7">
+        <f t="shared" si="117"/>
+        <v>54.827360613461018</v>
+      </c>
+      <c r="CA43" s="7">
+        <f t="shared" si="117"/>
+        <v>54.27908700732641</v>
+      </c>
+      <c r="CB43" s="7">
+        <f t="shared" si="117"/>
+        <v>53.736296137253149</v>
+      </c>
+      <c r="CC43" s="7">
+        <f t="shared" si="117"/>
+        <v>53.198933175880619</v>
+      </c>
+      <c r="CD43" s="7">
+        <f t="shared" si="117"/>
+        <v>52.666943844121811</v>
+      </c>
+      <c r="CE43" s="7">
+        <f t="shared" si="117"/>
+        <v>52.140274405680593</v>
+      </c>
+      <c r="CF43" s="7">
+        <f t="shared" si="117"/>
+        <v>51.618871661623785</v>
+      </c>
+      <c r="CG43" s="7">
+        <f t="shared" si="117"/>
+        <v>51.102682945007544</v>
+      </c>
+      <c r="CH43" s="7">
+        <f t="shared" si="117"/>
+        <v>50.59165611555747</v>
+      </c>
+      <c r="CI43" s="7">
+        <f t="shared" si="117"/>
+        <v>50.085739554401897</v>
+      </c>
+      <c r="CJ43" s="7">
+        <f t="shared" si="117"/>
+        <v>49.58488215885788</v>
+      </c>
+      <c r="CK43" s="7">
+        <f t="shared" si="117"/>
+        <v>49.089033337269299</v>
+      </c>
+      <c r="CL43" s="7">
+        <f t="shared" si="117"/>
+        <v>48.598143003896602</v>
+      </c>
+      <c r="CM43" s="7">
+        <f t="shared" si="117"/>
+        <v>48.112161573857634</v>
+      </c>
+      <c r="CN43" s="7">
+        <f t="shared" si="117"/>
+        <v>47.631039958119054</v>
+      </c>
+      <c r="CO43" s="7">
+        <f t="shared" si="117"/>
+        <v>47.154729558537866</v>
+      </c>
+      <c r="CP43" s="7">
+        <f t="shared" si="117"/>
+        <v>46.683182262952485</v>
+      </c>
+      <c r="CQ43" s="7">
+        <f t="shared" si="117"/>
+        <v>46.216350440322962</v>
+      </c>
+      <c r="CR43" s="7">
+        <f t="shared" si="117"/>
+        <v>45.754186935919734</v>
+      </c>
+      <c r="CS43" s="7">
+        <f t="shared" si="117"/>
+        <v>45.296645066560536</v>
+      </c>
+      <c r="CT43" s="7">
+        <f t="shared" si="117"/>
+        <v>44.84367861589493</v>
+      </c>
+      <c r="CU43" s="7">
+        <f t="shared" si="117"/>
+        <v>44.39524182973598</v>
+      </c>
+      <c r="CV43" s="7">
+        <f t="shared" si="117"/>
+        <v>43.951289411438623</v>
+      </c>
+      <c r="CW43" s="7">
+        <f t="shared" si="117"/>
+        <v>43.511776517324236</v>
+      </c>
+      <c r="CX43" s="7">
+        <f t="shared" ref="CX43:EN43" si="118">CW43*(1+$AM$24)</f>
+        <v>43.07665875215099</v>
+      </c>
+      <c r="CY43" s="7">
+        <f t="shared" si="118"/>
+        <v>42.64589216462948</v>
+      </c>
+      <c r="CZ43" s="7">
+        <f t="shared" si="118"/>
+        <v>42.219433242983186</v>
+      </c>
+      <c r="DA43" s="7">
+        <f t="shared" si="118"/>
+        <v>41.797238910553354</v>
+      </c>
+      <c r="DB43" s="7">
+        <f t="shared" si="118"/>
+        <v>41.379266521447818</v>
+      </c>
+      <c r="DC43" s="7">
+        <f t="shared" si="118"/>
+        <v>40.965473856233338</v>
+      </c>
+      <c r="DD43" s="7">
+        <f t="shared" si="118"/>
+        <v>40.555819117671007</v>
+      </c>
+      <c r="DE43" s="7">
+        <f t="shared" si="118"/>
+        <v>40.150260926494298</v>
+      </c>
+      <c r="DF43" s="7">
+        <f t="shared" si="118"/>
+        <v>39.748758317229353</v>
+      </c>
+      <c r="DG43" s="7">
+        <f t="shared" si="118"/>
+        <v>39.35127073405706</v>
+      </c>
+      <c r="DH43" s="7">
+        <f t="shared" si="118"/>
+        <v>38.95775802671649</v>
+      </c>
+      <c r="DI43" s="7">
+        <f t="shared" si="118"/>
+        <v>38.568180446449325</v>
+      </c>
+      <c r="DJ43" s="7">
+        <f t="shared" si="118"/>
+        <v>38.182498641984829</v>
+      </c>
+      <c r="DK43" s="7">
+        <f t="shared" si="118"/>
+        <v>37.800673655564978</v>
+      </c>
+      <c r="DL43" s="7">
+        <f t="shared" si="118"/>
+        <v>37.42266691900933</v>
+      </c>
+      <c r="DM43" s="7">
+        <f t="shared" si="118"/>
+        <v>37.048440249819237</v>
+      </c>
+      <c r="DN43" s="7">
+        <f t="shared" si="118"/>
+        <v>36.677955847321044</v>
+      </c>
+      <c r="DO43" s="7">
+        <f t="shared" si="118"/>
+        <v>36.311176288847832</v>
+      </c>
+      <c r="DP43" s="7">
+        <f t="shared" si="118"/>
+        <v>35.948064525959353</v>
+      </c>
+      <c r="DQ43" s="7">
+        <f t="shared" si="118"/>
+        <v>35.588583880699758</v>
+      </c>
+      <c r="DR43" s="7">
+        <f t="shared" si="118"/>
+        <v>35.23269804189276</v>
+      </c>
+      <c r="DS43" s="7">
+        <f t="shared" si="118"/>
+        <v>34.880371061473831</v>
+      </c>
+      <c r="DT43" s="7">
+        <f t="shared" si="118"/>
+        <v>34.531567350859092</v>
+      </c>
+      <c r="DU43" s="7">
+        <f t="shared" si="118"/>
+        <v>34.186251677350498</v>
+      </c>
+      <c r="DV43" s="7">
+        <f t="shared" si="118"/>
+        <v>33.844389160576995</v>
+      </c>
+      <c r="DW43" s="7">
+        <f t="shared" si="118"/>
+        <v>33.505945268971224</v>
+      </c>
+      <c r="DX43" s="7">
+        <f t="shared" si="118"/>
+        <v>33.170885816281512</v>
+      </c>
+      <c r="DY43" s="7">
+        <f t="shared" si="118"/>
+        <v>32.839176958118699</v>
+      </c>
+      <c r="DZ43" s="7">
+        <f t="shared" si="118"/>
+        <v>32.510785188537511</v>
+      </c>
+      <c r="EA43" s="7">
+        <f t="shared" si="118"/>
+        <v>32.185677336652134</v>
+      </c>
+      <c r="EB43" s="7">
+        <f t="shared" si="118"/>
+        <v>31.863820563285611</v>
+      </c>
+      <c r="EC43" s="7">
+        <f t="shared" si="118"/>
+        <v>31.545182357652756</v>
+      </c>
+      <c r="ED43" s="7">
+        <f t="shared" si="118"/>
+        <v>31.229730534076229</v>
+      </c>
+      <c r="EE43" s="7">
+        <f t="shared" si="118"/>
+        <v>30.917433228735465</v>
+      </c>
+      <c r="EF43" s="7">
+        <f t="shared" si="118"/>
+        <v>30.60825889644811</v>
+      </c>
+      <c r="EG43" s="7">
+        <f t="shared" si="118"/>
+        <v>30.302176307483627</v>
+      </c>
+      <c r="EH43" s="7">
+        <f t="shared" si="118"/>
+        <v>29.999154544408789</v>
+      </c>
+      <c r="EI43" s="7">
+        <f t="shared" si="118"/>
+        <v>29.699162998964702</v>
+      </c>
+      <c r="EJ43" s="7">
+        <f t="shared" si="118"/>
+        <v>29.402171368975054</v>
+      </c>
+      <c r="EK43" s="7">
+        <f t="shared" si="118"/>
+        <v>29.108149655285303</v>
+      </c>
+      <c r="EL43" s="7">
+        <f t="shared" si="118"/>
+        <v>28.81706815873245</v>
+      </c>
+      <c r="EM43" s="7">
+        <f t="shared" si="118"/>
+        <v>28.528897477145126</v>
+      </c>
+      <c r="EN43" s="7">
+        <f t="shared" si="118"/>
+        <v>28.243608502373675</v>
+      </c>
+    </row>
+    <row r="45" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="W45" s="9">
+        <f>W42/V42-1</f>
+        <v>0</v>
+      </c>
+      <c r="X45" s="9">
+        <f t="shared" ref="X45:Z45" si="119">X42/W42-1</f>
+        <v>0.66666666666666674</v>
+      </c>
+      <c r="Y45" s="9">
+        <f t="shared" si="119"/>
+        <v>1.6</v>
+      </c>
+      <c r="Z45" s="9">
+        <f t="shared" si="119"/>
+        <v>7.6923076923076872E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="AL46" t="s">
+        <v>53</v>
+      </c>
+      <c r="AM46" s="2">
+        <f>NPV(AM25,Z43:EN43)</f>
+        <v>587.88464249081744</v>
+      </c>
+    </row>
+    <row r="47" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="AL47" t="s">
+        <v>57</v>
+      </c>
+      <c r="AM47" s="2">
+        <f>Main!D8</f>
+        <v>-71.5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:144" x14ac:dyDescent="0.3">
+      <c r="AL48" t="s">
+        <v>54</v>
+      </c>
+      <c r="AM48" s="2">
+        <f>AM46+AM47</f>
+        <v>516.38464249081744</v>
+      </c>
+    </row>
+    <row r="49" spans="38:39" x14ac:dyDescent="0.3">
+      <c r="AL49" t="s">
+        <v>55</v>
+      </c>
+      <c r="AM49" s="1">
+        <f>AM48/AJ19</f>
+        <v>14.464555812067715</v>
+      </c>
+    </row>
+    <row r="50" spans="38:39" x14ac:dyDescent="0.3">
+      <c r="AL50" t="s">
+        <v>56</v>
+      </c>
+      <c r="AM50" s="1">
+        <f>Main!D3</f>
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="51" spans="38:39" x14ac:dyDescent="0.3">
+      <c r="AL51" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="AM51" s="10">
+        <f>AM49/AM50-1</f>
+        <v>0.87122326158702634</v>
       </c>
     </row>
   </sheetData>
